--- a/Qualidade_Sessoes.xlsx
+++ b/Qualidade_Sessoes.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -414,7 +414,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -424,12 +424,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>RAMIANE</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Sessão_2</t>
+          <t>Sessão_5</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -444,17 +444,17 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>18-Feb-2026</t>
+          <t>26-Mar-2026</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3918786000009856153</t>
+          <t>3918786000009891291</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -471,7 +471,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -486,7 +486,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Sessão_3</t>
+          <t>Sessão_7</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -501,17 +501,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>25-Feb-2026</t>
+          <t>25-Mar-2026</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3918786000009856149</t>
+          <t>3918786000009891287</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -528,7 +528,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -543,12 +543,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Sessão_4</t>
+          <t>Sessão_6</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -558,17 +558,17 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>04-Mar-2026</t>
+          <t>25-Mar-2026</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3918786000009856145</t>
+          <t>3918786000009888175</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -585,7 +585,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -595,17 +595,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>RAMIANE</t>
+          <t>MUELEGE</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Sessão_2</t>
+          <t>Sessão_6</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -615,7 +615,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>19-Feb-2026</t>
+          <t>19-Mar-2026</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -625,7 +625,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3918786000009856141</t>
+          <t>3918786000009886133</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -642,7 +642,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -652,17 +652,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>RAMIANE</t>
+          <t>MUELEGE</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Sessão_3</t>
+          <t>Sessão_5</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -670,14 +670,19 @@
           <t>0</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>12-Mar-2026</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3918786000009856137</t>
+          <t>3918786000009886129</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -694,7 +699,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -709,7 +714,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Sessão_5</t>
+          <t>Sessão_2</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -724,17 +729,17 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>11-Mar-2026</t>
+          <t>18-Feb-2026</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3918786000009856133</t>
+          <t>3918786000009856153</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -751,7 +756,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -766,7 +771,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Sessão_6</t>
+          <t>Sessão_3</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -781,17 +786,17 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>17-Mar-2026</t>
+          <t>25-Feb-2026</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3918786000009856129</t>
+          <t>3918786000009856149</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -808,55 +813,335 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>TOPELANE</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Sessão_4</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>04-Mar-2026</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>3918786000009856145</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>RAMIANE</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Sessão_2</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>19-Feb-2026</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>3918786000009856141</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>RAMIANE</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Sessão_3</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>3918786000009856137</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>TOPELANE</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Sessão_5</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>11-Mar-2026</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>3918786000009856133</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>TOPELANE</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Sessão_6</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>17-Mar-2026</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>3918786000009856129</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
         <is>
           <t>RAMIANE</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>Sessão_4</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
         <is>
           <t>19-Mar-2026</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>3918786000009856125</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>Monapo</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1123,13 +1408,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9D864F1B-50B7-4B48-B29C-EB0E98691091}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{68751767-3BB7-432F-876E-8BC47C781FE2}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{72214033-EFBB-4A83-8B22-4AC6F575DD0C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{61C623FD-AAF4-4CD2-A205-63301154B33F}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{030493C4-A909-4310-BB99-CE535C21ABB0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5C516DBE-EE66-40DF-BFA8-6B93641F9A18}"/>
 </file>
--- a/Qualidade_Sessoes.xlsx
+++ b/Qualidade_Sessoes.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:K44"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -429,7 +429,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Sessão_5</t>
+          <t>Sessão_7</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -444,7 +444,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>26-Mar-2026</t>
+          <t>09-Apr-2026</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -454,7 +454,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3918786000009891291</t>
+          <t>3918786000010020060</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -471,7 +471,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -481,17 +481,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>MESEREPANE</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Sessão_7</t>
+          <t>Sessão_9</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -501,17 +501,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>25-Mar-2026</t>
+          <t>09-Apr-2026</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3918786000009891287</t>
+          <t>3918786000010019064</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -528,7 +528,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -538,17 +538,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>MONAPO RIO</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Sessão_6</t>
+          <t>Sessão_9</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -558,17 +558,17 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>25-Mar-2026</t>
+          <t>08-Apr-2026</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3918786000009888175</t>
+          <t>3918786000010011002</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -585,7 +585,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -595,12 +595,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MUELEGE</t>
+          <t>TOPELANE</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Sessão_6</t>
+          <t>Sessão_8</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -615,17 +615,17 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>19-Mar-2026</t>
+          <t>08-Apr-2026</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3918786000009886133</t>
+          <t>3918786000010007188</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -642,7 +642,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -657,7 +657,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Sessão_5</t>
+          <t>Sessão_8</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -672,17 +672,17 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>12-Mar-2026</t>
+          <t>09-Apr-2026</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3918786000009886129</t>
+          <t>3918786000010007186</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -699,7 +699,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -714,12 +714,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Sessão_2</t>
+          <t>Sessão_7</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -729,17 +729,17 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>18-Feb-2026</t>
+          <t>27-Mar-2026</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3918786000009856153</t>
+          <t>3918786000009978061</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -756,7 +756,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -771,12 +771,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Sessão_3</t>
+          <t>Sessão_7</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -786,17 +786,17 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>25-Feb-2026</t>
+          <t>25-Mar-2026</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3918786000009856149</t>
+          <t>3918786000009978059</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -813,7 +813,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -828,12 +828,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Sessão_4</t>
+          <t>Sessão_6</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -843,17 +843,17 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>04-Mar-2026</t>
+          <t>25-Mar-2026</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3918786000009856145</t>
+          <t>3918786000009978057</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -870,7 +870,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -880,17 +880,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>RAMIANE</t>
+          <t>TOPELANE</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Sessão_2</t>
+          <t>Sessão_5</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -900,17 +900,17 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>19-Feb-2026</t>
+          <t>11-Mar-2026</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3918786000009856141</t>
+          <t>3918786000009978055</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -937,17 +937,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>RAMIANE</t>
+          <t>TOPELANE</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Sessão_3</t>
+          <t>Sessão_5</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -955,14 +955,19 @@
           <t>0</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>11-Mar-2026</t>
+        </is>
+      </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3918786000009856137</t>
+          <t>3918786000009978053</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -979,7 +984,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -989,17 +994,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>MUELEGE</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Sessão_5</t>
+          <t>Sessão_7</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1009,17 +1014,17 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>11-Mar-2026</t>
+          <t>02-Apr-2026</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3918786000009856133</t>
+          <t>3918786000009978051</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1046,17 +1051,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>MESEREPANE</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Sessão_6</t>
+          <t>Sessão_8</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1066,17 +1071,17 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>17-Mar-2026</t>
+          <t>02-Apr-2026</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3918786000009856129</t>
+          <t>3918786000009975096</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1093,55 +1098,1760 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>RAMIANE</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Sessão_6</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>02-Apr-2026</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>3918786000009966138</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>TOPELANE</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Sessão_8</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>01-Apr-2026</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>3918786000009966136</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>MESEREPANE</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Sessão_7</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>01-Apr-2026</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>3918786000009964076</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>MESEREPANE</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Sessão_6</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>08-Apr-2026</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>3918786000009964074</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>MESEREPANE</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Sessão_5</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>01-Apr-2026</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>3918786000009964072</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>MESEREPANE</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Sessão_4</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>01-Apr-2026</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>3918786000009964070</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>MESEREPANE</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Sessão_3</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>01-Apr-2026</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>3918786000009964068</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>MESEREPANE</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Sessão_2</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>01-Apr-2026</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>3918786000009964066</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>MESEREPANE</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Sessão_1</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>01-Apr-2026</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>3918786000009964064</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>MONAPO RIO</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Sessão_8</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>31-Mar-2026</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>3918786000009964062</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>TOPELANE</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Sessão_8</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>01-Apr-2026</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>3918786000009962078</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>MONAPO RIO</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Sessão_7</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>24-Mar-2026</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>3918786000009962026</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>MONAPO RIO</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Sessão_6</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>17-Mar-2026</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>3918786000009962024</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>MONAPO RIO</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Sessão_5</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>10-Mar-2026</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>3918786000009962022</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>MONAPO RIO</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Sessão_4</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>03-Mar-2026</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>3918786000009962020</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>MONAPO RIO</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Sessão_3</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>24-Feb-2026</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>3918786000009962018</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>MONAPO RIO</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Sessão_2</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>17-Feb-2026</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>3918786000009962016</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>MONAPO RIO</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Sessão_1</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>13-Feb-2026</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>3918786000009962014</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>RAMIANE</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Sessão_5</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>26-Mar-2026</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>3918786000009891291</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>TOPELANE</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Sessão_7</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>25-Mar-2026</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>3918786000009891287</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>TOPELANE</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Sessão_6</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>25-Mar-2026</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>3918786000009888175</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>MUELEGE</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Sessão_6</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>19-Mar-2026</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>3918786000009886133</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>MUELEGE</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Sessão_5</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>12-Mar-2026</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>3918786000009886129</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>TOPELANE</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Sessão_2</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>18-Feb-2026</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>3918786000009856153</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>TOPELANE</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Sessão_3</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>25-Feb-2026</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>3918786000009856149</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>TOPELANE</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Sessão_4</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>04-Mar-2026</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>3918786000009856145</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>RAMIANE</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Sessão_2</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>19-Feb-2026</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>3918786000009856141</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>RAMIANE</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Sessão_3</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>3918786000009856137</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>TOPELANE</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Sessão_5</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>11-Mar-2026</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>3918786000009856133</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>TOPELANE</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Sessão_6</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>17-Mar-2026</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>3918786000009856129</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
         <is>
           <t>RAMIANE</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>Sessão_4</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
         <is>
           <t>19-Mar-2026</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t>3918786000009856125</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Monapo</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1408,13 +3118,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{68751767-3BB7-432F-876E-8BC47C781FE2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{723B055D-CCB3-4475-AF18-0CAE188C0F17}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{61C623FD-AAF4-4CD2-A205-63301154B33F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0D9C1861-49A7-48E8-BE00-BF7E47814083}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5C516DBE-EE66-40DF-BFA8-6B93641F9A18}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7B7ABA38-48FC-462B-9FD8-0816A93709E0}"/>
 </file>
--- a/Qualidade_Sessoes.xlsx
+++ b/Qualidade_Sessoes.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K44"/>
+  <dimension ref="A1:K70"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -414,7 +414,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -424,17 +424,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>RAMIANE</t>
+          <t>MUELEGE</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Sessão_7</t>
+          <t>Sessão_3</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -444,17 +444,17 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>09-Apr-2026</t>
+          <t>26-Feb-2026</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3918786000010020060</t>
+          <t>3918786000010039074</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -471,7 +471,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -481,17 +481,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>MESEREPANE</t>
+          <t>MUELEGE</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Sessão_9</t>
+          <t>Sessão_4</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -501,17 +501,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>09-Apr-2026</t>
+          <t>05-Mar-2026</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3918786000010019064</t>
+          <t>3918786000010039072</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -528,7 +528,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -538,17 +538,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MONAPO RIO</t>
+          <t>MUELEGE</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Sessão_9</t>
+          <t>Sessão_2</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -558,17 +558,17 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>08-Apr-2026</t>
+          <t>19-Feb-2026</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3918786000010011002</t>
+          <t>3918786000010039070</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -585,7 +585,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -595,12 +595,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>MUELEGE</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Sessão_8</t>
+          <t>Sessão_1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -615,17 +615,17 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>08-Apr-2026</t>
+          <t>14-Feb-2026</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3918786000010007188</t>
+          <t>3918786000010039068</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -652,12 +652,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MUELEGE</t>
+          <t>TOPELANE</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Sessão_8</t>
+          <t>Sessão_3</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -672,17 +672,17 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>09-Apr-2026</t>
+          <t>25-Mar-2026</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3918786000010007186</t>
+          <t>3918786000010039066</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -699,7 +699,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Sessão_7</t>
+          <t>Sessão_2</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -729,17 +729,17 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>27-Mar-2026</t>
+          <t>18-Apr-2026</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3918786000009978061</t>
+          <t>3918786000010039064</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Sessão_7</t>
+          <t>Sessão_1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -786,17 +786,17 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>25-Mar-2026</t>
+          <t>13-Feb-2026</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3918786000009978059</t>
+          <t>3918786000010039062</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -813,7 +813,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -828,7 +828,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Sessão_6</t>
+          <t>Sessão_4</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -843,17 +843,17 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>25-Mar-2026</t>
+          <t>04-Mar-2026</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3918786000009978057</t>
+          <t>3918786000010039060</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -870,7 +870,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Sessão_5</t>
+          <t>Sessão_4</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -900,17 +900,17 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>11-Mar-2026</t>
+          <t>04-Mar-2026</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3918786000009978055</t>
+          <t>3918786000010039058</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -927,7 +927,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -942,7 +942,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Sessão_5</t>
+          <t>Sessão_3</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -957,17 +957,17 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>11-Mar-2026</t>
+          <t>25-Feb-2026</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3918786000009978053</t>
+          <t>3918786000010039056</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -984,7 +984,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MUELEGE</t>
+          <t>TOPELANE</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Sessão_7</t>
+          <t>Sessão_2</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1014,17 +1014,17 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>02-Apr-2026</t>
+          <t>18-Feb-2026</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3918786000009978051</t>
+          <t>3918786000010039054</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1041,7 +1041,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1051,17 +1051,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MESEREPANE</t>
+          <t>TOPELANE</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Sessão_8</t>
+          <t>Sessão_1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1071,17 +1071,17 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>02-Apr-2026</t>
+          <t>13-Feb-2026</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3918786000009975096</t>
+          <t>3918786000010039052</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1098,7 +1098,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1108,17 +1108,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>RAMIANE</t>
+          <t>MUELEGE</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Sessão_6</t>
+          <t>Sessão_9</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>02-Apr-2026</t>
+          <t>14-Apr-2026</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3918786000009966138</t>
+          <t>3918786000010039050</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1155,7 +1155,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>RAMIANE</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>01-Apr-2026</t>
+          <t>10-Apr-2026</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3918786000009966136</t>
+          <t>3918786000010023384</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1212,7 +1212,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MESEREPANE</t>
+          <t>RAMIANE</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Sessão_7</t>
+          <t>Sessão_1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1242,17 +1242,17 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>01-Apr-2026</t>
+          <t>11-Feb-2026</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>3918786000009964076</t>
+          <t>3918786000010023382</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1269,7 +1269,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1279,17 +1279,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MESEREPANE</t>
+          <t>TOPELANE</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Sessão_6</t>
+          <t>Sessão_9</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1304,12 +1304,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>3918786000009964074</t>
+          <t>3918786000010023380</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1326,7 +1326,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1336,17 +1336,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MESEREPANE</t>
+          <t>TOPELANE</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Sessão_5</t>
+          <t>Sessão_1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1356,17 +1356,17 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>01-Apr-2026</t>
+          <t>13-Feb-2026</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>3918786000009964072</t>
+          <t>3918786000010023378</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1383,7 +1383,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1393,17 +1393,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>MESEREPANE</t>
+          <t>RAMIANE</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Sessão_4</t>
+          <t>Sessão_7</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1413,17 +1413,17 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>01-Apr-2026</t>
+          <t>09-Apr-2026</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>3918786000009964070</t>
+          <t>3918786000010020060</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Sessão_3</t>
+          <t>Sessão_9</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1470,17 +1470,17 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>01-Apr-2026</t>
+          <t>09-Apr-2026</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>3918786000009964068</t>
+          <t>3918786000010019064</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1497,52 +1497,52 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>MESEREPANE</t>
+          <t>MATHAPUE</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Sessão_2</t>
+          <t>Sessão_8</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+          <t>FERNANDES LIMA &amp; TAIRAHA ESQUADRO</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>01-Apr-2026</t>
+          <t>31-Mar-2026</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>3918786000009964066</t>
+          <t>3918786000010015292</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1554,37 +1554,37 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>MESEREPANE</t>
+          <t>MATHAPUE</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Sessão_1</t>
+          <t>Sessão_7</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+          <t>FERNANDES LIMA &amp; TAIRAHA ESQUADRO</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>01-Apr-2026</t>
+          <t>31-Mar-2026</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1594,12 +1594,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>3918786000009964064</t>
+          <t>3918786000010015290</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1611,32 +1611,32 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>MONAPO RIO</t>
+          <t>MATHAPUE</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Sessão_8</t>
+          <t>Sessão_6</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+          <t>FERNANDES LIMA &amp; TAIRAHA ESQUADRO</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1646,17 +1646,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>3918786000009964062</t>
+          <t>3918786000010015288</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1668,52 +1668,52 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>MATHAPUE</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Sessão_8</t>
+          <t>Sessão_5</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+          <t>FERNANDES LIMA &amp; TAIRAHA ESQUADRO</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>01-Apr-2026</t>
+          <t>31-Mar-2026</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>3918786000009962078</t>
+          <t>3918786000010015286</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1725,52 +1725,52 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>MONAPO RIO</t>
+          <t>MATHAPUE</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Sessão_7</t>
+          <t>Sessão_4</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+          <t>FERNANDES LIMA &amp; TAIRAHA ESQUADRO</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>24-Mar-2026</t>
+          <t>31-Mar-2026</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>3918786000009962026</t>
+          <t>3918786000010015284</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1782,52 +1782,52 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>MONAPO RIO</t>
+          <t>MATHAPUE</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Sessão_6</t>
+          <t>Sessão_3</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+          <t>FERNANDES LIMA &amp; TAIRAHA ESQUADRO</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>17-Mar-2026</t>
+          <t>31-Mar-2026</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>3918786000009962024</t>
+          <t>3918786000010015282</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -1839,52 +1839,52 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>MONAPO RIO</t>
+          <t>MATHAPUE</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Sessão_5</t>
+          <t>Sessão_2</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+          <t>FERNANDES LIMA &amp; TAIRAHA ESQUADRO</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>10-Mar-2026</t>
+          <t>31-Mar-2026</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>3918786000009962022</t>
+          <t>3918786000010015280</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -1896,52 +1896,52 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>MONAPO RIO</t>
+          <t>MATHAPUE</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Sessão_4</t>
+          <t>Sessão_1</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+          <t>FERNANDES LIMA &amp; TAIRAHA ESQUADRO</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>03-Mar-2026</t>
+          <t>31-Mar-2026</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>3918786000009962020</t>
+          <t>3918786000010015278</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -1968,7 +1968,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Sessão_3</t>
+          <t>Sessão_9</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1983,17 +1983,17 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>24-Feb-2026</t>
+          <t>08-Apr-2026</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>3918786000009962018</t>
+          <t>3918786000010011002</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2010,7 +2010,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2020,17 +2020,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>MONAPO RIO</t>
+          <t>TOPELANE</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Sessão_2</t>
+          <t>Sessão_8</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2040,17 +2040,17 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>17-Feb-2026</t>
+          <t>08-Apr-2026</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>3918786000009962016</t>
+          <t>3918786000010007188</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2077,17 +2077,17 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>MONAPO RIO</t>
+          <t>MUELEGE</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Sessão_1</t>
+          <t>Sessão_8</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2097,17 +2097,17 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>13-Feb-2026</t>
+          <t>09-Apr-2026</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>3918786000009962014</t>
+          <t>3918786000010007186</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2124,7 +2124,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2134,17 +2134,17 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>RAMIANE</t>
+          <t>TOPELANE</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Sessão_5</t>
+          <t>Sessão_9</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2154,17 +2154,17 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>26-Mar-2026</t>
+          <t>10-Apr-2026</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>3918786000009891291</t>
+          <t>3918786000010005495</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2181,7 +2181,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>25-Mar-2026</t>
+          <t>27-Mar-2026</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2221,7 +2221,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>3918786000009891287</t>
+          <t>3918786000009978061</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2238,7 +2238,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Sessão_6</t>
+          <t>Sessão_7</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2273,12 +2273,12 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>3918786000009888175</t>
+          <t>3918786000009978059</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2305,7 +2305,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>MUELEGE</t>
+          <t>TOPELANE</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2325,17 +2325,17 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>19-Mar-2026</t>
+          <t>25-Mar-2026</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>3918786000009886133</t>
+          <t>3918786000009978057</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2352,7 +2352,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2362,7 +2362,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>MUELEGE</t>
+          <t>TOPELANE</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2382,17 +2382,17 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>12-Mar-2026</t>
+          <t>11-Mar-2026</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>3918786000009886129</t>
+          <t>3918786000009978055</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2409,7 +2409,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2424,12 +2424,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Sessão_2</t>
+          <t>Sessão_5</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2439,17 +2439,17 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>18-Feb-2026</t>
+          <t>11-Mar-2026</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>3918786000009856153</t>
+          <t>3918786000009978053</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2466,7 +2466,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2476,17 +2476,17 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>MUELEGE</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Sessão_3</t>
+          <t>Sessão_7</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2496,17 +2496,17 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>25-Feb-2026</t>
+          <t>02-Apr-2026</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>3918786000009856149</t>
+          <t>3918786000009978051</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2523,7 +2523,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2533,17 +2533,17 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>MESEREPANE</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Sessão_4</t>
+          <t>Sessão_8</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2553,17 +2553,17 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>04-Mar-2026</t>
+          <t>02-Apr-2026</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>3918786000009856145</t>
+          <t>3918786000009975096</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2580,7 +2580,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2595,7 +2595,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Sessão_2</t>
+          <t>Sessão_6</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2610,17 +2610,17 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>19-Feb-2026</t>
+          <t>02-Apr-2026</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>3918786000009856141</t>
+          <t>3918786000009966138</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2637,7 +2637,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2647,12 +2647,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>RAMIANE</t>
+          <t>TOPELANE</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Sessão_3</t>
+          <t>Sessão_8</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2665,14 +2665,19 @@
           <t>0</t>
         </is>
       </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>01-Apr-2026</t>
+        </is>
+      </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>3918786000009856137</t>
+          <t>3918786000009966136</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2689,7 +2694,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2699,17 +2704,17 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>MESEREPANE</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Sessão_5</t>
+          <t>Sessão_7</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2719,17 +2724,17 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>11-Mar-2026</t>
+          <t>01-Apr-2026</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>3918786000009856133</t>
+          <t>3918786000009964076</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -2746,7 +2751,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2756,7 +2761,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>MESEREPANE</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2766,7 +2771,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2776,17 +2781,17 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>17-Mar-2026</t>
+          <t>08-Apr-2026</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>3918786000009856129</t>
+          <t>3918786000009964074</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -2803,55 +2808,1537 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>MESEREPANE</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Sessão_5</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>01-Apr-2026</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>3918786000009964072</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>MESEREPANE</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Sessão_4</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>01-Apr-2026</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>3918786000009964070</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>MESEREPANE</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Sessão_3</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>01-Apr-2026</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>3918786000009964068</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>MESEREPANE</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Sessão_2</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>01-Apr-2026</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>3918786000009964066</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>MESEREPANE</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Sessão_1</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>01-Apr-2026</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>3918786000009964064</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>MONAPO RIO</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Sessão_8</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>31-Mar-2026</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>3918786000009964062</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>TOPELANE</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Sessão_8</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>01-Apr-2026</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>3918786000009962078</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>MONAPO RIO</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Sessão_7</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>24-Mar-2026</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>3918786000009962026</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>MONAPO RIO</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Sessão_6</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>17-Mar-2026</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>3918786000009962024</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>MONAPO RIO</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Sessão_5</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>10-Mar-2026</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>3918786000009962022</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>MONAPO RIO</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Sessão_4</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>03-Mar-2026</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>3918786000009962020</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>MONAPO RIO</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Sessão_3</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>24-Feb-2026</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>3918786000009962018</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>MONAPO RIO</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Sessão_2</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>17-Feb-2026</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>3918786000009962016</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>MONAPO RIO</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Sessão_1</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>13-Feb-2026</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>3918786000009962014</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>RAMIANE</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Sessão_5</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>26-Mar-2026</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>3918786000009891291</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>TOPELANE</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Sessão_7</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>25-Mar-2026</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>3918786000009891287</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>TOPELANE</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Sessão_6</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>25-Mar-2026</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>3918786000009888175</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>MUELEGE</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Sessão_6</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>19-Mar-2026</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>3918786000009886133</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>MUELEGE</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Sessão_5</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>12-Mar-2026</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>3918786000009886129</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>TOPELANE</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Sessão_2</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>18-Feb-2026</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>3918786000009856153</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>TOPELANE</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Sessão_3</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>25-Feb-2026</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>3918786000009856149</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>TOPELANE</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Sessão_4</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>04-Mar-2026</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>3918786000009856145</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>RAMIANE</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Sessão_2</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>19-Feb-2026</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>3918786000009856141</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>RAMIANE</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Sessão_3</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>26-Feb-2026</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>3918786000009856137</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>TOPELANE</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Sessão_5</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>11-Mar-2026</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>3918786000009856133</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>TOPELANE</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Sessão_6</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>17-Mar-2026</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>3918786000009856129</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
         <is>
           <t>RAMIANE</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D70" t="inlineStr">
         <is>
           <t>Sessão_4</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="E70" t="inlineStr">
         <is>
           <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
         <is>
           <t>19-Mar-2026</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="H70" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
+      <c r="I70" t="inlineStr">
         <is>
           <t>3918786000009856125</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>Monapo</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -3118,13 +4605,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{723B055D-CCB3-4475-AF18-0CAE188C0F17}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{95F58293-6994-4974-8E2D-DD663C674542}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0D9C1861-49A7-48E8-BE00-BF7E47814083}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B00EB8E-3B6B-4087-88E0-334D42B4ED95}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7B7ABA38-48FC-462B-9FD8-0816A93709E0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{69C8AC43-6896-4294-85CB-51E8DF774B78}"/>
 </file>
--- a/Qualidade_Sessoes.xlsx
+++ b/Qualidade_Sessoes.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K70"/>
+  <dimension ref="A1:K74"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -424,17 +424,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>MUELEGE</t>
+          <t>MESEREPANE</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Sessão_3</t>
+          <t>Sessão_10</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -444,17 +444,17 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>26-Feb-2026</t>
+          <t>16-Apr-2026</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3918786000010039074</t>
+          <t>3918786000010055064</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -471,7 +471,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -481,17 +481,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>MUELEGE</t>
+          <t>MONAPO RIO</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Sessão_4</t>
+          <t>Sessão_10</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -501,17 +501,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>05-Mar-2026</t>
+          <t>14-Apr-2026</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3918786000010039072</t>
+          <t>3918786000010050002</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -528,7 +528,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -543,7 +543,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Sessão_2</t>
+          <t>Sessão_3</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -558,17 +558,17 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>19-Feb-2026</t>
+          <t>26-Feb-2026</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3918786000010039070</t>
+          <t>3918786000010039074</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -585,7 +585,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Sessão_1</t>
+          <t>Sessão_4</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -615,17 +615,17 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>14-Feb-2026</t>
+          <t>05-Mar-2026</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3918786000010039068</t>
+          <t>3918786000010039072</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -642,7 +642,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -652,12 +652,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>MUELEGE</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Sessão_3</t>
+          <t>Sessão_2</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -672,17 +672,17 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>25-Mar-2026</t>
+          <t>19-Feb-2026</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3918786000010039066</t>
+          <t>3918786000010039070</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -699,47 +699,47 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>MUELEGE</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Sessão_1</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>14-Feb-2026</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>TOPELANE</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Sessão_2</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>18-Apr-2026</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3918786000010039064</t>
+          <t>3918786000010039068</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -756,7 +756,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Sessão_1</t>
+          <t>Sessão_3</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -786,17 +786,17 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>13-Feb-2026</t>
+          <t>25-Mar-2026</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3918786000010039062</t>
+          <t>3918786000010039066</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -813,7 +813,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -828,7 +828,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Sessão_4</t>
+          <t>Sessão_2</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -843,17 +843,17 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>04-Mar-2026</t>
+          <t>18-Apr-2026</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3918786000010039060</t>
+          <t>3918786000010039064</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -870,7 +870,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Sessão_4</t>
+          <t>Sessão_1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -900,17 +900,17 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>04-Mar-2026</t>
+          <t>13-Feb-2026</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3918786000010039058</t>
+          <t>3918786000010039062</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -927,7 +927,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -942,7 +942,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Sessão_3</t>
+          <t>Sessão_4</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -957,17 +957,17 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>25-Feb-2026</t>
+          <t>04-Mar-2026</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3918786000010039056</t>
+          <t>3918786000010039060</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Sessão_2</t>
+          <t>Sessão_4</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1014,17 +1014,17 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>18-Feb-2026</t>
+          <t>04-Mar-2026</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3918786000010039054</t>
+          <t>3918786000010039058</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1041,7 +1041,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Sessão_1</t>
+          <t>Sessão_3</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1071,17 +1071,17 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>13-Feb-2026</t>
+          <t>25-Feb-2026</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3918786000010039052</t>
+          <t>3918786000010039056</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MUELEGE</t>
+          <t>TOPELANE</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Sessão_9</t>
+          <t>Sessão_2</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1128,17 +1128,17 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>14-Apr-2026</t>
+          <t>18-Feb-2026</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3918786000010039050</t>
+          <t>3918786000010039054</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1155,7 +1155,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>RAMIANE</t>
+          <t>TOPELANE</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Sessão_8</t>
+          <t>Sessão_1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1185,17 +1185,17 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>10-Apr-2026</t>
+          <t>13-Feb-2026</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3918786000010023384</t>
+          <t>3918786000010039052</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1212,7 +1212,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>RAMIANE</t>
+          <t>MUELEGE</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Sessão_1</t>
+          <t>Sessão_9</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1242,17 +1242,17 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>11-Feb-2026</t>
+          <t>14-Apr-2026</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>3918786000010023382</t>
+          <t>3918786000010039050</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Sessão_9</t>
+          <t>Sessão_10</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1299,17 +1299,17 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>08-Apr-2026</t>
+          <t>15-Apr-2026</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>3918786000010023380</t>
+          <t>3918786000010037472</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1326,7 +1326,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>RAMIANE</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Sessão_1</t>
+          <t>Sessão_9</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1356,17 +1356,17 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>13-Feb-2026</t>
+          <t>14-Apr-2026</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>3918786000010023378</t>
+          <t>3918786000010037470</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1383,7 +1383,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Sessão_7</t>
+          <t>Sessão_8</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>09-Apr-2026</t>
+          <t>10-Apr-2026</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>3918786000010020060</t>
+          <t>3918786000010023384</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1440,7 +1440,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1450,17 +1450,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>MESEREPANE</t>
+          <t>RAMIANE</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Sessão_9</t>
+          <t>Sessão_1</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1470,17 +1470,17 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>09-Apr-2026</t>
+          <t>11-Feb-2026</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>3918786000010019064</t>
+          <t>3918786000010023382</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1497,52 +1497,52 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>MATHAPUE</t>
+          <t>TOPELANE</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Sessão_8</t>
+          <t>Sessão_9</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>FERNANDES LIMA &amp; TAIRAHA ESQUADRO</t>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>31-Mar-2026</t>
+          <t>08-Apr-2026</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>3918786000010015292</t>
+          <t>3918786000010023380</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Nacala Porto</t>
+          <t>Monapo</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1554,52 +1554,52 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>MATHAPUE</t>
+          <t>TOPELANE</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Sessão_7</t>
+          <t>Sessão_1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>FERNANDES LIMA &amp; TAIRAHA ESQUADRO</t>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>31-Mar-2026</t>
+          <t>13-Feb-2026</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>3918786000010015290</t>
+          <t>3918786000010023378</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Nacala Porto</t>
+          <t>Monapo</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1611,37 +1611,37 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>MATHAPUE</t>
+          <t>RAMIANE</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Sessão_6</t>
+          <t>Sessão_7</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>FERNANDES LIMA &amp; TAIRAHA ESQUADRO</t>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>31-Mar-2026</t>
+          <t>09-Apr-2026</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1651,12 +1651,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>3918786000010015288</t>
+          <t>3918786000010020060</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Nacala Porto</t>
+          <t>Monapo</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1668,52 +1668,52 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>MATHAPUE</t>
+          <t>MESEREPANE</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Sessão_5</t>
+          <t>Sessão_9</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>FERNANDES LIMA &amp; TAIRAHA ESQUADRO</t>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>31-Mar-2026</t>
+          <t>09-Apr-2026</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>3918786000010015286</t>
+          <t>3918786000010019064</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Nacala Porto</t>
+          <t>Monapo</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Sessão_4</t>
+          <t>Sessão_8</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1760,12 +1760,12 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>3918786000010015284</t>
+          <t>3918786000010015292</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1782,7 +1782,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Sessão_3</t>
+          <t>Sessão_7</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1807,7 +1807,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1817,12 +1817,12 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>3918786000010015282</t>
+          <t>3918786000010015290</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -1839,7 +1839,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Sessão_2</t>
+          <t>Sessão_6</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1864,7 +1864,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1874,12 +1874,12 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>3918786000010015280</t>
+          <t>3918786000010015288</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -1896,12 +1896,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Sessão_1</t>
+          <t>Sessão_5</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1931,12 +1931,12 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>3918786000010015278</t>
+          <t>3918786000010015286</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -1953,52 +1953,52 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>MONAPO RIO</t>
+          <t>MATHAPUE</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Sessão_9</t>
+          <t>Sessão_4</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+          <t>FERNANDES LIMA &amp; TAIRAHA ESQUADRO</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>08-Apr-2026</t>
+          <t>31-Mar-2026</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>3918786000010011002</t>
+          <t>3918786000010015284</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2010,52 +2010,52 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>MATHAPUE</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Sessão_8</t>
+          <t>Sessão_3</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+          <t>FERNANDES LIMA &amp; TAIRAHA ESQUADRO</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>08-Apr-2026</t>
+          <t>31-Mar-2026</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>3918786000010007188</t>
+          <t>3918786000010015282</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2067,37 +2067,37 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>MUELEGE</t>
+          <t>MATHAPUE</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Sessão_8</t>
+          <t>Sessão_2</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+          <t>FERNANDES LIMA &amp; TAIRAHA ESQUADRO</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>09-Apr-2026</t>
+          <t>31-Mar-2026</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2107,12 +2107,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>3918786000010007186</t>
+          <t>3918786000010015280</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2124,52 +2124,52 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>MATHAPUE</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Sessão_9</t>
+          <t>Sessão_1</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+          <t>FERNANDES LIMA &amp; TAIRAHA ESQUADRO</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>10-Apr-2026</t>
+          <t>31-Mar-2026</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>3918786000010005495</t>
+          <t>3918786000010015278</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2191,17 +2191,17 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>MONAPO RIO</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Sessão_7</t>
+          <t>Sessão_9</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2211,17 +2211,17 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>27-Mar-2026</t>
+          <t>08-Apr-2026</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>3918786000009978061</t>
+          <t>3918786000010011002</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2238,7 +2238,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Sessão_7</t>
+          <t>Sessão_8</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2268,17 +2268,17 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>25-Mar-2026</t>
+          <t>08-Apr-2026</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>3918786000009978059</t>
+          <t>3918786000010007188</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2295,7 +2295,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2305,12 +2305,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>MUELEGE</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Sessão_6</t>
+          <t>Sessão_8</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2325,17 +2325,17 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>25-Mar-2026</t>
+          <t>09-Apr-2026</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>3918786000009978057</t>
+          <t>3918786000010007186</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2367,7 +2367,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Sessão_5</t>
+          <t>Sessão_9</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2382,17 +2382,17 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>11-Mar-2026</t>
+          <t>10-Apr-2026</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>3918786000009978055</t>
+          <t>3918786000010005495</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2409,7 +2409,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Sessão_5</t>
+          <t>Sessão_7</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2439,17 +2439,17 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>11-Mar-2026</t>
+          <t>27-Mar-2026</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>3918786000009978053</t>
+          <t>3918786000009978061</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2466,7 +2466,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2476,7 +2476,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>MUELEGE</t>
+          <t>TOPELANE</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2496,17 +2496,17 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>02-Apr-2026</t>
+          <t>25-Mar-2026</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>3918786000009978051</t>
+          <t>3918786000009978059</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2523,7 +2523,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2533,17 +2533,17 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>MESEREPANE</t>
+          <t>TOPELANE</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Sessão_8</t>
+          <t>Sessão_6</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2553,17 +2553,17 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>02-Apr-2026</t>
+          <t>25-Mar-2026</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>3918786000009975096</t>
+          <t>3918786000009978057</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2580,7 +2580,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2590,17 +2590,17 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>RAMIANE</t>
+          <t>TOPELANE</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Sessão_6</t>
+          <t>Sessão_5</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2610,17 +2610,17 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>02-Apr-2026</t>
+          <t>11-Mar-2026</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>3918786000009966138</t>
+          <t>3918786000009978055</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2637,7 +2637,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2652,12 +2652,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Sessão_8</t>
+          <t>Sessão_5</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2667,17 +2667,17 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>01-Apr-2026</t>
+          <t>11-Mar-2026</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>3918786000009966136</t>
+          <t>3918786000009978053</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2694,7 +2694,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2704,7 +2704,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>MESEREPANE</t>
+          <t>MUELEGE</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>01-Apr-2026</t>
+          <t>02-Apr-2026</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>3918786000009964076</t>
+          <t>3918786000009978051</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -2751,7 +2751,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2766,7 +2766,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Sessão_6</t>
+          <t>Sessão_8</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2781,17 +2781,17 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>08-Apr-2026</t>
+          <t>02-Apr-2026</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>3918786000009964074</t>
+          <t>3918786000009975096</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -2808,7 +2808,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2818,17 +2818,17 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>MESEREPANE</t>
+          <t>RAMIANE</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Sessão_5</t>
+          <t>Sessão_6</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>01-Apr-2026</t>
+          <t>02-Apr-2026</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2848,7 +2848,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>3918786000009964072</t>
+          <t>3918786000009966138</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -2865,7 +2865,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2875,17 +2875,17 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>MESEREPANE</t>
+          <t>TOPELANE</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Sessão_4</t>
+          <t>Sessão_8</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2900,12 +2900,12 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>3918786000009964070</t>
+          <t>3918786000009966136</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -2922,7 +2922,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2937,7 +2937,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Sessão_3</t>
+          <t>Sessão_7</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2957,12 +2957,12 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>3918786000009964068</t>
+          <t>3918786000009964076</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -2979,7 +2979,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Sessão_2</t>
+          <t>Sessão_6</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3009,17 +3009,17 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>01-Apr-2026</t>
+          <t>08-Apr-2026</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>3918786000009964066</t>
+          <t>3918786000009964074</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3036,7 +3036,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Sessão_1</t>
+          <t>Sessão_5</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3071,12 +3071,12 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>3918786000009964064</t>
+          <t>3918786000009964072</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3093,7 +3093,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3103,12 +3103,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>MONAPO RIO</t>
+          <t>MESEREPANE</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Sessão_8</t>
+          <t>Sessão_4</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3123,17 +3123,17 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>31-Mar-2026</t>
+          <t>01-Apr-2026</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>3918786000009964062</t>
+          <t>3918786000009964070</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3150,7 +3150,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3160,17 +3160,17 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>MESEREPANE</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Sessão_8</t>
+          <t>Sessão_3</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>3918786000009962078</t>
+          <t>3918786000009964068</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3207,7 +3207,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3217,12 +3217,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>MONAPO RIO</t>
+          <t>MESEREPANE</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Sessão_7</t>
+          <t>Sessão_2</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3237,17 +3237,17 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>24-Mar-2026</t>
+          <t>01-Apr-2026</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>3918786000009962026</t>
+          <t>3918786000009964066</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3264,7 +3264,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>MONAPO RIO</t>
+          <t>MESEREPANE</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Sessão_6</t>
+          <t>Sessão_1</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3294,17 +3294,17 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>17-Mar-2026</t>
+          <t>01-Apr-2026</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>3918786000009962024</t>
+          <t>3918786000009964064</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Sessão_5</t>
+          <t>Sessão_8</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3351,17 +3351,17 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>10-Mar-2026</t>
+          <t>31-Mar-2026</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>3918786000009962022</t>
+          <t>3918786000009964062</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -3378,7 +3378,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3388,17 +3388,17 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>MONAPO RIO</t>
+          <t>TOPELANE</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Sessão_4</t>
+          <t>Sessão_8</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -3408,17 +3408,17 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>03-Mar-2026</t>
+          <t>01-Apr-2026</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>3918786000009962020</t>
+          <t>3918786000009962078</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Sessão_3</t>
+          <t>Sessão_7</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3465,7 +3465,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>24-Feb-2026</t>
+          <t>24-Mar-2026</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3475,7 +3475,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>3918786000009962018</t>
+          <t>3918786000009962026</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -3507,7 +3507,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Sessão_2</t>
+          <t>Sessão_6</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3522,17 +3522,17 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>17-Feb-2026</t>
+          <t>17-Mar-2026</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>3918786000009962016</t>
+          <t>3918786000009962024</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Sessão_1</t>
+          <t>Sessão_5</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3579,17 +3579,17 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>13-Feb-2026</t>
+          <t>10-Mar-2026</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>3918786000009962014</t>
+          <t>3918786000009962022</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -3606,7 +3606,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3616,17 +3616,17 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>RAMIANE</t>
+          <t>MONAPO RIO</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Sessão_5</t>
+          <t>Sessão_4</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -3636,17 +3636,17 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>26-Mar-2026</t>
+          <t>03-Mar-2026</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>3918786000009891291</t>
+          <t>3918786000009962020</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -3663,7 +3663,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3673,17 +3673,17 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>MONAPO RIO</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Sessão_7</t>
+          <t>Sessão_3</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -3693,17 +3693,17 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>25-Mar-2026</t>
+          <t>24-Feb-2026</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>3918786000009891287</t>
+          <t>3918786000009962018</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -3720,7 +3720,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3730,17 +3730,17 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>MONAPO RIO</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Sessão_6</t>
+          <t>Sessão_2</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -3750,17 +3750,17 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>25-Mar-2026</t>
+          <t>17-Feb-2026</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>3918786000009888175</t>
+          <t>3918786000009962016</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -3777,7 +3777,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3787,17 +3787,17 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>MUELEGE</t>
+          <t>MONAPO RIO</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Sessão_6</t>
+          <t>Sessão_1</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -3807,17 +3807,17 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>19-Mar-2026</t>
+          <t>13-Feb-2026</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>3918786000009886133</t>
+          <t>3918786000009962014</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -3834,7 +3834,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3844,7 +3844,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>MUELEGE</t>
+          <t>RAMIANE</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3854,7 +3854,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -3864,17 +3864,17 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>12-Mar-2026</t>
+          <t>26-Mar-2026</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>3918786000009886129</t>
+          <t>3918786000009891291</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -3891,7 +3891,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Sessão_2</t>
+          <t>Sessão_7</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -3921,17 +3921,17 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>18-Feb-2026</t>
+          <t>25-Mar-2026</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>3918786000009856153</t>
+          <t>3918786000009891287</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -3948,7 +3948,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3963,12 +3963,12 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Sessão_3</t>
+          <t>Sessão_6</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -3978,17 +3978,17 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>25-Feb-2026</t>
+          <t>25-Mar-2026</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>3918786000009856149</t>
+          <t>3918786000009888175</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -4005,7 +4005,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4015,17 +4015,17 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>MUELEGE</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Sessão_4</t>
+          <t>Sessão_6</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -4035,17 +4035,17 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>04-Mar-2026</t>
+          <t>19-Mar-2026</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>3918786000009856145</t>
+          <t>3918786000009886133</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -4072,17 +4072,17 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>RAMIANE</t>
+          <t>MUELEGE</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Sessão_2</t>
+          <t>Sessão_5</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -4092,17 +4092,17 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>19-Feb-2026</t>
+          <t>12-Mar-2026</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>3918786000009856141</t>
+          <t>3918786000009886129</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -4119,7 +4119,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4129,12 +4129,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>RAMIANE</t>
+          <t>TOPELANE</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Sessão_3</t>
+          <t>Sessão_2</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4149,17 +4149,17 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>26-Feb-2026</t>
+          <t>18-Feb-2026</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>3918786000009856137</t>
+          <t>3918786000009856153</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -4176,7 +4176,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Sessão_5</t>
+          <t>Sessão_3</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4206,17 +4206,17 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>11-Mar-2026</t>
+          <t>25-Feb-2026</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>3918786000009856133</t>
+          <t>3918786000009856149</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -4233,7 +4233,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4248,7 +4248,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Sessão_6</t>
+          <t>Sessão_4</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4263,17 +4263,17 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>17-Mar-2026</t>
+          <t>04-Mar-2026</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>3918786000009856129</t>
+          <t>3918786000009856145</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -4290,55 +4290,283 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>RAMIANE</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Sessão_2</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>19-Feb-2026</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>3918786000009856141</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>RAMIANE</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Sessão_3</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>26-Feb-2026</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>3918786000009856137</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>TOPELANE</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Sessão_5</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>11-Mar-2026</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>3918786000009856133</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>TOPELANE</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Sessão_6</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>17-Mar-2026</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>3918786000009856129</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
         <is>
           <t>RAMIANE</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
+      <c r="D74" t="inlineStr">
         <is>
           <t>Sessão_4</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="E74" t="inlineStr">
         <is>
           <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
         <is>
           <t>19-Mar-2026</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
+      <c r="H74" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
+      <c r="I74" t="inlineStr">
         <is>
           <t>3918786000009856125</t>
         </is>
       </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>Monapo</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -4605,13 +4833,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{95F58293-6994-4974-8E2D-DD663C674542}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{68735154-487A-4E1C-87E9-E4FEDA786EA4}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B00EB8E-3B6B-4087-88E0-334D42B4ED95}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12B360E7-B2FF-4F5F-9D7A-718BD43FB1E1}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{69C8AC43-6896-4294-85CB-51E8DF774B78}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F096A08E-736E-49C4-AF82-A89D0D24FF96}"/>
 </file>
--- a/Qualidade_Sessoes.xlsx
+++ b/Qualidade_Sessoes.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K74"/>
+  <dimension ref="A1:K98"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -414,7 +414,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -424,7 +424,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>MESEREPANE</t>
+          <t>MUELEGE</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -434,7 +434,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -444,17 +444,17 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>15-Apr-2026</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3918786000010055064</t>
+          <t>3918786000010070032</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -481,17 +481,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>MONAPO RIO</t>
+          <t>TOPELANE</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Sessão_10</t>
+          <t>Sessão_9</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -501,17 +501,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>14-Apr-2026</t>
+          <t>15-Apr-2026</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3918786000010050002</t>
+          <t>3918786000010070030</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -528,7 +528,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -538,12 +538,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MUELEGE</t>
+          <t>TOPELANE</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Sessão_3</t>
+          <t>Sessão_10</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -558,17 +558,17 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>26-Feb-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3918786000010039074</t>
+          <t>3918786000010069058</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -585,7 +585,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -595,17 +595,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MUELEGE</t>
+          <t>RAMIANE</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Sessão_4</t>
+          <t>Sessão_10</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -615,17 +615,17 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>05-Mar-2026</t>
+          <t>16-Apr-2026</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3918786000010039072</t>
+          <t>3918786000010066060</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -642,7 +642,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -652,17 +652,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MUELEGE</t>
+          <t>MOCONE</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Sessão_2</t>
+          <t>Sessão_9</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -672,22 +672,22 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>19-Feb-2026</t>
+          <t>08-Apr-2026</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3918786000010039070</t>
+          <t>3918786000010065072</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -699,7 +699,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -709,17 +709,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MUELEGE</t>
+          <t>MOCONE</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Sessão_1</t>
+          <t>Sessão_8</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -729,22 +729,22 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>14-Feb-2026</t>
+          <t>01-Apr-2026</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3918786000010039068</t>
+          <t>3918786000010065070</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -756,7 +756,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -766,22 +766,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>MOCONE</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Sessão_3</t>
+          <t>Sessão_7</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -791,17 +791,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3918786000010039066</t>
+          <t>3918786000010065068</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -813,52 +813,52 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>MOCONE</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Sessão_6</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>TOPELANE</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Sessão_2</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>18-Apr-2026</t>
+          <t>18-Mar-2026</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3918786000010039064</t>
+          <t>3918786000010065066</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -870,7 +870,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -880,17 +880,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>MOCONE</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Sessão_1</t>
+          <t>Sessão_5</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -900,22 +900,22 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>13-Feb-2026</t>
+          <t>11-Mar-2026</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3918786000010039062</t>
+          <t>3918786000010065064</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -927,7 +927,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>MOCONE</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -962,17 +962,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3918786000010039060</t>
+          <t>3918786000010065062</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -984,7 +984,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -994,42 +994,42 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>MOCONE</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Sessão_4</t>
+          <t>Sessão_3</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>04-Mar-2026</t>
+          <t>25-Feb-2026</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3918786000010039058</t>
+          <t>3918786000010065060</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1041,7 +1041,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1051,17 +1051,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>MOCONE</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Sessão_3</t>
+          <t>Sessão_2</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1071,22 +1071,22 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>25-Feb-2026</t>
+          <t>18-Feb-2026</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3918786000010039056</t>
+          <t>3918786000010065058</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1098,7 +1098,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1108,17 +1108,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>MOCONE</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Sessão_2</t>
+          <t>Sessão_1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1128,27 +1128,27 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>18-Feb-2026</t>
+          <t>11-Feb-2026</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3918786000010039054</t>
+          <t>3918786000010065056</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -1165,17 +1165,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>MOCONE</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Sessão_1</t>
+          <t>Sessão_10</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1185,22 +1185,22 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>13-Feb-2026</t>
+          <t>15-Apr-2026</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3918786000010039052</t>
+          <t>3918786000010065054</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1212,7 +1212,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MUELEGE</t>
+          <t>MURRUPELANE</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Sessão_9</t>
+          <t>Sessão_10</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>3918786000010039050</t>
+          <t>3918786000010055144</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1269,27 +1269,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>MURRUPELANE</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Sessão_10</t>
+          <t>Sessão_9</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1299,34 +1299,34 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>15-Apr-2026</t>
+          <t>09-Apr-2026</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>3918786000010037472</t>
+          <t>3918786000010055142</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1336,17 +1336,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>RAMIANE</t>
+          <t>MORRUPELANE</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Sessão_9</t>
+          <t>Sessão_8</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1356,22 +1356,22 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>14-Apr-2026</t>
+          <t>31-Mar-2026</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>3918786000010037470</t>
+          <t>3918786000010055140</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1383,7 +1383,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1393,17 +1393,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>RAMIANE</t>
+          <t>MURRUPELANE</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Sessão_8</t>
+          <t>Sessão_7</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1413,22 +1413,22 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>10-Apr-2026</t>
+          <t>24-Mar-2026</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>3918786000010023384</t>
+          <t>3918786000010055138</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1440,7 +1440,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1450,27 +1450,27 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>RAMIANE</t>
+          <t>MURRUPELANE</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Sessão_1</t>
+          <t>Sessão_6</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>11-Feb-2026</t>
+          <t>17-Mar-2026</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1480,12 +1480,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>3918786000010023382</t>
+          <t>3918786000010055136</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1497,7 +1497,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1507,17 +1507,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>MURRUPELANE</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Sessão_9</t>
+          <t>Sessão_5</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1527,22 +1527,22 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>08-Apr-2026</t>
+          <t>10-Mar-2026</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>3918786000010023380</t>
+          <t>3918786000010055134</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1564,42 +1564,42 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>MURRUPELANE</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Sessão_1</t>
+          <t>Sessão_4</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>13-Feb-2026</t>
+          <t>03-Mar-2026</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>3918786000010023378</t>
+          <t>3918786000010055132</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1611,7 +1611,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1621,17 +1621,17 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>RAMIANE</t>
+          <t>MORRUPELANE</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Sessão_7</t>
+          <t>Sessão_3</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1641,22 +1641,22 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>09-Apr-2026</t>
+          <t>24-Feb-2026</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>3918786000010020060</t>
+          <t>3918786000010055130</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1668,27 +1668,27 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>MESEREPANE</t>
+          <t>MURRUPELANE</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Sessão_9</t>
+          <t>Sessão_2</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1698,22 +1698,22 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>09-Apr-2026</t>
+          <t>17-Feb-2026</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>3918786000010019064</t>
+          <t>3918786000010055128</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1725,47 +1725,47 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>MATHAPUE</t>
+          <t>MURRUPELANE</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Sessão_8</t>
+          <t>Sessão_1</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>FERNANDES LIMA &amp; TAIRAHA ESQUADRO</t>
+          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>31-Mar-2026</t>
+          <t>10-Feb-2026</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>3918786000010015292</t>
+          <t>3918786000010055126</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1782,52 +1782,52 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>MATHAPUE</t>
+          <t>MESEREPANE</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Sessão_7</t>
+          <t>Sessão_10</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>FERNANDES LIMA &amp; TAIRAHA ESQUADRO</t>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>31-Mar-2026</t>
+          <t>16-Apr-2026</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>3918786000010015290</t>
+          <t>3918786000010055064</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Nacala Porto</t>
+          <t>Monapo</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -1839,52 +1839,52 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>MATHAPUE</t>
+          <t>MONAPO RIO</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Sessão_6</t>
+          <t>Sessão_10</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>FERNANDES LIMA &amp; TAIRAHA ESQUADRO</t>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>31-Mar-2026</t>
+          <t>14-Apr-2026</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>3918786000010015288</t>
+          <t>3918786000010050002</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Nacala Porto</t>
+          <t>Monapo</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -1896,52 +1896,52 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>MATHAPUE</t>
+          <t>MUELEGE</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Sessão_5</t>
+          <t>Sessão_3</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>FERNANDES LIMA &amp; TAIRAHA ESQUADRO</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>31-Mar-2026</t>
+          <t>26-Feb-2026</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>3918786000010015286</t>
+          <t>3918786000010039074</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Nacala Porto</t>
+          <t>Monapo</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -1953,17 +1953,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>MATHAPUE</t>
+          <t>MUELEGE</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1973,17 +1973,17 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>FERNANDES LIMA &amp; TAIRAHA ESQUADRO</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>31-Mar-2026</t>
+          <t>05-Mar-2026</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1993,12 +1993,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>3918786000010015284</t>
+          <t>3918786000010039072</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Nacala Porto</t>
+          <t>Monapo</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2010,52 +2010,52 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>MATHAPUE</t>
+          <t>MUELEGE</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Sessão_3</t>
+          <t>Sessão_2</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>FERNANDES LIMA &amp; TAIRAHA ESQUADRO</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>31-Mar-2026</t>
+          <t>19-Feb-2026</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>3918786000010015282</t>
+          <t>3918786000010039070</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Nacala Porto</t>
+          <t>Monapo</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2067,52 +2067,52 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>MUELEGE</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Sessão_1</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>14-Feb-2026</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>MATHAPUE</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Sessão_2</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>FERNANDES LIMA &amp; TAIRAHA ESQUADRO</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>31-Mar-2026</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>3918786000010015280</t>
+          <t>3918786000010039068</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Nacala Porto</t>
+          <t>Monapo</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2124,52 +2124,52 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>MATHAPUE</t>
+          <t>TOPELANE</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Sessão_1</t>
+          <t>Sessão_3</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>FERNANDES LIMA &amp; TAIRAHA ESQUADRO</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>31-Mar-2026</t>
+          <t>25-Mar-2026</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>3918786000010015278</t>
+          <t>3918786000010039066</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Nacala Porto</t>
+          <t>Monapo</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2181,7 +2181,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2191,17 +2191,17 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>MONAPO RIO</t>
+          <t>TOPELANE</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Sessão_9</t>
+          <t>Sessão_2</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2211,17 +2211,17 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>08-Apr-2026</t>
+          <t>18-Apr-2026</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>3918786000010011002</t>
+          <t>3918786000010039064</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2238,7 +2238,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Sessão_8</t>
+          <t>Sessão_1</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2268,17 +2268,17 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>08-Apr-2026</t>
+          <t>13-Feb-2026</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>3918786000010007188</t>
+          <t>3918786000010039062</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2295,7 +2295,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2305,12 +2305,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>MUELEGE</t>
+          <t>TOPELANE</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Sessão_8</t>
+          <t>Sessão_4</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2325,17 +2325,17 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>09-Apr-2026</t>
+          <t>04-Mar-2026</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>3918786000010007186</t>
+          <t>3918786000010039060</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2352,7 +2352,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2367,7 +2367,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Sessão_9</t>
+          <t>Sessão_4</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2382,17 +2382,17 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>10-Apr-2026</t>
+          <t>04-Mar-2026</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>3918786000010005495</t>
+          <t>3918786000010039058</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Sessão_7</t>
+          <t>Sessão_3</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2439,17 +2439,17 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>27-Mar-2026</t>
+          <t>25-Feb-2026</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>3918786000009978061</t>
+          <t>3918786000010039056</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2466,7 +2466,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Sessão_7</t>
+          <t>Sessão_2</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2496,17 +2496,17 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>25-Mar-2026</t>
+          <t>18-Feb-2026</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>3918786000009978059</t>
+          <t>3918786000010039054</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2523,7 +2523,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Sessão_6</t>
+          <t>Sessão_1</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2553,17 +2553,17 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>25-Mar-2026</t>
+          <t>13-Feb-2026</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>3918786000009978057</t>
+          <t>3918786000010039052</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2580,7 +2580,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2590,12 +2590,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>MUELEGE</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Sessão_5</t>
+          <t>Sessão_9</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2610,17 +2610,17 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>11-Mar-2026</t>
+          <t>14-Apr-2026</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>3918786000009978055</t>
+          <t>3918786000010039050</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2637,7 +2637,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2652,12 +2652,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Sessão_5</t>
+          <t>Sessão_10</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2667,17 +2667,17 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>11-Mar-2026</t>
+          <t>15-Apr-2026</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>3918786000009978053</t>
+          <t>3918786000010037472</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2694,7 +2694,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2704,17 +2704,17 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>MUELEGE</t>
+          <t>RAMIANE</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Sessão_7</t>
+          <t>Sessão_9</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>02-Apr-2026</t>
+          <t>14-Apr-2026</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>3918786000009978051</t>
+          <t>3918786000010037470</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -2751,7 +2751,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>MESEREPANE</t>
+          <t>RAMIANE</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2781,17 +2781,17 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>02-Apr-2026</t>
+          <t>10-Apr-2026</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>3918786000009975096</t>
+          <t>3918786000010023384</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -2808,7 +2808,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2823,7 +2823,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Sessão_6</t>
+          <t>Sessão_1</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2838,17 +2838,17 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>02-Apr-2026</t>
+          <t>11-Feb-2026</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>3918786000009966138</t>
+          <t>3918786000010023382</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -2865,7 +2865,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2880,7 +2880,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Sessão_8</t>
+          <t>Sessão_9</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>01-Apr-2026</t>
+          <t>08-Apr-2026</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2905,7 +2905,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>3918786000009966136</t>
+          <t>3918786000010023380</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -2922,7 +2922,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2932,17 +2932,17 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>MESEREPANE</t>
+          <t>TOPELANE</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Sessão_7</t>
+          <t>Sessão_1</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2952,17 +2952,17 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>01-Apr-2026</t>
+          <t>13-Feb-2026</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>3918786000009964076</t>
+          <t>3918786000010023378</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -2979,7 +2979,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2989,17 +2989,17 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>MESEREPANE</t>
+          <t>RAMIANE</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Sessão_6</t>
+          <t>Sessão_7</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -3009,17 +3009,17 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>08-Apr-2026</t>
+          <t>09-Apr-2026</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>3918786000009964074</t>
+          <t>3918786000010020060</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3036,7 +3036,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Sessão_5</t>
+          <t>Sessão_9</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3066,17 +3066,17 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>01-Apr-2026</t>
+          <t>09-Apr-2026</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>3918786000009964072</t>
+          <t>3918786000010019064</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3098,47 +3098,47 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>MESEREPANE</t>
+          <t>MATHAPUE</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Sessão_4</t>
+          <t>Sessão_8</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+          <t>FERNANDES LIMA &amp; TAIRAHA ESQUADRO</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>01-Apr-2026</t>
+          <t>31-Mar-2026</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>3918786000009964070</t>
+          <t>3918786000010015292</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3150,52 +3150,52 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>MESEREPANE</t>
+          <t>MATHAPUE</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Sessão_3</t>
+          <t>Sessão_7</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+          <t>FERNANDES LIMA &amp; TAIRAHA ESQUADRO</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>01-Apr-2026</t>
+          <t>31-Mar-2026</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>3918786000009964068</t>
+          <t>3918786000010015290</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3207,52 +3207,52 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>MESEREPANE</t>
+          <t>MATHAPUE</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Sessão_2</t>
+          <t>Sessão_6</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+          <t>FERNANDES LIMA &amp; TAIRAHA ESQUADRO</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>01-Apr-2026</t>
+          <t>31-Mar-2026</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>3918786000009964066</t>
+          <t>3918786000010015288</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3264,52 +3264,52 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>MESEREPANE</t>
+          <t>MATHAPUE</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Sessão_1</t>
+          <t>Sessão_5</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+          <t>FERNANDES LIMA &amp; TAIRAHA ESQUADRO</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>01-Apr-2026</t>
+          <t>31-Mar-2026</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>3918786000009964064</t>
+          <t>3918786000010015286</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3321,32 +3321,32 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>MONAPO RIO</t>
+          <t>MATHAPUE</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Sessão_8</t>
+          <t>Sessão_4</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+          <t>FERNANDES LIMA &amp; TAIRAHA ESQUADRO</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3356,17 +3356,17 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>3918786000009964062</t>
+          <t>3918786000010015284</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -3378,52 +3378,52 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>MATHAPUE</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Sessão_8</t>
+          <t>Sessão_3</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+          <t>FERNANDES LIMA &amp; TAIRAHA ESQUADRO</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>01-Apr-2026</t>
+          <t>31-Mar-2026</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>3918786000009962078</t>
+          <t>3918786000010015282</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -3435,52 +3435,52 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>MONAPO RIO</t>
+          <t>MATHAPUE</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Sessão_7</t>
+          <t>Sessão_2</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+          <t>FERNANDES LIMA &amp; TAIRAHA ESQUADRO</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>24-Mar-2026</t>
+          <t>31-Mar-2026</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>3918786000009962026</t>
+          <t>3918786000010015280</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -3492,52 +3492,52 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>MONAPO RIO</t>
+          <t>MATHAPUE</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Sessão_6</t>
+          <t>Sessão_1</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+          <t>FERNANDES LIMA &amp; TAIRAHA ESQUADRO</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>17-Mar-2026</t>
+          <t>31-Mar-2026</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>3918786000009962024</t>
+          <t>3918786000010015278</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Sessão_5</t>
+          <t>Sessão_9</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3579,17 +3579,17 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>10-Mar-2026</t>
+          <t>08-Apr-2026</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>3918786000009962022</t>
+          <t>3918786000010011002</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -3606,7 +3606,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3616,17 +3616,17 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>MONAPO RIO</t>
+          <t>TOPELANE</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Sessão_4</t>
+          <t>Sessão_8</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -3636,17 +3636,17 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>03-Mar-2026</t>
+          <t>08-Apr-2026</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>3918786000009962020</t>
+          <t>3918786000010007188</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -3673,17 +3673,17 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>MONAPO RIO</t>
+          <t>MUELEGE</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Sessão_3</t>
+          <t>Sessão_8</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -3693,17 +3693,17 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>24-Feb-2026</t>
+          <t>09-Apr-2026</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>3918786000009962018</t>
+          <t>3918786000010007186</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -3720,7 +3720,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3730,17 +3730,17 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>MONAPO RIO</t>
+          <t>TOPELANE</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Sessão_2</t>
+          <t>Sessão_9</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -3750,17 +3750,17 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>17-Feb-2026</t>
+          <t>10-Apr-2026</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>3918786000009962016</t>
+          <t>3918786000010005495</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -3787,17 +3787,17 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>MONAPO RIO</t>
+          <t>TOPELANE</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Sessão_1</t>
+          <t>Sessão_7</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -3807,17 +3807,17 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>13-Feb-2026</t>
+          <t>27-Mar-2026</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>3918786000009962014</t>
+          <t>3918786000009978061</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -3834,7 +3834,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3844,17 +3844,17 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>RAMIANE</t>
+          <t>TOPELANE</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Sessão_5</t>
+          <t>Sessão_7</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -3864,17 +3864,17 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>26-Mar-2026</t>
+          <t>25-Mar-2026</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>3918786000009891291</t>
+          <t>3918786000009978059</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Sessão_7</t>
+          <t>Sessão_6</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>3918786000009891287</t>
+          <t>3918786000009978057</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -3963,7 +3963,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Sessão_6</t>
+          <t>Sessão_5</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -3978,17 +3978,17 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>25-Mar-2026</t>
+          <t>11-Mar-2026</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>3918786000009888175</t>
+          <t>3918786000009978055</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -4005,7 +4005,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4015,12 +4015,12 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>MUELEGE</t>
+          <t>TOPELANE</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Sessão_6</t>
+          <t>Sessão_5</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4035,17 +4035,17 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>19-Mar-2026</t>
+          <t>11-Mar-2026</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>3918786000009886133</t>
+          <t>3918786000009978053</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -4062,7 +4062,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4077,7 +4077,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Sessão_5</t>
+          <t>Sessão_7</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4092,17 +4092,17 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>12-Mar-2026</t>
+          <t>02-Apr-2026</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>3918786000009886129</t>
+          <t>3918786000009978051</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -4119,7 +4119,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4129,17 +4129,17 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>MESEREPANE</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Sessão_2</t>
+          <t>Sessão_8</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -4149,17 +4149,17 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>18-Feb-2026</t>
+          <t>02-Apr-2026</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>3918786000009856153</t>
+          <t>3918786000009975096</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -4176,7 +4176,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4186,12 +4186,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>RAMIANE</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Sessão_3</t>
+          <t>Sessão_6</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4206,17 +4206,17 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>25-Feb-2026</t>
+          <t>02-Apr-2026</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>3918786000009856149</t>
+          <t>3918786000009966138</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -4233,7 +4233,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4248,7 +4248,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Sessão_4</t>
+          <t>Sessão_8</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4263,17 +4263,17 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>04-Mar-2026</t>
+          <t>01-Apr-2026</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>3918786000009856145</t>
+          <t>3918786000009966136</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -4290,7 +4290,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4300,17 +4300,17 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>RAMIANE</t>
+          <t>MESEREPANE</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Sessão_2</t>
+          <t>Sessão_7</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -4320,17 +4320,17 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>19-Feb-2026</t>
+          <t>01-Apr-2026</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>3918786000009856141</t>
+          <t>3918786000009964076</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -4347,7 +4347,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4357,17 +4357,17 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>RAMIANE</t>
+          <t>MESEREPANE</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Sessão_3</t>
+          <t>Sessão_6</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -4377,17 +4377,17 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>26-Feb-2026</t>
+          <t>08-Apr-2026</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>3918786000009856137</t>
+          <t>3918786000009964074</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -4404,7 +4404,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4414,7 +4414,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>MESEREPANE</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -4434,17 +4434,17 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>11-Mar-2026</t>
+          <t>01-Apr-2026</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>3918786000009856133</t>
+          <t>3918786000009964072</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -4461,7 +4461,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4471,17 +4471,17 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>MESEREPANE</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Sessão_6</t>
+          <t>Sessão_4</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -4491,17 +4491,17 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>17-Mar-2026</t>
+          <t>01-Apr-2026</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>3918786000009856129</t>
+          <t>3918786000009964070</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -4518,55 +4518,1423 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>MESEREPANE</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Sessão_3</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>01-Apr-2026</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>3918786000009964068</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>MESEREPANE</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Sessão_2</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>01-Apr-2026</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>3918786000009964066</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>MESEREPANE</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Sessão_1</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>01-Apr-2026</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>3918786000009964064</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>MONAPO RIO</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Sessão_8</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>31-Mar-2026</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>3918786000009964062</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>TOPELANE</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Sessão_8</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>01-Apr-2026</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>3918786000009962078</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>MONAPO RIO</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Sessão_7</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>24-Mar-2026</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>3918786000009962026</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>MONAPO RIO</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Sessão_6</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>17-Mar-2026</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>3918786000009962024</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>MONAPO RIO</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Sessão_5</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>10-Mar-2026</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>3918786000009962022</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>MONAPO RIO</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Sessão_4</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>03-Mar-2026</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>3918786000009962020</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>MONAPO RIO</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Sessão_3</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>24-Feb-2026</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>3918786000009962018</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>MONAPO RIO</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Sessão_2</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>17-Feb-2026</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>3918786000009962016</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>MONAPO RIO</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Sessão_1</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>13-Feb-2026</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>3918786000009962014</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>RAMIANE</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Sessão_5</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>26-Mar-2026</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>3918786000009891291</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>TOPELANE</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Sessão_7</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>25-Mar-2026</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>3918786000009891287</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>TOPELANE</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Sessão_6</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>25-Mar-2026</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>3918786000009888175</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>MUELEGE</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Sessão_6</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>19-Mar-2026</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>3918786000009886133</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>MUELEGE</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Sessão_5</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>12-Mar-2026</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>3918786000009886129</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>TOPELANE</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Sessão_2</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>18-Feb-2026</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>3918786000009856153</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>TOPELANE</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Sessão_3</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>25-Feb-2026</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>3918786000009856149</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>TOPELANE</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Sessão_4</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>04-Mar-2026</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>3918786000009856145</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>RAMIANE</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Sessão_2</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>19-Feb-2026</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>3918786000009856141</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>RAMIANE</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Sessão_3</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>26-Feb-2026</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>3918786000009856137</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>TOPELANE</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Sessão_5</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>11-Mar-2026</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>3918786000009856133</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>TOPELANE</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Sessão_6</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>17-Mar-2026</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>3918786000009856129</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
         <is>
           <t>RAMIANE</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
+      <c r="D98" t="inlineStr">
         <is>
           <t>Sessão_4</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
+      <c r="E98" t="inlineStr">
         <is>
           <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
         <is>
           <t>19-Mar-2026</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
+      <c r="H98" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
+      <c r="I98" t="inlineStr">
         <is>
           <t>3918786000009856125</t>
         </is>
       </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>Monapo</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -4833,13 +6201,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{68735154-487A-4E1C-87E9-E4FEDA786EA4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{50646A16-A334-4C48-8E7B-FDC4CDC64B89}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12B360E7-B2FF-4F5F-9D7A-718BD43FB1E1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA05B69D-E208-41C9-990C-41CDBB364A64}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F096A08E-736E-49C4-AF82-A89D0D24FF96}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B36614B6-DCE4-4131-9FD5-BC3968F5FD09}"/>
 </file>
--- a/Qualidade_Sessoes.xlsx
+++ b/Qualidade_Sessoes.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K98"/>
+  <dimension ref="A1:K117"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -414,7 +414,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -424,17 +424,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>MUELEGE</t>
+          <t>MATHAPUE</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Sessão_10</t>
+          <t>Sessão_11</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+          <t>FERNANDES LIMA &amp; TAIRAHA ESQUADRO</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -444,22 +444,22 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>15-Apr-2026</t>
+          <t>21-Apr-2026</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3918786000010070032</t>
+          <t>3918786000010098124</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -471,7 +471,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -481,17 +481,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>MATHAPUE</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Sessão_9</t>
+          <t>Sessão_10</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+          <t>FERNANDES LIMA &amp; TAIRAHA ESQUADRO</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -501,22 +501,22 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>15-Apr-2026</t>
+          <t>21-Apr-2026</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3918786000010070030</t>
+          <t>3918786000010098122</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -528,7 +528,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -538,17 +538,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>MATHAPUE</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Sessão_10</t>
+          <t>Sessão_9</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+          <t>FERNANDES LIMA &amp; TAIRAHA ESQUADRO</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -558,22 +558,22 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>21-Apr-2026</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>32</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3918786000010069058</t>
+          <t>3918786000010098120</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -585,7 +585,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -595,17 +595,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>RAMIANE</t>
+          <t>MOCONE</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Sessão_10</t>
+          <t>Sessão_11</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -615,22 +615,22 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3918786000010066060</t>
+          <t>3918786000010095002</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -642,7 +642,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -652,17 +652,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MOCONE</t>
+          <t>ONTUPAIA</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Sessão_9</t>
+          <t>Sessão_11</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
+          <t>NUCHATE ESTEVAO &amp; BELITO LUCIANO</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -672,17 +672,17 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>08-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3918786000010065072</t>
+          <t>3918786000010092104</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -699,7 +699,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -709,17 +709,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MOCONE</t>
+          <t>ONTUPAIA</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Sessão_8</t>
+          <t>Sessão_10</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
+          <t>NUCHATE ESTEVAO &amp; BELITO LUCIANO</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -729,17 +729,17 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>01-Apr-2026</t>
+          <t>15-Apr-2026</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3918786000010065070</t>
+          <t>3918786000010092102</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -756,7 +756,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -766,37 +766,37 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MOCONE</t>
+          <t>ONTUPAIA</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Sessão_7</t>
+          <t>Sessão_9</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
+          <t>NUCHATE ESTEVAO &amp; BELITO LUCIANO</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>25-Mar-2026</t>
+          <t>08-Apr-2026</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3918786000010065068</t>
+          <t>3918786000010092100</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -813,7 +813,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -823,37 +823,37 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MOCONE</t>
+          <t>ONTUPAIA</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Sessão_6</t>
+          <t>Sessão_8</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
+          <t>NUCHATE ESTEVAO &amp; BELITO LUCIANO</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>18-Mar-2026</t>
+          <t>01-Apr-2026</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3918786000010065066</t>
+          <t>3918786000010092098</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -870,7 +870,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -880,17 +880,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MOCONE</t>
+          <t>ONTUPAIA</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Sessão_5</t>
+          <t>Sessão_7</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
+          <t>NUCHATE ESTEVAO &amp; BELITO LUCIANO</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -900,17 +900,17 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>11-Mar-2026</t>
+          <t>25-Mar-2026</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3918786000010065064</t>
+          <t>3918786000010092096</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -927,7 +927,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -937,17 +937,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MOCONE</t>
+          <t>ONTUPAIA</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Sessão_4</t>
+          <t>Sessão_6</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
+          <t>NUCHATE ESTEVAO &amp; BELITO LUCIANO</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -957,17 +957,17 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>04-Mar-2026</t>
+          <t>18-Mar-2026</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3918786000010065062</t>
+          <t>3918786000010092094</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -984,7 +984,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -994,37 +994,37 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MOCONE</t>
+          <t>ONTUPAIA</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Sessão_3</t>
+          <t>Sessão_5</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
+          <t>NUCHATE ESTEVAO &amp; BELITO LUCIANO</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>25-Feb-2026</t>
+          <t>11-Mar-2026</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3918786000010065060</t>
+          <t>3918786000010092092</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1041,7 +1041,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1051,17 +1051,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MOCONE</t>
+          <t>ONTUPAIA</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Sessão_2</t>
+          <t>Sessão_4</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
+          <t>NUCHATE ESTEVAO &amp; BELITO LUCIANO</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1071,17 +1071,17 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>18-Feb-2026</t>
+          <t>04-Mar-2026</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3918786000010065058</t>
+          <t>3918786000010092090</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1098,7 +1098,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1108,17 +1108,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MOCONE</t>
+          <t>ONTUPAIA</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Sessão_1</t>
+          <t>Sessão_3</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
+          <t>NUCHATE ESTEVAO &amp; BELITO LUCIANO</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1128,17 +1128,17 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>11-Feb-2026</t>
+          <t>25-Mar-2026</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3918786000010065056</t>
+          <t>3918786000010092088</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1148,14 +1148,14 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MOCONE</t>
+          <t>ONTUPAIA</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Sessão_10</t>
+          <t>Sessão_2</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
+          <t>NUCHATE ESTEVAO &amp; BELITO LUCIANO</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1185,17 +1185,17 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>15-Apr-2026</t>
+          <t>18-Feb-2026</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3918786000010065054</t>
+          <t>3918786000010092086</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1212,7 +1212,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MURRUPELANE</t>
+          <t>ONTUPAIA</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Sessão_10</t>
+          <t>Sessão_1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
+          <t>NUCHATE ESTEVAO &amp; BELITO LUCIANO</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1242,17 +1242,17 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>14-Apr-2026</t>
+          <t>11-Feb-2026</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>3918786000010055144</t>
+          <t>3918786000010092084</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1269,27 +1269,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MURRUPELANE</t>
+          <t>TOPELANE</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Sessão_9</t>
+          <t>Sessão_11</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1299,27 +1299,27 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>09-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>3918786000010055142</t>
+          <t>3918786000010088069</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Nacala Porto</t>
+          <t>Monapo</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -1336,17 +1336,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MORRUPELANE</t>
+          <t>TOPELANE</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Sessão_8</t>
+          <t>Sessão_11</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1356,22 +1356,22 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>31-Mar-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>3918786000010055140</t>
+          <t>3918786000010088067</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Nacala Porto</t>
+          <t>Monapo</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1383,7 +1383,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1393,17 +1393,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>MURRUPELANE</t>
+          <t>TOPELANE</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Sessão_7</t>
+          <t>Sessão_11</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1413,22 +1413,22 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>24-Mar-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>3918786000010055138</t>
+          <t>3918786000010087128</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Nacala Porto</t>
+          <t>Monapo</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1440,7 +1440,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1450,42 +1450,42 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>MURRUPELANE</t>
+          <t>MESEREPANE</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Sessão_6</t>
+          <t>Sessão_11</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>17-Mar-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>3918786000010055136</t>
+          <t>3918786000010087064</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Nacala Porto</t>
+          <t>Monapo</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1497,7 +1497,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1507,17 +1507,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>MURRUPELANE</t>
+          <t>MUELEGE</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Sessão_5</t>
+          <t>Sessão_10</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1527,22 +1527,22 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>10-Mar-2026</t>
+          <t>15-Apr-2026</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>3918786000010055134</t>
+          <t>3918786000010070032</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Nacala Porto</t>
+          <t>Monapo</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1554,7 +1554,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1564,42 +1564,42 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>MURRUPELANE</t>
+          <t>TOPELANE</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Sessão_4</t>
+          <t>Sessão_9</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>03-Mar-2026</t>
+          <t>15-Apr-2026</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>3918786000010055132</t>
+          <t>3918786000010070030</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Nacala Porto</t>
+          <t>Monapo</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1611,7 +1611,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1621,17 +1621,17 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>MORRUPELANE</t>
+          <t>TOPELANE</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Sessão_3</t>
+          <t>Sessão_10</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1641,22 +1641,22 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>24-Feb-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>3918786000010055130</t>
+          <t>3918786000010069058</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Nacala Porto</t>
+          <t>Monapo</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1668,27 +1668,27 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>MURRUPELANE</t>
+          <t>RAMIANE</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Sessão_2</t>
+          <t>Sessão_10</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1698,22 +1698,22 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>17-Feb-2026</t>
+          <t>16-Apr-2026</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>3918786000010055128</t>
+          <t>3918786000010066060</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Nacala Porto</t>
+          <t>Monapo</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1725,22 +1725,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>MURRUPELANE</t>
+          <t>MOCONE</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Sessão_1</t>
+          <t>Sessão_9</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1750,22 +1750,22 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>10-Feb-2026</t>
+          <t>08-Apr-2026</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>3918786000010055126</t>
+          <t>3918786000010065072</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1782,7 +1782,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1792,17 +1792,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>MESEREPANE</t>
+          <t>MOCONE</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Sessão_10</t>
+          <t>Sessão_8</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1812,22 +1812,22 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>01-Apr-2026</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>3918786000010055064</t>
+          <t>3918786000010065070</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -1839,7 +1839,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1849,42 +1849,42 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>MONAPO RIO</t>
+          <t>MOCONE</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Sessão_10</t>
+          <t>Sessão_7</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>14-Apr-2026</t>
+          <t>25-Mar-2026</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>3918786000010050002</t>
+          <t>3918786000010065068</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -1896,7 +1896,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1906,42 +1906,42 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>MUELEGE</t>
+          <t>MOCONE</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Sessão_3</t>
+          <t>Sessão_6</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>26-Feb-2026</t>
+          <t>18-Mar-2026</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>3918786000010039074</t>
+          <t>3918786000010065066</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -1953,7 +1953,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1963,17 +1963,17 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>MUELEGE</t>
+          <t>MOCONE</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Sessão_4</t>
+          <t>Sessão_5</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1983,22 +1983,22 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>05-Mar-2026</t>
+          <t>11-Mar-2026</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>3918786000010039072</t>
+          <t>3918786000010065064</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2010,7 +2010,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2020,17 +2020,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>MUELEGE</t>
+          <t>MOCONE</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Sessão_2</t>
+          <t>Sessão_4</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2040,22 +2040,22 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>19-Feb-2026</t>
+          <t>04-Mar-2026</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>3918786000010039070</t>
+          <t>3918786000010065062</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2067,7 +2067,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2077,42 +2077,42 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>MUELEGE</t>
+          <t>MOCONE</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Sessão_1</t>
+          <t>Sessão_3</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>14-Feb-2026</t>
+          <t>25-Feb-2026</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>3918786000010039068</t>
+          <t>3918786000010065060</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2124,7 +2124,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2134,17 +2134,17 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>MOCONE</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Sessão_3</t>
+          <t>Sessão_2</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2154,22 +2154,22 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>25-Mar-2026</t>
+          <t>18-Feb-2026</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>3918786000010039066</t>
+          <t>3918786000010065058</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2181,7 +2181,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2191,17 +2191,17 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>MOCONE</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Sessão_2</t>
+          <t>Sessão_1</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2211,34 +2211,34 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>18-Apr-2026</t>
+          <t>11-Feb-2026</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>3918786000010039064</t>
+          <t>3918786000010065056</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2248,17 +2248,17 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>MOCONE</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Sessão_1</t>
+          <t>Sessão_10</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>13-Feb-2026</t>
+          <t>15-Apr-2026</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>3918786000010039062</t>
+          <t>3918786000010065054</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2295,7 +2295,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2305,17 +2305,17 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>MURRUPELANE</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Sessão_4</t>
+          <t>Sessão_10</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2325,22 +2325,22 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>04-Mar-2026</t>
+          <t>14-Apr-2026</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>3918786000010039060</t>
+          <t>3918786000010055144</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2352,27 +2352,27 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>MURRUPELANE</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Sessão_4</t>
+          <t>Sessão_9</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2382,34 +2382,34 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>04-Mar-2026</t>
+          <t>09-Apr-2026</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>3918786000010039058</t>
+          <t>3918786000010055142</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2419,17 +2419,17 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>MORRUPELANE</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Sessão_3</t>
+          <t>Sessão_8</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2439,22 +2439,22 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>25-Feb-2026</t>
+          <t>31-Mar-2026</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>3918786000010039056</t>
+          <t>3918786000010055140</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2466,7 +2466,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2476,17 +2476,17 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>MURRUPELANE</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Sessão_2</t>
+          <t>Sessão_7</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2496,22 +2496,22 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>18-Feb-2026</t>
+          <t>24-Mar-2026</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>3918786000010039054</t>
+          <t>3918786000010055138</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2523,52 +2523,52 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>MURRUPELANE</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Sessão_6</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>TOPELANE</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Sessão_1</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>13-Feb-2026</t>
+          <t>17-Mar-2026</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>3918786000010039052</t>
+          <t>3918786000010055136</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2580,7 +2580,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2590,17 +2590,17 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>MUELEGE</t>
+          <t>MURRUPELANE</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Sessão_9</t>
+          <t>Sessão_5</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2610,22 +2610,22 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>14-Apr-2026</t>
+          <t>10-Mar-2026</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>3918786000010039050</t>
+          <t>3918786000010055134</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2637,7 +2637,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2647,42 +2647,42 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>MURRUPELANE</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Sessão_10</t>
+          <t>Sessão_4</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>15-Apr-2026</t>
+          <t>03-Mar-2026</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>3918786000010037472</t>
+          <t>3918786000010055132</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2694,7 +2694,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2704,17 +2704,17 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>RAMIANE</t>
+          <t>MORRUPELANE</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Sessão_9</t>
+          <t>Sessão_3</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2724,22 +2724,22 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>14-Apr-2026</t>
+          <t>24-Feb-2026</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>3918786000010037470</t>
+          <t>3918786000010055130</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -2751,27 +2751,27 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>RAMIANE</t>
+          <t>MURRUPELANE</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Sessão_8</t>
+          <t>Sessão_2</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2781,22 +2781,22 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>10-Apr-2026</t>
+          <t>17-Feb-2026</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>3918786000010023384</t>
+          <t>3918786000010055128</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -2808,17 +2808,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>RAMIANE</t>
+          <t>MURRUPELANE</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2828,32 +2828,32 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>11-Feb-2026</t>
+          <t>10-Feb-2026</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>3918786000010023382</t>
+          <t>3918786000010055126</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -2865,7 +2865,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2875,17 +2875,17 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>MESEREPANE</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Sessão_9</t>
+          <t>Sessão_10</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2895,17 +2895,17 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>08-Apr-2026</t>
+          <t>16-Apr-2026</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>3918786000010023380</t>
+          <t>3918786000010055064</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -2922,7 +2922,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2932,17 +2932,17 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>MONAPO RIO</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Sessão_1</t>
+          <t>Sessão_10</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2952,17 +2952,17 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>13-Feb-2026</t>
+          <t>14-Apr-2026</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>3918786000010023378</t>
+          <t>3918786000010050002</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -2979,7 +2979,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2989,17 +2989,17 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>RAMIANE</t>
+          <t>MUELEGE</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Sessão_7</t>
+          <t>Sessão_3</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -3009,17 +3009,17 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>09-Apr-2026</t>
+          <t>26-Feb-2026</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>3918786000010020060</t>
+          <t>3918786000010039074</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3036,7 +3036,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3046,17 +3046,17 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>MESEREPANE</t>
+          <t>MUELEGE</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Sessão_9</t>
+          <t>Sessão_4</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -3066,17 +3066,17 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>09-Apr-2026</t>
+          <t>05-Mar-2026</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>3918786000010019064</t>
+          <t>3918786000010039072</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3093,52 +3093,52 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>MATHAPUE</t>
+          <t>MUELEGE</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Sessão_8</t>
+          <t>Sessão_2</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>FERNANDES LIMA &amp; TAIRAHA ESQUADRO</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>31-Mar-2026</t>
+          <t>19-Feb-2026</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>3918786000010015292</t>
+          <t>3918786000010039070</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Nacala Porto</t>
+          <t>Monapo</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3150,52 +3150,52 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>MATHAPUE</t>
+          <t>MUELEGE</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Sessão_7</t>
+          <t>Sessão_1</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>FERNANDES LIMA &amp; TAIRAHA ESQUADRO</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>14-Feb-2026</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>31-Mar-2026</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>3918786000010015290</t>
+          <t>3918786000010039068</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Nacala Porto</t>
+          <t>Monapo</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3207,52 +3207,52 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>MATHAPUE</t>
+          <t>TOPELANE</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Sessão_6</t>
+          <t>Sessão_3</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>FERNANDES LIMA &amp; TAIRAHA ESQUADRO</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>31-Mar-2026</t>
+          <t>25-Mar-2026</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>3918786000010015288</t>
+          <t>3918786000010039066</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Nacala Porto</t>
+          <t>Monapo</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3264,52 +3264,52 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>MATHAPUE</t>
+          <t>TOPELANE</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Sessão_5</t>
+          <t>Sessão_2</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>FERNANDES LIMA &amp; TAIRAHA ESQUADRO</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>31-Mar-2026</t>
+          <t>18-Apr-2026</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>3918786000010015286</t>
+          <t>3918786000010039064</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Nacala Porto</t>
+          <t>Monapo</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3321,37 +3321,37 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>MATHAPUE</t>
+          <t>TOPELANE</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Sessão_4</t>
+          <t>Sessão_1</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>FERNANDES LIMA &amp; TAIRAHA ESQUADRO</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>31-Mar-2026</t>
+          <t>13-Feb-2026</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3361,12 +3361,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>3918786000010015284</t>
+          <t>3918786000010039062</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Nacala Porto</t>
+          <t>Monapo</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -3378,52 +3378,52 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>MATHAPUE</t>
+          <t>TOPELANE</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Sessão_3</t>
+          <t>Sessão_4</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>FERNANDES LIMA &amp; TAIRAHA ESQUADRO</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>31-Mar-2026</t>
+          <t>04-Mar-2026</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>3918786000010015282</t>
+          <t>3918786000010039060</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Nacala Porto</t>
+          <t>Monapo</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -3435,52 +3435,52 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>MATHAPUE</t>
+          <t>TOPELANE</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Sessão_2</t>
+          <t>Sessão_4</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>FERNANDES LIMA &amp; TAIRAHA ESQUADRO</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>31-Mar-2026</t>
+          <t>04-Mar-2026</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>3918786000010015280</t>
+          <t>3918786000010039058</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Nacala Porto</t>
+          <t>Monapo</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -3492,52 +3492,52 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>MATHAPUE</t>
+          <t>TOPELANE</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Sessão_1</t>
+          <t>Sessão_3</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>FERNANDES LIMA &amp; TAIRAHA ESQUADRO</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>31-Mar-2026</t>
+          <t>25-Feb-2026</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>3918786000010015278</t>
+          <t>3918786000010039056</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Nacala Porto</t>
+          <t>Monapo</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -3559,17 +3559,17 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>MONAPO RIO</t>
+          <t>TOPELANE</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Sessão_9</t>
+          <t>Sessão_2</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -3579,17 +3579,17 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>08-Apr-2026</t>
+          <t>18-Feb-2026</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>3918786000010011002</t>
+          <t>3918786000010039054</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -3606,7 +3606,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3621,7 +3621,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Sessão_8</t>
+          <t>Sessão_1</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3636,17 +3636,17 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>08-Apr-2026</t>
+          <t>13-Feb-2026</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>3918786000010007188</t>
+          <t>3918786000010039052</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -3678,7 +3678,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Sessão_8</t>
+          <t>Sessão_9</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3693,17 +3693,17 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>09-Apr-2026</t>
+          <t>14-Apr-2026</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>3918786000010007186</t>
+          <t>3918786000010039050</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -3720,7 +3720,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Sessão_9</t>
+          <t>Sessão_10</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -3750,17 +3750,17 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>10-Apr-2026</t>
+          <t>15-Apr-2026</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>3918786000010005495</t>
+          <t>3918786000010037472</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -3777,7 +3777,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3787,17 +3787,17 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>RAMIANE</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Sessão_7</t>
+          <t>Sessão_9</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -3807,17 +3807,17 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>27-Mar-2026</t>
+          <t>14-Apr-2026</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>3918786000009978061</t>
+          <t>3918786000010037470</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -3834,7 +3834,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3844,17 +3844,17 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>RAMIANE</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Sessão_7</t>
+          <t>Sessão_8</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -3864,17 +3864,17 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>25-Mar-2026</t>
+          <t>10-Apr-2026</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>3918786000009978059</t>
+          <t>3918786000010023384</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -3891,7 +3891,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3901,17 +3901,17 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>RAMIANE</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Sessão_6</t>
+          <t>Sessão_1</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -3921,17 +3921,17 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>25-Mar-2026</t>
+          <t>11-Feb-2026</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>3918786000009978057</t>
+          <t>3918786000010023382</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -3948,7 +3948,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3963,12 +3963,12 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Sessão_5</t>
+          <t>Sessão_9</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -3978,17 +3978,17 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>11-Mar-2026</t>
+          <t>08-Apr-2026</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>3918786000009978055</t>
+          <t>3918786000010023380</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -4005,7 +4005,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4020,12 +4020,12 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Sessão_5</t>
+          <t>Sessão_1</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -4035,17 +4035,17 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>11-Mar-2026</t>
+          <t>13-Feb-2026</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>3918786000009978053</t>
+          <t>3918786000010023378</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -4062,7 +4062,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4072,7 +4072,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>MUELEGE</t>
+          <t>RAMIANE</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -4082,7 +4082,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -4092,17 +4092,17 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>02-Apr-2026</t>
+          <t>09-Apr-2026</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>3918786000009978051</t>
+          <t>3918786000010020060</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -4134,7 +4134,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Sessão_8</t>
+          <t>Sessão_9</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4149,7 +4149,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>02-Apr-2026</t>
+          <t>09-Apr-2026</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4159,7 +4159,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>3918786000009975096</t>
+          <t>3918786000010019064</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -4176,52 +4176,52 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>RAMIANE</t>
+          <t>MATHAPUE</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Sessão_6</t>
+          <t>Sessão_8</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+          <t>FERNANDES LIMA &amp; TAIRAHA ESQUADRO</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>02-Apr-2026</t>
+          <t>31-Mar-2026</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>3918786000009966138</t>
+          <t>3918786000010015292</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -4233,52 +4233,52 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>MATHAPUE</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Sessão_8</t>
+          <t>Sessão_7</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+          <t>FERNANDES LIMA &amp; TAIRAHA ESQUADRO</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>01-Apr-2026</t>
+          <t>31-Mar-2026</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>3918786000009966136</t>
+          <t>3918786000010015290</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -4290,52 +4290,52 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>MESEREPANE</t>
+          <t>MATHAPUE</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Sessão_7</t>
+          <t>Sessão_6</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+          <t>FERNANDES LIMA &amp; TAIRAHA ESQUADRO</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>01-Apr-2026</t>
+          <t>31-Mar-2026</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>3918786000009964076</t>
+          <t>3918786000010015288</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -4347,52 +4347,52 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>MESEREPANE</t>
+          <t>MATHAPUE</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Sessão_6</t>
+          <t>Sessão_5</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+          <t>FERNANDES LIMA &amp; TAIRAHA ESQUADRO</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>08-Apr-2026</t>
+          <t>31-Mar-2026</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>3918786000009964074</t>
+          <t>3918786000010015286</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -4404,52 +4404,52 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>MESEREPANE</t>
+          <t>MATHAPUE</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Sessão_5</t>
+          <t>Sessão_4</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+          <t>FERNANDES LIMA &amp; TAIRAHA ESQUADRO</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>01-Apr-2026</t>
+          <t>31-Mar-2026</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>3918786000009964072</t>
+          <t>3918786000010015284</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -4466,47 +4466,47 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>MESEREPANE</t>
+          <t>MATHAPUE</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Sessão_4</t>
+          <t>Sessão_3</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+          <t>FERNANDES LIMA &amp; TAIRAHA ESQUADRO</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>01-Apr-2026</t>
+          <t>31-Mar-2026</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>3918786000009964070</t>
+          <t>3918786000010015282</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -4518,52 +4518,52 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>MESEREPANE</t>
+          <t>MATHAPUE</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Sessão_3</t>
+          <t>Sessão_2</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+          <t>FERNANDES LIMA &amp; TAIRAHA ESQUADRO</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>01-Apr-2026</t>
+          <t>31-Mar-2026</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>3918786000009964068</t>
+          <t>3918786000010015280</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -4575,52 +4575,52 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>MESEREPANE</t>
+          <t>MATHAPUE</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Sessão_2</t>
+          <t>Sessão_1</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+          <t>FERNANDES LIMA &amp; TAIRAHA ESQUADRO</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>01-Apr-2026</t>
+          <t>31-Mar-2026</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>3918786000009964066</t>
+          <t>3918786000010015278</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -4632,7 +4632,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>MESEREPANE</t>
+          <t>MONAPO RIO</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Sessão_1</t>
+          <t>Sessão_9</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -4662,17 +4662,17 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>01-Apr-2026</t>
+          <t>08-Apr-2026</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>3918786000009964064</t>
+          <t>3918786000010011002</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -4689,7 +4689,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -4699,7 +4699,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>MONAPO RIO</t>
+          <t>TOPELANE</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -4709,7 +4709,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -4719,17 +4719,17 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>31-Mar-2026</t>
+          <t>08-Apr-2026</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>3918786000009964062</t>
+          <t>3918786000010007188</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -4746,7 +4746,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>MUELEGE</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -4776,17 +4776,17 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>01-Apr-2026</t>
+          <t>09-Apr-2026</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>3918786000009962078</t>
+          <t>3918786000010007186</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -4803,7 +4803,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -4813,17 +4813,17 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>MONAPO RIO</t>
+          <t>TOPELANE</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Sessão_7</t>
+          <t>Sessão_9</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -4833,17 +4833,17 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>24-Mar-2026</t>
+          <t>10-Apr-2026</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>3918786000009962026</t>
+          <t>3918786000010005495</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -4870,17 +4870,17 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>MONAPO RIO</t>
+          <t>TOPELANE</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Sessão_6</t>
+          <t>Sessão_7</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -4890,17 +4890,17 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>17-Mar-2026</t>
+          <t>27-Mar-2026</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>3918786000009962024</t>
+          <t>3918786000009978061</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -4917,7 +4917,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -4927,17 +4927,17 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>MONAPO RIO</t>
+          <t>TOPELANE</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Sessão_5</t>
+          <t>Sessão_7</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -4947,17 +4947,17 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>10-Mar-2026</t>
+          <t>25-Mar-2026</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>3918786000009962022</t>
+          <t>3918786000009978059</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -4974,7 +4974,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -4984,17 +4984,17 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>MONAPO RIO</t>
+          <t>TOPELANE</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Sessão_4</t>
+          <t>Sessão_6</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -5004,17 +5004,17 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>03-Mar-2026</t>
+          <t>25-Mar-2026</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>3918786000009962020</t>
+          <t>3918786000009978057</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -5031,7 +5031,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5041,17 +5041,17 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>MONAPO RIO</t>
+          <t>TOPELANE</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Sessão_3</t>
+          <t>Sessão_5</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -5061,17 +5061,17 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>24-Feb-2026</t>
+          <t>11-Mar-2026</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>3918786000009962018</t>
+          <t>3918786000009978055</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -5088,7 +5088,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5098,17 +5098,17 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>MONAPO RIO</t>
+          <t>TOPELANE</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Sessão_2</t>
+          <t>Sessão_5</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -5118,17 +5118,17 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>17-Feb-2026</t>
+          <t>11-Mar-2026</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>3918786000009962016</t>
+          <t>3918786000009978053</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -5145,7 +5145,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5155,17 +5155,17 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>MONAPO RIO</t>
+          <t>MUELEGE</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Sessão_1</t>
+          <t>Sessão_7</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -5175,17 +5175,17 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>13-Feb-2026</t>
+          <t>02-Apr-2026</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>3918786000009962014</t>
+          <t>3918786000009978051</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -5202,7 +5202,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5212,17 +5212,17 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>RAMIANE</t>
+          <t>MESEREPANE</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Sessão_5</t>
+          <t>Sessão_8</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -5232,17 +5232,17 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>26-Mar-2026</t>
+          <t>02-Apr-2026</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>3918786000009891291</t>
+          <t>3918786000009975096</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -5259,7 +5259,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5269,12 +5269,12 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>RAMIANE</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Sessão_7</t>
+          <t>Sessão_6</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5289,17 +5289,17 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>25-Mar-2026</t>
+          <t>02-Apr-2026</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>3918786000009891287</t>
+          <t>3918786000009966138</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -5316,7 +5316,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Sessão_6</t>
+          <t>Sessão_8</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -5346,17 +5346,17 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>25-Mar-2026</t>
+          <t>01-Apr-2026</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>3918786000009888175</t>
+          <t>3918786000009966136</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -5373,7 +5373,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5383,17 +5383,17 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>MUELEGE</t>
+          <t>MESEREPANE</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Sessão_6</t>
+          <t>Sessão_7</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -5403,17 +5403,17 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>19-Mar-2026</t>
+          <t>01-Apr-2026</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>3918786000009886133</t>
+          <t>3918786000009964076</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -5430,7 +5430,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5440,17 +5440,17 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>MUELEGE</t>
+          <t>MESEREPANE</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Sessão_5</t>
+          <t>Sessão_6</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -5460,17 +5460,17 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>12-Mar-2026</t>
+          <t>08-Apr-2026</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>3918786000009886129</t>
+          <t>3918786000009964074</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -5487,7 +5487,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5497,17 +5497,17 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>MESEREPANE</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Sessão_2</t>
+          <t>Sessão_5</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -5517,17 +5517,17 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>18-Feb-2026</t>
+          <t>01-Apr-2026</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>3918786000009856153</t>
+          <t>3918786000009964072</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -5544,7 +5544,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -5554,17 +5554,17 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>MESEREPANE</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Sessão_3</t>
+          <t>Sessão_4</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -5574,17 +5574,17 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>25-Feb-2026</t>
+          <t>01-Apr-2026</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>3918786000009856149</t>
+          <t>3918786000009964070</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -5601,7 +5601,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -5611,17 +5611,17 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>MESEREPANE</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Sessão_4</t>
+          <t>Sessão_3</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -5631,17 +5631,17 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>04-Mar-2026</t>
+          <t>01-Apr-2026</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>3918786000009856145</t>
+          <t>3918786000009964068</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -5658,7 +5658,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -5668,7 +5668,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>RAMIANE</t>
+          <t>MESEREPANE</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -5688,17 +5688,17 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>19-Feb-2026</t>
+          <t>01-Apr-2026</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>3918786000009856141</t>
+          <t>3918786000009964066</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -5715,7 +5715,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -5725,17 +5725,17 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>RAMIANE</t>
+          <t>MESEREPANE</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Sessão_3</t>
+          <t>Sessão_1</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -5745,17 +5745,17 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>26-Feb-2026</t>
+          <t>01-Apr-2026</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>3918786000009856137</t>
+          <t>3918786000009964064</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -5772,7 +5772,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -5782,17 +5782,17 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>MONAPO RIO</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Sessão_5</t>
+          <t>Sessão_8</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -5802,17 +5802,17 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>11-Mar-2026</t>
+          <t>31-Mar-2026</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>3918786000009856133</t>
+          <t>3918786000009964062</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -5829,7 +5829,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -5844,12 +5844,12 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Sessão_6</t>
+          <t>Sessão_8</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -5859,17 +5859,17 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>17-Mar-2026</t>
+          <t>01-Apr-2026</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>3918786000009856129</t>
+          <t>3918786000009962078</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -5886,55 +5886,1138 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>MONAPO RIO</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Sessão_7</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>24-Mar-2026</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>3918786000009962026</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>MONAPO RIO</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Sessão_6</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>17-Mar-2026</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>3918786000009962024</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>MONAPO RIO</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Sessão_5</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>10-Mar-2026</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>3918786000009962022</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>MONAPO RIO</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Sessão_4</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>03-Mar-2026</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>3918786000009962020</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>MONAPO RIO</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Sessão_3</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>24-Feb-2026</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>3918786000009962018</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>MONAPO RIO</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Sessão_2</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>17-Feb-2026</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>3918786000009962016</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>MONAPO RIO</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Sessão_1</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>13-Feb-2026</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>3918786000009962014</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>RAMIANE</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Sessão_5</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>26-Mar-2026</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>3918786000009891291</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>TOPELANE</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Sessão_7</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>25-Mar-2026</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>3918786000009891287</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>TOPELANE</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Sessão_6</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>25-Mar-2026</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>3918786000009888175</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>MUELEGE</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Sessão_6</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>19-Mar-2026</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>3918786000009886133</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>MUELEGE</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Sessão_5</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>12-Mar-2026</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>3918786000009886129</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>TOPELANE</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Sessão_2</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>18-Feb-2026</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>3918786000009856153</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>TOPELANE</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Sessão_3</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>25-Feb-2026</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>3918786000009856149</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>TOPELANE</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Sessão_4</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>04-Mar-2026</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>3918786000009856145</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>RAMIANE</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Sessão_2</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>19-Feb-2026</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>3918786000009856141</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>RAMIANE</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Sessão_3</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>26-Feb-2026</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>3918786000009856137</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>TOPELANE</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Sessão_5</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>11-Mar-2026</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>3918786000009856133</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>TOPELANE</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Sessão_6</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>17-Mar-2026</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>3918786000009856129</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
         <is>
           <t>RAMIANE</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr">
+      <c r="D117" t="inlineStr">
         <is>
           <t>Sessão_4</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr">
+      <c r="E117" t="inlineStr">
         <is>
           <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
         </is>
       </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
         <is>
           <t>19-Mar-2026</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
+      <c r="H117" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="I98" t="inlineStr">
+      <c r="I117" t="inlineStr">
         <is>
           <t>3918786000009856125</t>
         </is>
       </c>
-      <c r="J98" t="inlineStr">
+      <c r="J117" t="inlineStr">
         <is>
           <t>Monapo</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr">
+      <c r="K117" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -6201,13 +7284,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{50646A16-A334-4C48-8E7B-FDC4CDC64B89}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{507DE559-1BBD-4FD9-A52D-329618178BBD}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA05B69D-E208-41C9-990C-41CDBB364A64}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{979A11B2-CA46-461C-9951-5CB9DC9AF005}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B36614B6-DCE4-4131-9FD5-BC3968F5FD09}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{23568F56-5CA8-4F4C-AEBA-4E029C7FCA7C}"/>
 </file>
--- a/Qualidade_Sessoes.xlsx
+++ b/Qualidade_Sessoes.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K117"/>
+  <dimension ref="A1:K146"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -414,7 +414,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -424,17 +424,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>MATHAPUE</t>
+          <t>NAUAIA</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Sessão_11</t>
+          <t>Sessão_12</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>FERNANDES LIMA &amp; TAIRAHA ESQUADRO</t>
+          <t>VANIL HORACIO &amp; ARMANDO ROANEQUE</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -444,17 +444,17 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>21-Apr-2026</t>
+          <t>28-Apr-2026</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3918786000010098124</t>
+          <t>3918786000010132024</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -471,7 +471,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -481,17 +481,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>MATHAPUE</t>
+          <t>NAUAIA</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Sessão_10</t>
+          <t>Sessão_11</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FERNANDES LIMA &amp; TAIRAHA ESQUADRO</t>
+          <t>VANIL HORACIO &amp; ARMANDO ROANEQUE</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -506,12 +506,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3918786000010098122</t>
+          <t>3918786000010132022</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -528,7 +528,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -538,17 +538,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MATHAPUE</t>
+          <t>NAUAIA</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Sessão_9</t>
+          <t>Sessão_10</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>FERNANDES LIMA &amp; TAIRAHA ESQUADRO</t>
+          <t>VANIL HORACIO &amp; ARMANDO ROANEQUE</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -558,17 +558,17 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>21-Apr-2026</t>
+          <t>15-Apr-2026</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3918786000010098120</t>
+          <t>3918786000010132020</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -585,7 +585,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -595,17 +595,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MOCONE</t>
+          <t>NAUAIA</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Sessão_11</t>
+          <t>Sessão_9</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
+          <t>VANIL HORACIO &amp; ARMANDO ROANEQUE</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -615,17 +615,17 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>09-Apr-2026</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3918786000010095002</t>
+          <t>3918786000010132018</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -642,7 +642,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -652,17 +652,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ONTUPAIA</t>
+          <t>NAUAIA</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Sessão_11</t>
+          <t>Sessão_8</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>NUCHATE ESTEVAO &amp; BELITO LUCIANO</t>
+          <t>VANIL HORACIO &amp; ARMANDO ROANEQUE</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -672,17 +672,17 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>31-Mar-2026</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3918786000010092104</t>
+          <t>3918786000010132016</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -699,7 +699,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -709,17 +709,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ONTUPAIA</t>
+          <t>NAUAIA</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Sessão_10</t>
+          <t>Sessão_7</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>NUCHATE ESTEVAO &amp; BELITO LUCIANO</t>
+          <t>VANIL HORACIO &amp; ARMANDO ROANEQUE</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -729,7 +729,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>15-Apr-2026</t>
+          <t>24-Mar-2026</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3918786000010092102</t>
+          <t>3918786000010132014</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -756,7 +756,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -766,17 +766,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ONTUPAIA</t>
+          <t>NAUAIA</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Sessão_9</t>
+          <t>Sessão_6</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>NUCHATE ESTEVAO &amp; BELITO LUCIANO</t>
+          <t>VANIL HORACIO &amp; ARMANDO ROANEQUE</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -786,17 +786,17 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>08-Apr-2026</t>
+          <t>19-Mar-2026</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3918786000010092100</t>
+          <t>3918786000010132012</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -813,7 +813,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -823,17 +823,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ONTUPAIA</t>
+          <t>NAUAIA</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Sessão_8</t>
+          <t>Sessão_5</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>NUCHATE ESTEVAO &amp; BELITO LUCIANO</t>
+          <t>VANIL HORACIO &amp; ARMANDO ROANEQUE</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>01-Apr-2026</t>
+          <t>10-Mar-2026</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -853,7 +853,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3918786000010092098</t>
+          <t>3918786000010132010</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -870,7 +870,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -880,17 +880,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ONTUPAIA</t>
+          <t>NAUAIA</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Sessão_7</t>
+          <t>Sessão_4</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>NUCHATE ESTEVAO &amp; BELITO LUCIANO</t>
+          <t>VANIL HORACIO &amp; ARMANDO ROANEQUE</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -900,17 +900,17 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>25-Mar-2026</t>
+          <t>03-Mar-2026</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3918786000010092096</t>
+          <t>3918786000010132008</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -937,37 +937,37 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ONTUPAIA</t>
+          <t>NAUAIA</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Sessão_6</t>
+          <t>Sessão_3</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>NUCHATE ESTEVAO &amp; BELITO LUCIANO</t>
+          <t>VANIL HORACIO &amp; ARMANDO ROANEQUE</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>18-Mar-2026</t>
+          <t>24-Feb-2026</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3918786000010092094</t>
+          <t>3918786000010132006</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -984,7 +984,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -994,37 +994,37 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ONTUPAIA</t>
+          <t>NAUAIA</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Sessão_5</t>
+          <t>Sessão_2</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>NUCHATE ESTEVAO &amp; BELITO LUCIANO</t>
+          <t>VANIL HORACIO &amp; ARMANDO ROANEQUE</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>11-Mar-2026</t>
+          <t>17-Feb-2026</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3918786000010092092</t>
+          <t>3918786000010132004</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1034,14 +1034,14 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1051,37 +1051,37 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ONTUPAIA</t>
+          <t>NAUAIA</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Sessão_4</t>
+          <t>Sessão_1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>NUCHATE ESTEVAO &amp; BELITO LUCIANO</t>
+          <t>VANIL HORACIO &amp; ARMANDO ROANEQUE</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>04-Mar-2026</t>
+          <t>10-Feb-2026</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3918786000010092090</t>
+          <t>3918786000010132002</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1098,7 +1098,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Sessão_3</t>
+          <t>Sessão_12</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1123,22 +1123,22 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>25-Mar-2026</t>
+          <t>29-Apr-2026</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3918786000010092088</t>
+          <t>3918786000010131087</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1155,7 +1155,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ONTUPAIA</t>
+          <t>NAHERENQUE</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Sessão_2</t>
+          <t>Sessão_12</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1180,22 +1180,22 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>18-Feb-2026</t>
+          <t>28-Apr-2026</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3918786000010092086</t>
+          <t>3918786000010126084</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1212,22 +1212,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ONTUPAIA</t>
+          <t>NAHERENQUE</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Sessão_1</t>
+          <t>Sessão_11</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1237,22 +1237,22 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>11-Feb-2026</t>
+          <t>21-Apr-2026</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>3918786000010092084</t>
+          <t>3918786000010126082</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1262,59 +1262,59 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>NAHERENQUE</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Sessão_11</t>
+          <t>Sessão_10</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+          <t>NUCHATE ESTEVAO &amp; BELITO LUCIANO</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>16-Apr-2026</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>3918786000010088069</t>
+          <t>3918786000010126080</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1326,7 +1326,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1336,42 +1336,42 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>NAHERENQUE</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Sessão_11</t>
+          <t>Sessão_9</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+          <t>NUCHATE ESTEVAO &amp; BELITO LUCIANO</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>09-Apr-2026</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>3918786000010088067</t>
+          <t>3918786000010126078</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1393,17 +1393,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>NAHERENQUE</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Sessão_11</t>
+          <t>Sessão_8</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+          <t>NUCHATE ESTEVAO &amp; BELITO LUCIANO</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>31-Mar-2026</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>3918786000010087128</t>
+          <t>3918786000010126076</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1440,7 +1440,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1450,17 +1450,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>MESEREPANE</t>
+          <t>NAHERENQUE</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Sessão_11</t>
+          <t>Sessão_7</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+          <t>NUCHATE ESTEVAO &amp; BELITO LUCIANO</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1470,22 +1470,22 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>26-Mar-2026</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>3918786000010087064</t>
+          <t>3918786000010126074</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1507,42 +1507,42 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>MUELEGE</t>
+          <t>NAHERENQUE</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Sessão_10</t>
+          <t>Sessão_6</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+          <t>NUCHATE ESTEVAO &amp; BELITO LUCIANO</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>15-Apr-2026</t>
+          <t>17-Mar-2026</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>3918786000010070032</t>
+          <t>3918786000010126072</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1554,7 +1554,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1564,17 +1564,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>NAHERENQUE</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Sessão_9</t>
+          <t>Sessão_5</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+          <t>NUCHATE ESTEVAO &amp; BELITO LUCIANO</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>15-Apr-2026</t>
+          <t>10-Mar-2026</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1594,12 +1594,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>3918786000010070030</t>
+          <t>3918786000010126070</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1611,7 +1611,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1621,17 +1621,17 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>NAHERENQUE</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Sessão_10</t>
+          <t>Sessão_4</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+          <t>NUCHATE ESTEVAO &amp; BELITO LUCIANO</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1641,22 +1641,22 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>03-Mar-2026</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>3918786000010069058</t>
+          <t>3918786000010126068</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1668,7 +1668,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1678,17 +1678,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>RAMIANE</t>
+          <t>NAHERENQUE</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Sessão_10</t>
+          <t>Sessão_3</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+          <t>NUCHATE ESTEVAO &amp; BELITO LUCIANO</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1698,22 +1698,22 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>24-Feb-2026</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>3918786000010066060</t>
+          <t>3918786000010126066</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1725,7 +1725,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1735,17 +1735,17 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>MOCONE</t>
+          <t>NAHERENQUE</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Sessão_9</t>
+          <t>Sessão_2</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
+          <t>NUCHATE ESTEVAO &amp; BELITO LUCIANO</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1755,17 +1755,17 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>08-Apr-2026</t>
+          <t>17-Feb-2026</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>3918786000010065072</t>
+          <t>3918786000010126064</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1782,7 +1782,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1792,37 +1792,37 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>MOCONE</t>
+          <t>NAHERENQUE</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Sessão_8</t>
+          <t>Sessão_1</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
+          <t>NUCHATE ESTEVAO &amp; BELITO LUCIANO</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>01-Apr-2026</t>
+          <t>10-Feb-2026</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>3918786000010065070</t>
+          <t>3918786000010126062</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -1839,7 +1839,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1849,42 +1849,42 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>MOCONE</t>
+          <t>MONAPO RIO</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Sessão_7</t>
+          <t>Sessão_11</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>25-Mar-2026</t>
+          <t>21-Apr-2026</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>3918786000010065068</t>
+          <t>3918786000010102118</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Nacala Porto</t>
+          <t>Monapo</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -1896,7 +1896,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1906,37 +1906,37 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>MOCONE</t>
+          <t>MATHAPUE</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Sessão_6</t>
+          <t>Sessão_11</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
+          <t>FERNANDES LIMA &amp; TAIRAHA ESQUADRO</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>18-Mar-2026</t>
+          <t>21-Apr-2026</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>3918786000010065066</t>
+          <t>3918786000010098124</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -1953,7 +1953,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1963,17 +1963,17 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>MOCONE</t>
+          <t>MATHAPUE</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Sessão_5</t>
+          <t>Sessão_10</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
+          <t>FERNANDES LIMA &amp; TAIRAHA ESQUADRO</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1983,17 +1983,17 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>11-Mar-2026</t>
+          <t>21-Apr-2026</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>3918786000010065064</t>
+          <t>3918786000010098122</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2010,7 +2010,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2020,17 +2020,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>MOCONE</t>
+          <t>MATHAPUE</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Sessão_4</t>
+          <t>Sessão_9</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
+          <t>FERNANDES LIMA &amp; TAIRAHA ESQUADRO</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2040,17 +2040,17 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>04-Mar-2026</t>
+          <t>21-Apr-2026</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>32</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>3918786000010065062</t>
+          <t>3918786000010098120</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2067,47 +2067,47 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>MURRUPELANE</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Sessão_11</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>23-Apr-2026</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>MOCONE</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Sessão_3</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>25-Feb-2026</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>3918786000010065060</t>
+          <t>3918786000010095084</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2124,7 +2124,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Sessão_2</t>
+          <t>Sessão_11</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2154,17 +2154,17 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>18-Feb-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>3918786000010065058</t>
+          <t>3918786000010095002</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2181,7 +2181,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2191,17 +2191,17 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>MOCONE</t>
+          <t>RAMIANE</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Sessão_1</t>
+          <t>Sessão_11</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2211,34 +2211,34 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>11-Feb-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>3918786000010065056</t>
+          <t>3918786000010094010</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Nacala Porto</t>
+          <t>Monapo</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2248,17 +2248,17 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>MOCONE</t>
+          <t>ONTUPAIA</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Sessão_10</t>
+          <t>Sessão_11</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
+          <t>NUCHATE ESTEVAO &amp; BELITO LUCIANO</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2268,17 +2268,17 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>15-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>3918786000010065054</t>
+          <t>3918786000010092104</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2295,7 +2295,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2305,7 +2305,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>MURRUPELANE</t>
+          <t>ONTUPAIA</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2315,7 +2315,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
+          <t>NUCHATE ESTEVAO &amp; BELITO LUCIANO</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2325,17 +2325,17 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>14-Apr-2026</t>
+          <t>15-Apr-2026</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>3918786000010055144</t>
+          <t>3918786000010092102</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2352,17 +2352,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>MURRUPELANE</t>
+          <t>ONTUPAIA</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2372,7 +2372,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
+          <t>NUCHATE ESTEVAO &amp; BELITO LUCIANO</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2382,17 +2382,17 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>09-Apr-2026</t>
+          <t>08-Apr-2026</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>3918786000010055142</t>
+          <t>3918786000010092100</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2402,14 +2402,14 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2419,7 +2419,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>MORRUPELANE</t>
+          <t>ONTUPAIA</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2429,7 +2429,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
+          <t>NUCHATE ESTEVAO &amp; BELITO LUCIANO</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2439,17 +2439,17 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>31-Mar-2026</t>
+          <t>01-Apr-2026</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>3918786000010055140</t>
+          <t>3918786000010092098</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2466,7 +2466,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2476,7 +2476,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>MURRUPELANE</t>
+          <t>ONTUPAIA</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
+          <t>NUCHATE ESTEVAO &amp; BELITO LUCIANO</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2496,17 +2496,17 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>24-Mar-2026</t>
+          <t>25-Mar-2026</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>3918786000010055138</t>
+          <t>3918786000010092096</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2523,7 +2523,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>MURRUPELANE</t>
+          <t>ONTUPAIA</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2543,27 +2543,27 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
+          <t>NUCHATE ESTEVAO &amp; BELITO LUCIANO</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>17-Mar-2026</t>
+          <t>18-Mar-2026</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>3918786000010055136</t>
+          <t>3918786000010092094</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2580,7 +2580,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2590,7 +2590,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>MURRUPELANE</t>
+          <t>ONTUPAIA</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2600,7 +2600,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
+          <t>NUCHATE ESTEVAO &amp; BELITO LUCIANO</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2610,17 +2610,17 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>10-Mar-2026</t>
+          <t>11-Mar-2026</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>3918786000010055134</t>
+          <t>3918786000010092092</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2637,7 +2637,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>MURRUPELANE</t>
+          <t>ONTUPAIA</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2657,27 +2657,27 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
+          <t>NUCHATE ESTEVAO &amp; BELITO LUCIANO</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>03-Mar-2026</t>
+          <t>04-Mar-2026</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>3918786000010055132</t>
+          <t>3918786000010092090</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2694,7 +2694,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2704,7 +2704,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>MORRUPELANE</t>
+          <t>ONTUPAIA</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
+          <t>NUCHATE ESTEVAO &amp; BELITO LUCIANO</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>24-Feb-2026</t>
+          <t>25-Mar-2026</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>3918786000010055130</t>
+          <t>3918786000010092088</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -2751,17 +2751,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>MURRUPELANE</t>
+          <t>ONTUPAIA</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
+          <t>NUCHATE ESTEVAO &amp; BELITO LUCIANO</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2781,17 +2781,17 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>17-Feb-2026</t>
+          <t>18-Feb-2026</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>3918786000010055128</t>
+          <t>3918786000010092086</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -2808,17 +2808,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>MURRUPELANE</t>
+          <t>ONTUPAIA</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2828,27 +2828,27 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
+          <t>NUCHATE ESTEVAO &amp; BELITO LUCIANO</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>10-Feb-2026</t>
+          <t>11-Feb-2026</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>3918786000010055126</t>
+          <t>3918786000010092084</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -2865,7 +2865,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2875,17 +2875,17 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>MESEREPANE</t>
+          <t>MUELEGE</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Sessão_10</t>
+          <t>Sessão_11</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2895,17 +2895,17 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>3918786000010055064</t>
+          <t>3918786000010091122</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -2932,17 +2932,17 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>MONAPO RIO</t>
+          <t>TOPELANE</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Sessão_10</t>
+          <t>Sessão_11</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2952,17 +2952,17 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>14-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>3918786000010050002</t>
+          <t>3918786000010088069</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -2979,7 +2979,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>MUELEGE</t>
+          <t>TOPELANE</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Sessão_3</t>
+          <t>Sessão_11</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3009,17 +3009,17 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>26-Feb-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>3918786000010039074</t>
+          <t>3918786000010088067</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3046,17 +3046,17 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>MUELEGE</t>
+          <t>TOPELANE</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Sessão_4</t>
+          <t>Sessão_11</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -3066,17 +3066,17 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>05-Mar-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>3918786000010039072</t>
+          <t>3918786000010087128</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3093,7 +3093,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3103,17 +3103,17 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>MUELEGE</t>
+          <t>MESEREPANE</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Sessão_2</t>
+          <t>Sessão_11</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -3123,17 +3123,17 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>19-Feb-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>3918786000010039070</t>
+          <t>3918786000010087064</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3150,7 +3150,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3165,7 +3165,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Sessão_1</t>
+          <t>Sessão_10</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3180,17 +3180,17 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>14-Feb-2026</t>
+          <t>15-Apr-2026</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>3918786000010039068</t>
+          <t>3918786000010070032</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3222,7 +3222,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Sessão_3</t>
+          <t>Sessão_9</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3237,17 +3237,17 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>25-Mar-2026</t>
+          <t>15-Apr-2026</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>3918786000010039066</t>
+          <t>3918786000010070030</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3279,7 +3279,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Sessão_2</t>
+          <t>Sessão_10</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3294,17 +3294,17 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>18-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>3918786000010039064</t>
+          <t>3918786000010069058</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -3321,7 +3321,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3331,17 +3331,17 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>RAMIANE</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Sessão_1</t>
+          <t>Sessão_10</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -3351,17 +3351,17 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>13-Feb-2026</t>
+          <t>16-Apr-2026</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>3918786000010039062</t>
+          <t>3918786000010066060</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -3378,7 +3378,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3388,17 +3388,17 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>MOCONE</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Sessão_4</t>
+          <t>Sessão_9</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -3408,22 +3408,22 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>04-Mar-2026</t>
+          <t>08-Apr-2026</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>3918786000010039060</t>
+          <t>3918786000010065072</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -3435,7 +3435,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3445,17 +3445,17 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>MOCONE</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Sessão_4</t>
+          <t>Sessão_8</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -3465,22 +3465,22 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>04-Mar-2026</t>
+          <t>01-Apr-2026</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>3918786000010039058</t>
+          <t>3918786000010065070</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -3492,7 +3492,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3502,42 +3502,42 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>MOCONE</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Sessão_3</t>
+          <t>Sessão_7</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>25-Feb-2026</t>
+          <t>25-Mar-2026</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>3918786000010039056</t>
+          <t>3918786000010065068</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -3549,7 +3549,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3559,42 +3559,42 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>MOCONE</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Sessão_2</t>
+          <t>Sessão_6</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>18-Feb-2026</t>
+          <t>18-Mar-2026</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>3918786000010039054</t>
+          <t>3918786000010065066</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -3606,7 +3606,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3616,17 +3616,17 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>MOCONE</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Sessão_1</t>
+          <t>Sessão_5</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -3636,22 +3636,22 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>13-Feb-2026</t>
+          <t>11-Mar-2026</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>3918786000010039052</t>
+          <t>3918786000010065064</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -3663,7 +3663,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3673,17 +3673,17 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>MUELEGE</t>
+          <t>MOCONE</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Sessão_9</t>
+          <t>Sessão_4</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -3693,22 +3693,22 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>14-Apr-2026</t>
+          <t>04-Mar-2026</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>3918786000010039050</t>
+          <t>3918786000010065062</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -3720,7 +3720,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3730,42 +3730,42 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>MOCONE</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Sessão_10</t>
+          <t>Sessão_3</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>15-Apr-2026</t>
+          <t>25-Feb-2026</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>3918786000010037472</t>
+          <t>3918786000010065060</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -3777,7 +3777,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3787,17 +3787,17 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>RAMIANE</t>
+          <t>MOCONE</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Sessão_9</t>
+          <t>Sessão_2</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -3807,7 +3807,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>14-Apr-2026</t>
+          <t>18-Feb-2026</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -3817,12 +3817,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>3918786000010037470</t>
+          <t>3918786000010065058</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -3834,7 +3834,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3844,17 +3844,17 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>RAMIANE</t>
+          <t>MOCONE</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Sessão_8</t>
+          <t>Sessão_1</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -3864,34 +3864,34 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>10-Apr-2026</t>
+          <t>11-Feb-2026</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>3918786000010023384</t>
+          <t>3918786000010065056</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3901,17 +3901,17 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>RAMIANE</t>
+          <t>MOCONE</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Sessão_1</t>
+          <t>Sessão_10</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -3921,22 +3921,22 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>11-Feb-2026</t>
+          <t>15-Apr-2026</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>3918786000010023382</t>
+          <t>3918786000010065054</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -3948,7 +3948,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3958,17 +3958,17 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>MURRUPELANE</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Sessão_9</t>
+          <t>Sessão_10</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -3978,22 +3978,22 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>08-Apr-2026</t>
+          <t>14-Apr-2026</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>3918786000010023380</t>
+          <t>3918786000010055144</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -4005,27 +4005,27 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>MURRUPELANE</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Sessão_1</t>
+          <t>Sessão_9</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -4035,34 +4035,34 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>13-Feb-2026</t>
+          <t>09-Apr-2026</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>3918786000010023378</t>
+          <t>3918786000010055142</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4072,17 +4072,17 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>RAMIANE</t>
+          <t>MORRUPELANE</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Sessão_7</t>
+          <t>Sessão_8</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -4092,22 +4092,22 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>09-Apr-2026</t>
+          <t>31-Mar-2026</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>3918786000010020060</t>
+          <t>3918786000010055140</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -4119,7 +4119,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4129,17 +4129,17 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>MESEREPANE</t>
+          <t>MURRUPELANE</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Sessão_9</t>
+          <t>Sessão_7</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -4149,22 +4149,22 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>09-Apr-2026</t>
+          <t>24-Mar-2026</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>3918786000010019064</t>
+          <t>3918786000010055138</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -4176,47 +4176,47 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>MATHAPUE</t>
+          <t>MURRUPELANE</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Sessão_8</t>
+          <t>Sessão_6</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>FERNANDES LIMA &amp; TAIRAHA ESQUADRO</t>
+          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>17-Mar-2026</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>31-Mar-2026</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>3918786000010015292</t>
+          <t>3918786000010055136</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -4233,47 +4233,47 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>MATHAPUE</t>
+          <t>MURRUPELANE</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Sessão_7</t>
+          <t>Sessão_5</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>FERNANDES LIMA &amp; TAIRAHA ESQUADRO</t>
+          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>31-Mar-2026</t>
+          <t>10-Mar-2026</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>3918786000010015290</t>
+          <t>3918786000010055134</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -4290,47 +4290,47 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>MATHAPUE</t>
+          <t>MURRUPELANE</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Sessão_6</t>
+          <t>Sessão_4</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>FERNANDES LIMA &amp; TAIRAHA ESQUADRO</t>
+          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>31-Mar-2026</t>
+          <t>03-Mar-2026</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>3918786000010015288</t>
+          <t>3918786000010055132</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -4347,47 +4347,47 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>MATHAPUE</t>
+          <t>MORRUPELANE</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Sessão_5</t>
+          <t>Sessão_3</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>FERNANDES LIMA &amp; TAIRAHA ESQUADRO</t>
+          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>31-Mar-2026</t>
+          <t>24-Feb-2026</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>3918786000010015286</t>
+          <t>3918786000010055130</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -4404,47 +4404,47 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>MURRUPELANE</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Sessão_2</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>17-Feb-2026</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>MATHAPUE</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>Sessão_4</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>FERNANDES LIMA &amp; TAIRAHA ESQUADRO</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>31-Mar-2026</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>3918786000010015284</t>
+          <t>3918786000010055128</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -4461,47 +4461,47 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>MATHAPUE</t>
+          <t>MURRUPELANE</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Sessão_3</t>
+          <t>Sessão_1</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>FERNANDES LIMA &amp; TAIRAHA ESQUADRO</t>
+          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>31-Mar-2026</t>
+          <t>10-Feb-2026</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>3918786000010015282</t>
+          <t>3918786000010055126</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -4518,52 +4518,52 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>MATHAPUE</t>
+          <t>MESEREPANE</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Sessão_2</t>
+          <t>Sessão_10</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>FERNANDES LIMA &amp; TAIRAHA ESQUADRO</t>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>31-Mar-2026</t>
+          <t>16-Apr-2026</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>3918786000010015280</t>
+          <t>3918786000010055064</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Nacala Porto</t>
+          <t>Monapo</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -4575,52 +4575,52 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>MATHAPUE</t>
+          <t>MONAPO RIO</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Sessão_1</t>
+          <t>Sessão_10</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>FERNANDES LIMA &amp; TAIRAHA ESQUADRO</t>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>31-Mar-2026</t>
+          <t>14-Apr-2026</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>3918786000010015278</t>
+          <t>3918786000010050002</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Nacala Porto</t>
+          <t>Monapo</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -4642,17 +4642,17 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>MONAPO RIO</t>
+          <t>MUELEGE</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Sessão_9</t>
+          <t>Sessão_3</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -4662,17 +4662,17 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>08-Apr-2026</t>
+          <t>26-Feb-2026</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>3918786000010011002</t>
+          <t>3918786000010039074</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -4689,7 +4689,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -4699,12 +4699,12 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>MUELEGE</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Sessão_8</t>
+          <t>Sessão_4</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -4719,17 +4719,17 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>08-Apr-2026</t>
+          <t>05-Mar-2026</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>3918786000010007188</t>
+          <t>3918786000010039072</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -4746,7 +4746,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Sessão_8</t>
+          <t>Sessão_2</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -4776,17 +4776,17 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>09-Apr-2026</t>
+          <t>19-Feb-2026</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>3918786000010007186</t>
+          <t>3918786000010039070</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -4803,7 +4803,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -4813,12 +4813,12 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>MUELEGE</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Sessão_9</t>
+          <t>Sessão_1</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -4833,17 +4833,17 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>10-Apr-2026</t>
+          <t>14-Feb-2026</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>3918786000010005495</t>
+          <t>3918786000010039068</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -4875,7 +4875,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Sessão_7</t>
+          <t>Sessão_3</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -4890,17 +4890,17 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>27-Mar-2026</t>
+          <t>25-Mar-2026</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>3918786000009978061</t>
+          <t>3918786000010039066</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -4917,7 +4917,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -4932,7 +4932,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Sessão_7</t>
+          <t>Sessão_2</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -4947,17 +4947,17 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>25-Mar-2026</t>
+          <t>18-Apr-2026</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>3918786000009978059</t>
+          <t>3918786000010039064</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -4974,7 +4974,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -4989,7 +4989,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Sessão_6</t>
+          <t>Sessão_1</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -5004,17 +5004,17 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>25-Mar-2026</t>
+          <t>13-Feb-2026</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>3918786000009978057</t>
+          <t>3918786000010039062</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -5031,7 +5031,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Sessão_5</t>
+          <t>Sessão_4</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -5061,17 +5061,17 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>11-Mar-2026</t>
+          <t>04-Mar-2026</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>3918786000009978055</t>
+          <t>3918786000010039060</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -5088,7 +5088,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Sessão_5</t>
+          <t>Sessão_4</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -5118,17 +5118,17 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>11-Mar-2026</t>
+          <t>04-Mar-2026</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>3918786000009978053</t>
+          <t>3918786000010039058</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -5145,7 +5145,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>MUELEGE</t>
+          <t>TOPELANE</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Sessão_7</t>
+          <t>Sessão_3</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -5175,17 +5175,17 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>02-Apr-2026</t>
+          <t>25-Feb-2026</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>3918786000009978051</t>
+          <t>3918786000010039056</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -5212,17 +5212,17 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>MESEREPANE</t>
+          <t>TOPELANE</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Sessão_8</t>
+          <t>Sessão_2</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -5232,17 +5232,17 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>02-Apr-2026</t>
+          <t>18-Feb-2026</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>3918786000009975096</t>
+          <t>3918786000010039054</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -5259,7 +5259,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5269,17 +5269,17 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>RAMIANE</t>
+          <t>TOPELANE</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Sessão_6</t>
+          <t>Sessão_1</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -5289,17 +5289,17 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>02-Apr-2026</t>
+          <t>13-Feb-2026</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>3918786000009966138</t>
+          <t>3918786000010039052</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -5316,7 +5316,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5326,17 +5326,17 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>MUELEGE</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Sessão_8</t>
+          <t>Sessão_9</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -5346,7 +5346,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>01-Apr-2026</t>
+          <t>14-Apr-2026</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -5356,7 +5356,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>3918786000009966136</t>
+          <t>3918786000010039050</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -5373,7 +5373,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5383,17 +5383,17 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>MESEREPANE</t>
+          <t>TOPELANE</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Sessão_7</t>
+          <t>Sessão_10</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -5403,17 +5403,17 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>01-Apr-2026</t>
+          <t>15-Apr-2026</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>3918786000009964076</t>
+          <t>3918786000010037472</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -5430,7 +5430,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5440,17 +5440,17 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>MESEREPANE</t>
+          <t>RAMIANE</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Sessão_6</t>
+          <t>Sessão_9</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -5460,17 +5460,17 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>08-Apr-2026</t>
+          <t>14-Apr-2026</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>3918786000009964074</t>
+          <t>3918786000010037470</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -5487,7 +5487,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5497,17 +5497,17 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>MESEREPANE</t>
+          <t>RAMIANE</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Sessão_5</t>
+          <t>Sessão_8</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -5517,17 +5517,17 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>01-Apr-2026</t>
+          <t>10-Apr-2026</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>3918786000009964072</t>
+          <t>3918786000010023384</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -5544,7 +5544,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -5554,17 +5554,17 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>MESEREPANE</t>
+          <t>RAMIANE</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Sessão_4</t>
+          <t>Sessão_1</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -5574,17 +5574,17 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>01-Apr-2026</t>
+          <t>11-Feb-2026</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>3918786000009964070</t>
+          <t>3918786000010023382</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -5601,7 +5601,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -5611,17 +5611,17 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>MESEREPANE</t>
+          <t>TOPELANE</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Sessão_3</t>
+          <t>Sessão_9</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -5631,17 +5631,17 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>01-Apr-2026</t>
+          <t>08-Apr-2026</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>3918786000009964068</t>
+          <t>3918786000010023380</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -5658,7 +5658,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -5668,17 +5668,17 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>MESEREPANE</t>
+          <t>TOPELANE</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Sessão_2</t>
+          <t>Sessão_1</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -5688,17 +5688,17 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>01-Apr-2026</t>
+          <t>13-Feb-2026</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>3918786000009964066</t>
+          <t>3918786000010023378</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -5715,7 +5715,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -5725,17 +5725,17 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>MESEREPANE</t>
+          <t>RAMIANE</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Sessão_1</t>
+          <t>Sessão_7</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -5745,7 +5745,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>01-Apr-2026</t>
+          <t>09-Apr-2026</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -5755,7 +5755,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>3918786000009964064</t>
+          <t>3918786000010020060</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -5782,12 +5782,12 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>MONAPO RIO</t>
+          <t>MESEREPANE</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Sessão_8</t>
+          <t>Sessão_9</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -5802,17 +5802,17 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>31-Mar-2026</t>
+          <t>09-Apr-2026</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>3918786000009964062</t>
+          <t>3918786000010019064</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -5829,17 +5829,17 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>MATHAPUE</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -5849,32 +5849,32 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+          <t>FERNANDES LIMA &amp; TAIRAHA ESQUADRO</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>01-Apr-2026</t>
+          <t>31-Mar-2026</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>3918786000009962078</t>
+          <t>3918786000010015292</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -5886,17 +5886,17 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>MONAPO RIO</t>
+          <t>MATHAPUE</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -5906,32 +5906,32 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+          <t>FERNANDES LIMA &amp; TAIRAHA ESQUADRO</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>24-Mar-2026</t>
+          <t>31-Mar-2026</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>3918786000009962026</t>
+          <t>3918786000010015290</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -5943,17 +5943,17 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>MONAPO RIO</t>
+          <t>MATHAPUE</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -5963,32 +5963,32 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+          <t>FERNANDES LIMA &amp; TAIRAHA ESQUADRO</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>17-Mar-2026</t>
+          <t>31-Mar-2026</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>3918786000009962024</t>
+          <t>3918786000010015288</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -6000,17 +6000,17 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>MONAPO RIO</t>
+          <t>MATHAPUE</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -6020,32 +6020,32 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+          <t>FERNANDES LIMA &amp; TAIRAHA ESQUADRO</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>10-Mar-2026</t>
+          <t>31-Mar-2026</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>3918786000009962022</t>
+          <t>3918786000010015286</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -6057,17 +6057,17 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>MONAPO RIO</t>
+          <t>MATHAPUE</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -6077,32 +6077,32 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+          <t>FERNANDES LIMA &amp; TAIRAHA ESQUADRO</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>03-Mar-2026</t>
+          <t>31-Mar-2026</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>3918786000009962020</t>
+          <t>3918786000010015284</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -6114,17 +6114,17 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>MONAPO RIO</t>
+          <t>MATHAPUE</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -6134,32 +6134,32 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+          <t>FERNANDES LIMA &amp; TAIRAHA ESQUADRO</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>24-Feb-2026</t>
+          <t>31-Mar-2026</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>3918786000009962018</t>
+          <t>3918786000010015282</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -6171,17 +6171,17 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>MONAPO RIO</t>
+          <t>MATHAPUE</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -6191,32 +6191,32 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+          <t>FERNANDES LIMA &amp; TAIRAHA ESQUADRO</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>17-Feb-2026</t>
+          <t>31-Mar-2026</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>3918786000009962016</t>
+          <t>3918786000010015280</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -6228,17 +6228,17 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>MONAPO RIO</t>
+          <t>MATHAPUE</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -6248,32 +6248,32 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+          <t>FERNANDES LIMA &amp; TAIRAHA ESQUADRO</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>13-Feb-2026</t>
+          <t>31-Mar-2026</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>3918786000009962014</t>
+          <t>3918786000010015278</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -6285,7 +6285,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6295,17 +6295,17 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>RAMIANE</t>
+          <t>MONAPO RIO</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Sessão_5</t>
+          <t>Sessão_9</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -6315,17 +6315,17 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>26-Mar-2026</t>
+          <t>08-Apr-2026</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>3918786000009891291</t>
+          <t>3918786000010011002</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -6342,7 +6342,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6357,12 +6357,12 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Sessão_7</t>
+          <t>Sessão_8</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -6372,7 +6372,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>25-Mar-2026</t>
+          <t>08-Apr-2026</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -6382,7 +6382,7 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>3918786000009891287</t>
+          <t>3918786000010007188</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -6399,7 +6399,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>MUELEGE</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Sessão_6</t>
+          <t>Sessão_8</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -6429,7 +6429,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>25-Mar-2026</t>
+          <t>09-Apr-2026</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -6439,7 +6439,7 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>3918786000009888175</t>
+          <t>3918786000010007186</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -6466,12 +6466,12 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>MUELEGE</t>
+          <t>TOPELANE</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Sessão_6</t>
+          <t>Sessão_9</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -6486,17 +6486,17 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>19-Mar-2026</t>
+          <t>10-Apr-2026</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>3918786000009886133</t>
+          <t>3918786000010005495</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -6513,7 +6513,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -6523,12 +6523,12 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>MUELEGE</t>
+          <t>TOPELANE</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Sessão_5</t>
+          <t>Sessão_7</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -6543,17 +6543,17 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>12-Mar-2026</t>
+          <t>27-Mar-2026</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>3918786000009886129</t>
+          <t>3918786000009978061</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -6570,7 +6570,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Sessão_2</t>
+          <t>Sessão_7</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -6600,17 +6600,17 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>18-Feb-2026</t>
+          <t>25-Mar-2026</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>3918786000009856153</t>
+          <t>3918786000009978059</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -6627,7 +6627,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -6642,12 +6642,12 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Sessão_3</t>
+          <t>Sessão_6</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -6657,17 +6657,17 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>25-Feb-2026</t>
+          <t>25-Mar-2026</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>3918786000009856149</t>
+          <t>3918786000009978057</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -6684,7 +6684,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Sessão_4</t>
+          <t>Sessão_5</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -6714,17 +6714,17 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>04-Mar-2026</t>
+          <t>11-Mar-2026</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>3918786000009856145</t>
+          <t>3918786000009978055</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -6741,7 +6741,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -6751,17 +6751,17 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>RAMIANE</t>
+          <t>TOPELANE</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Sessão_2</t>
+          <t>Sessão_5</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -6771,17 +6771,17 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>19-Feb-2026</t>
+          <t>11-Mar-2026</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>3918786000009856141</t>
+          <t>3918786000009978053</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -6808,17 +6808,17 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>RAMIANE</t>
+          <t>MUELEGE</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Sessão_3</t>
+          <t>Sessão_7</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -6828,17 +6828,17 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>26-Feb-2026</t>
+          <t>02-Apr-2026</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>3918786000009856137</t>
+          <t>3918786000009978051</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -6855,7 +6855,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>MESEREPANE</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Sessão_5</t>
+          <t>Sessão_8</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -6885,17 +6885,17 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>11-Mar-2026</t>
+          <t>02-Apr-2026</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>3918786000009856133</t>
+          <t>3918786000009975096</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -6912,7 +6912,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -6922,7 +6922,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>RAMIANE</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -6942,17 +6942,17 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>17-Mar-2026</t>
+          <t>02-Apr-2026</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>3918786000009856129</t>
+          <t>3918786000009966138</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -6969,55 +6969,1708 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>TOPELANE</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Sessão_8</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>01-Apr-2026</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>3918786000009966136</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>MESEREPANE</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Sessão_7</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>01-Apr-2026</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>3918786000009964076</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>MESEREPANE</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Sessão_6</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>08-Apr-2026</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>3918786000009964074</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>MESEREPANE</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Sessão_5</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>01-Apr-2026</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>3918786000009964072</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>MESEREPANE</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Sessão_4</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>01-Apr-2026</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>3918786000009964070</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>MESEREPANE</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Sessão_3</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>01-Apr-2026</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>3918786000009964068</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>MESEREPANE</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Sessão_2</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>01-Apr-2026</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>3918786000009964066</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>MESEREPANE</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Sessão_1</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>01-Apr-2026</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>3918786000009964064</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>MONAPO RIO</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Sessão_8</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>31-Mar-2026</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>3918786000009964062</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>TOPELANE</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Sessão_8</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>01-Apr-2026</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>3918786000009962078</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>MONAPO RIO</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Sessão_7</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>24-Mar-2026</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>3918786000009962026</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>MONAPO RIO</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Sessão_6</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>17-Mar-2026</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>3918786000009962024</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>MONAPO RIO</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Sessão_5</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>10-Mar-2026</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>3918786000009962022</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>MONAPO RIO</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Sessão_4</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>03-Mar-2026</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>3918786000009962020</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>MONAPO RIO</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Sessão_3</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>24-Feb-2026</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>3918786000009962018</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>MONAPO RIO</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Sessão_2</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>17-Feb-2026</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>3918786000009962016</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>MONAPO RIO</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Sessão_1</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>13-Feb-2026</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>3918786000009962014</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>RAMIANE</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Sessão_5</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>26-Mar-2026</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>3918786000009891291</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>TOPELANE</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Sessão_7</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>25-Mar-2026</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>3918786000009891287</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>TOPELANE</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Sessão_6</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>25-Mar-2026</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>3918786000009888175</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>MUELEGE</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Sessão_6</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>19-Mar-2026</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>3918786000009886133</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>MUELEGE</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Sessão_5</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>12-Mar-2026</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>3918786000009886129</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>TOPELANE</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Sessão_2</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>18-Feb-2026</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>3918786000009856153</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>TOPELANE</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Sessão_3</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>25-Feb-2026</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>3918786000009856149</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>TOPELANE</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Sessão_4</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>04-Mar-2026</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>3918786000009856145</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>RAMIANE</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Sessão_2</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>19-Feb-2026</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>3918786000009856141</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>RAMIANE</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Sessão_3</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>26-Feb-2026</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>3918786000009856137</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>TOPELANE</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Sessão_5</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>11-Mar-2026</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>3918786000009856133</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>TOPELANE</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Sessão_6</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>17-Mar-2026</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>3918786000009856129</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
         <is>
           <t>RAMIANE</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr">
+      <c r="D146" t="inlineStr">
         <is>
           <t>Sessão_4</t>
         </is>
       </c>
-      <c r="E117" t="inlineStr">
+      <c r="E146" t="inlineStr">
         <is>
           <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
         </is>
       </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
         <is>
           <t>19-Mar-2026</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr">
+      <c r="H146" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="I117" t="inlineStr">
+      <c r="I146" t="inlineStr">
         <is>
           <t>3918786000009856125</t>
         </is>
       </c>
-      <c r="J117" t="inlineStr">
+      <c r="J146" t="inlineStr">
         <is>
           <t>Monapo</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr">
+      <c r="K146" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -7284,13 +8937,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{507DE559-1BBD-4FD9-A52D-329618178BBD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EB9CB245-E1FC-4C08-9999-2F16112B9993}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{979A11B2-CA46-461C-9951-5CB9DC9AF005}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3700520-80DE-4630-86FE-5C01C0F0154F}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{23568F56-5CA8-4F4C-AEBA-4E029C7FCA7C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A63D2A78-69A9-441A-A9C4-1B5A651E4760}"/>
 </file>
--- a/Qualidade_Sessoes.xlsx
+++ b/Qualidade_Sessoes.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K146"/>
+  <dimension ref="A1:K167"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -414,7 +414,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -424,7 +424,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>NAUAIA</t>
+          <t>TRIANGULO</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -449,12 +449,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3918786000010132024</t>
+          <t>3918786000010160880</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -471,7 +471,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -481,17 +481,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>NAUAIA</t>
+          <t>MURRUPELANE</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Sessão_11</t>
+          <t>Sessão_12</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>VANIL HORACIO &amp; ARMANDO ROANEQUE</t>
+          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -501,17 +501,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>21-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3918786000010132022</t>
+          <t>3918786000010152002</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -528,7 +528,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -538,42 +538,42 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>NAUAIA</t>
+          <t>MUELEGE</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Sessão_10</t>
+          <t>Sessão_12</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>VANIL HORACIO &amp; ARMANDO ROANEQUE</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>15-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3918786000010132020</t>
+          <t>3918786000010149050</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Nacala Porto</t>
+          <t>Monapo</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -585,7 +585,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -595,17 +595,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>NAUAIA</t>
+          <t>RAMIANE</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Sessão_9</t>
+          <t>Sessão_12</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>VANIL HORACIO &amp; ARMANDO ROANEQUE</t>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -615,22 +615,22 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>09-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3918786000010132018</t>
+          <t>3918786000010148062</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Nacala Porto</t>
+          <t>Monapo</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -652,17 +652,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>NAUAIA</t>
+          <t>MESEREPANE</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Sessão_8</t>
+          <t>Sessão_12</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>VANIL HORACIO &amp; ARMANDO ROANEQUE</t>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -672,22 +672,22 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>31-Mar-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3918786000010132016</t>
+          <t>3918786000010147062</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Nacala Porto</t>
+          <t>Monapo</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -699,7 +699,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -709,37 +709,37 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>NAUAIA</t>
+          <t>MOCONE</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Sessão_7</t>
+          <t>Sessão_12</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>VANIL HORACIO &amp; ARMANDO ROANEQUE</t>
+          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>24-Mar-2026</t>
+          <t>29-Apr-2026</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3918786000010132014</t>
+          <t>3918786000010141618</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -766,17 +766,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>NAUAIA</t>
+          <t>MONAPO RIO</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Sessão_6</t>
+          <t>Sessão_12</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>VANIL HORACIO &amp; ARMANDO ROANEQUE</t>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -786,22 +786,22 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>19-Mar-2026</t>
+          <t>28-Apr-2026</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3918786000010132012</t>
+          <t>3918786000010140062</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Nacala Porto</t>
+          <t>Monapo</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -813,7 +813,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -823,17 +823,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>NAUAIA</t>
+          <t>TOPELANE</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Sessão_5</t>
+          <t>Sessão_12</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>VANIL HORACIO &amp; ARMANDO ROANEQUE</t>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -843,22 +843,22 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>10-Mar-2026</t>
+          <t>29-Apr-2026</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3918786000010132010</t>
+          <t>3918786000010139064</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Nacala Porto</t>
+          <t>Monapo</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -870,7 +870,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -880,17 +880,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>NAUAIA</t>
+          <t>TOPELANE</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Sessão_4</t>
+          <t>Sessão_12</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>VANIL HORACIO &amp; ARMANDO ROANEQUE</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -900,22 +900,22 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>03-Mar-2026</t>
+          <t>29-Apr-2026</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3918786000010132008</t>
+          <t>3918786000010138146</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Nacala Porto</t>
+          <t>Monapo</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -927,7 +927,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -937,42 +937,42 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>NAUAIA</t>
+          <t>TOPELANE</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Sessão_3</t>
+          <t>Sessão_12</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>VANIL HORACIO &amp; ARMANDO ROANEQUE</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>24-Feb-2026</t>
+          <t>29-Apr-2026</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3918786000010132006</t>
+          <t>3918786000010138082</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Nacala Porto</t>
+          <t>Monapo</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -984,7 +984,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>NAUAIA</t>
+          <t>TRIANGULO</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Sessão_2</t>
+          <t>Sessão_11</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1009,22 +1009,22 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>17-Feb-2026</t>
+          <t>21-Apr-2026</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>32</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3918786000010132004</t>
+          <t>3918786000010138022</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1034,14 +1034,14 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1051,12 +1051,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>NAUAIA</t>
+          <t>TRIANGULO</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Sessão_1</t>
+          <t>Sessão_10</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1066,22 +1066,22 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>10-Feb-2026</t>
+          <t>15-Apr-2026</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3918786000010132002</t>
+          <t>3918786000010138020</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1098,7 +1098,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1108,37 +1108,37 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ONTUPAIA</t>
+          <t>TRIANGULO</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Sessão_12</t>
+          <t>Sessão_9</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>NUCHATE ESTEVAO &amp; BELITO LUCIANO</t>
+          <t>VANIL HORACIO &amp; ARMANDO ROANEQUE</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>29-Apr-2026</t>
+          <t>09-Apr-2026</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3918786000010131087</t>
+          <t>3918786000010138018</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1155,7 +1155,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1165,37 +1165,37 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>NAHERENQUE</t>
+          <t>TRIANGULO</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Sessão_12</t>
+          <t>Sessão_8</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>NUCHATE ESTEVAO &amp; BELITO LUCIANO</t>
+          <t>VANIL HORACIO &amp; ARMANDO ROANEQUE</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>28-Apr-2026</t>
+          <t>31-Mar-2026</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3918786000010126084</t>
+          <t>3918786000010138016</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1212,47 +1212,47 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>NAHERENQUE</t>
+          <t>TRIANGULO</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Sessão_11</t>
+          <t>Sessão_7</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>NUCHATE ESTEVAO &amp; BELITO LUCIANO</t>
+          <t>VANIL HORACIO &amp; ARMANDO ROANEQUE</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>21-Apr-2026</t>
+          <t>24-Mar-2026</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>35</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>3918786000010126082</t>
+          <t>3918786000010138014</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1262,54 +1262,54 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>NAHERENQUE</t>
+          <t>TRIANGULO</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Sessão_10</t>
+          <t>Sessão_6</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>NUCHATE ESTEVAO &amp; BELITO LUCIANO</t>
+          <t>VANIL HORACIO &amp; ARMANDO ROANEQUE</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>19-Apr-2026</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>35</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>3918786000010126080</t>
+          <t>3918786000010138012</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1326,7 +1326,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1336,37 +1336,37 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>NAHERENQUE</t>
+          <t>TRIANGULO</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Sessão_9</t>
+          <t>Sessão_5</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>NUCHATE ESTEVAO &amp; BELITO LUCIANO</t>
+          <t>VANIL HORACIO &amp; ARMANDO ROANEQUE</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>09-Apr-2026</t>
+          <t>10-Mar-2026</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>3918786000010126078</t>
+          <t>3918786000010138010</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1383,7 +1383,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1393,17 +1393,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>NAHERENQUE</t>
+          <t>TRIANGULO</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Sessão_8</t>
+          <t>Sessão_4</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>NUCHATE ESTEVAO &amp; BELITO LUCIANO</t>
+          <t>VANIL HORACIO &amp; ARMANDO ROANEQUE</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1413,17 +1413,17 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>31-Mar-2026</t>
+          <t>03-Mar-2026</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>3918786000010126076</t>
+          <t>3918786000010138008</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1440,7 +1440,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1450,17 +1450,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>NAHERENQUE</t>
+          <t>TRIANGULO</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Sessão_7</t>
+          <t>Sessão_3</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>NUCHATE ESTEVAO &amp; BELITO LUCIANO</t>
+          <t>VANIL HORACIO &amp; ARMANDO ROANEQUE</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1470,17 +1470,17 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>26-Mar-2026</t>
+          <t>24-Feb-2026</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>35</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>3918786000010126074</t>
+          <t>3918786000010138006</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1497,7 +1497,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1507,37 +1507,37 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>NAHERENQUE</t>
+          <t>TRIANGULO</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Sessão_6</t>
+          <t>Sessão_2</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>NUCHATE ESTEVAO &amp; BELITO LUCIANO</t>
+          <t>VANIL HORACIO &amp; ARMANDO ROANEQUE</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>17-Mar-2026</t>
+          <t>17-Feb-2026</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>3918786000010126072</t>
+          <t>3918786000010138004</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1554,7 +1554,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1564,37 +1564,37 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>NAHERENQUE</t>
+          <t>TRIANGULO</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Sessão_5</t>
+          <t>Sessão_12</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>NUCHATE ESTEVAO &amp; BELITO LUCIANO</t>
+          <t>VANIL HORACIO &amp; ARMANDO ROANEQUE</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>10-Mar-2026</t>
+          <t>10-Feb-2026</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>3918786000010126070</t>
+          <t>3918786000010138002</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1611,7 +1611,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1621,17 +1621,17 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>NAHERENQUE</t>
+          <t>NAUAIA</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Sessão_4</t>
+          <t>Sessão_12</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>NUCHATE ESTEVAO &amp; BELITO LUCIANO</t>
+          <t>VANIL HORACIO &amp; ARMANDO ROANEQUE</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1641,17 +1641,17 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>03-Mar-2026</t>
+          <t>28-Apr-2026</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>3918786000010126068</t>
+          <t>3918786000010132024</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1668,7 +1668,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1678,17 +1678,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>NAHERENQUE</t>
+          <t>NAUAIA</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Sessão_3</t>
+          <t>Sessão_11</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>NUCHATE ESTEVAO &amp; BELITO LUCIANO</t>
+          <t>VANIL HORACIO &amp; ARMANDO ROANEQUE</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1698,17 +1698,17 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>24-Feb-2026</t>
+          <t>21-Apr-2026</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>3918786000010126066</t>
+          <t>3918786000010132022</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1725,7 +1725,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1735,17 +1735,17 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>NAHERENQUE</t>
+          <t>NAUAIA</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Sessão_2</t>
+          <t>Sessão_10</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>NUCHATE ESTEVAO &amp; BELITO LUCIANO</t>
+          <t>VANIL HORACIO &amp; ARMANDO ROANEQUE</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1755,17 +1755,17 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>17-Feb-2026</t>
+          <t>15-Apr-2026</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>3918786000010126064</t>
+          <t>3918786000010132020</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1782,7 +1782,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1792,37 +1792,37 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>NAHERENQUE</t>
+          <t>NAUAIA</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Sessão_1</t>
+          <t>Sessão_9</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>NUCHATE ESTEVAO &amp; BELITO LUCIANO</t>
+          <t>VANIL HORACIO &amp; ARMANDO ROANEQUE</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>10-Feb-2026</t>
+          <t>09-Apr-2026</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>3918786000010126062</t>
+          <t>3918786000010132018</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -1849,17 +1849,17 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>MONAPO RIO</t>
+          <t>NAUAIA</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Sessão_11</t>
+          <t>Sessão_8</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+          <t>VANIL HORACIO &amp; ARMANDO ROANEQUE</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1869,22 +1869,22 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>21-Apr-2026</t>
+          <t>31-Mar-2026</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>3918786000010102118</t>
+          <t>3918786000010132016</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -1896,7 +1896,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1906,17 +1906,17 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>MATHAPUE</t>
+          <t>NAUAIA</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Sessão_11</t>
+          <t>Sessão_7</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>FERNANDES LIMA &amp; TAIRAHA ESQUADRO</t>
+          <t>VANIL HORACIO &amp; ARMANDO ROANEQUE</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1926,17 +1926,17 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>21-Apr-2026</t>
+          <t>24-Mar-2026</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>3918786000010098124</t>
+          <t>3918786000010132014</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -1953,7 +1953,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1963,17 +1963,17 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>MATHAPUE</t>
+          <t>NAUAIA</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Sessão_10</t>
+          <t>Sessão_6</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>FERNANDES LIMA &amp; TAIRAHA ESQUADRO</t>
+          <t>VANIL HORACIO &amp; ARMANDO ROANEQUE</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1983,17 +1983,17 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>21-Apr-2026</t>
+          <t>19-Mar-2026</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>3918786000010098122</t>
+          <t>3918786000010132012</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2010,7 +2010,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2020,17 +2020,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>MATHAPUE</t>
+          <t>NAUAIA</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Sessão_9</t>
+          <t>Sessão_5</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>FERNANDES LIMA &amp; TAIRAHA ESQUADRO</t>
+          <t>VANIL HORACIO &amp; ARMANDO ROANEQUE</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2040,17 +2040,17 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>21-Apr-2026</t>
+          <t>10-Mar-2026</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>3918786000010098120</t>
+          <t>3918786000010132010</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2067,7 +2067,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2077,37 +2077,37 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>MURRUPELANE</t>
+          <t>NAUAIA</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Sessão_11</t>
+          <t>Sessão_4</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
+          <t>VANIL HORACIO &amp; ARMANDO ROANEQUE</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>03-Mar-2026</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>3918786000010095084</t>
+          <t>3918786000010132008</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2124,7 +2124,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2134,37 +2134,37 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>MOCONE</t>
+          <t>NAUAIA</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Sessão_11</t>
+          <t>Sessão_3</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
+          <t>VANIL HORACIO &amp; ARMANDO ROANEQUE</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>24-Feb-2026</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>3918786000010095002</t>
+          <t>3918786000010132006</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2181,7 +2181,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2191,54 +2191,54 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>RAMIANE</t>
+          <t>NAUAIA</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Sessão_11</t>
+          <t>Sessão_2</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+          <t>VANIL HORACIO &amp; ARMANDO ROANEQUE</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>17-Feb-2026</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>3918786000010094010</t>
+          <t>3918786000010132004</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2248,37 +2248,37 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ONTUPAIA</t>
+          <t>NAUAIA</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Sessão_11</t>
+          <t>Sessão_1</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>NUCHATE ESTEVAO &amp; BELITO LUCIANO</t>
+          <t>VANIL HORACIO &amp; ARMANDO ROANEQUE</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>10-Feb-2026</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>3918786000010092104</t>
+          <t>3918786000010132002</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2295,7 +2295,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Sessão_10</t>
+          <t>Sessão_12</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2320,22 +2320,22 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>15-Apr-2026</t>
+          <t>29-Apr-2026</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>3918786000010092102</t>
+          <t>3918786000010131087</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ONTUPAIA</t>
+          <t>NAHERENQUE</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Sessão_9</t>
+          <t>Sessão_12</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>08-Apr-2026</t>
+          <t>28-Apr-2026</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>3918786000010092100</t>
+          <t>3918786000010126084</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2414,17 +2414,17 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ONTUPAIA</t>
+          <t>NAHERENQUE</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Sessão_8</t>
+          <t>Sessão_11</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2434,22 +2434,22 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>01-Apr-2026</t>
+          <t>21-Apr-2026</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>3918786000010092098</t>
+          <t>3918786000010126082</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2459,29 +2459,29 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>ONTUPAIA</t>
+          <t>NAHERENQUE</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Sessão_7</t>
+          <t>Sessão_10</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2491,22 +2491,22 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>25-Mar-2026</t>
+          <t>16-Apr-2026</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>3918786000010092096</t>
+          <t>3918786000010126080</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2523,7 +2523,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ONTUPAIA</t>
+          <t>NAHERENQUE</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Sessão_6</t>
+          <t>Sessão_9</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2548,22 +2548,22 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>18-Mar-2026</t>
+          <t>09-Apr-2026</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>3918786000010092094</t>
+          <t>3918786000010126078</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2580,7 +2580,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2590,12 +2590,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ONTUPAIA</t>
+          <t>NAHERENQUE</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Sessão_5</t>
+          <t>Sessão_8</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2610,17 +2610,17 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>11-Mar-2026</t>
+          <t>31-Mar-2026</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>3918786000010092092</t>
+          <t>3918786000010126076</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2637,7 +2637,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2647,12 +2647,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ONTUPAIA</t>
+          <t>NAHERENQUE</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Sessão_4</t>
+          <t>Sessão_7</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2667,17 +2667,17 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>04-Mar-2026</t>
+          <t>26-Mar-2026</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>3918786000010092090</t>
+          <t>3918786000010126074</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2694,7 +2694,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ONTUPAIA</t>
+          <t>NAHERENQUE</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Sessão_3</t>
+          <t>Sessão_6</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2719,22 +2719,22 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>25-Mar-2026</t>
+          <t>17-Mar-2026</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>3918786000010092088</t>
+          <t>3918786000010126072</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -2751,7 +2751,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2761,12 +2761,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>ONTUPAIA</t>
+          <t>NAHERENQUE</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Sessão_2</t>
+          <t>Sessão_5</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2781,7 +2781,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>18-Feb-2026</t>
+          <t>10-Mar-2026</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>3918786000010092086</t>
+          <t>3918786000010126070</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -2808,7 +2808,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>ONTUPAIA</t>
+          <t>NAHERENQUE</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Sessão_1</t>
+          <t>Sessão_4</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2838,17 +2838,17 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>11-Feb-2026</t>
+          <t>03-Mar-2026</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>3918786000010092084</t>
+          <t>3918786000010126068</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -2865,7 +2865,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2875,17 +2875,17 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>MUELEGE</t>
+          <t>NAHERENQUE</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Sessão_11</t>
+          <t>Sessão_3</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+          <t>NUCHATE ESTEVAO &amp; BELITO LUCIANO</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2895,22 +2895,22 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>24-Feb-2026</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>3918786000010091122</t>
+          <t>3918786000010126066</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -2922,7 +2922,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2932,17 +2932,17 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>NAHERENQUE</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Sessão_11</t>
+          <t>Sessão_2</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+          <t>NUCHATE ESTEVAO &amp; BELITO LUCIANO</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2952,22 +2952,22 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>17-Feb-2026</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>3918786000010088069</t>
+          <t>3918786000010126064</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -2979,52 +2979,52 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>NAHERENQUE</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Sessão_1</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>NUCHATE ESTEVAO &amp; BELITO LUCIANO</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>TOPELANE</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Sessão_11</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>10-Feb-2026</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>3918786000010088067</t>
+          <t>3918786000010126062</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -3036,7 +3036,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3046,7 +3046,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>MONAPO RIO</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3056,7 +3056,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -3066,7 +3066,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>21-Apr-2026</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>3918786000010087128</t>
+          <t>3918786000010102118</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3093,7 +3093,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>MESEREPANE</t>
+          <t>MATHAPUE</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3113,7 +3113,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+          <t>FERNANDES LIMA &amp; TAIRAHA ESQUADRO</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -3123,22 +3123,22 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>21-Apr-2026</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>3918786000010087064</t>
+          <t>3918786000010098124</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3150,7 +3150,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3160,7 +3160,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>MUELEGE</t>
+          <t>MATHAPUE</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+          <t>FERNANDES LIMA &amp; TAIRAHA ESQUADRO</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -3180,22 +3180,22 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>15-Apr-2026</t>
+          <t>21-Apr-2026</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>3918786000010070032</t>
+          <t>3918786000010098122</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3207,7 +3207,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3217,7 +3217,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>MATHAPUE</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+          <t>FERNANDES LIMA &amp; TAIRAHA ESQUADRO</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -3237,22 +3237,22 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>15-Apr-2026</t>
+          <t>21-Apr-2026</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>32</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>3918786000010070030</t>
+          <t>3918786000010098120</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3264,7 +3264,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3274,42 +3274,42 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>MURRUPELANE</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Sessão_10</t>
+          <t>Sessão_11</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>3918786000010069058</t>
+          <t>3918786000010095084</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3321,7 +3321,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3331,17 +3331,17 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>RAMIANE</t>
+          <t>MOCONE</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Sessão_10</t>
+          <t>Sessão_11</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -3351,22 +3351,22 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>3918786000010066060</t>
+          <t>3918786000010095002</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -3378,7 +3378,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3388,17 +3388,17 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>MOCONE</t>
+          <t>RAMIANE</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Sessão_9</t>
+          <t>Sessão_11</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -3408,22 +3408,22 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>08-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>3918786000010065072</t>
+          <t>3918786000010094010</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Nacala Porto</t>
+          <t>Monapo</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -3435,7 +3435,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3445,17 +3445,17 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>MOCONE</t>
+          <t>ONTUPAIA</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Sessão_8</t>
+          <t>Sessão_11</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
+          <t>NUCHATE ESTEVAO &amp; BELITO LUCIANO</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -3465,17 +3465,17 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>01-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>3918786000010065070</t>
+          <t>3918786000010092104</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -3492,7 +3492,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3502,37 +3502,37 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>MOCONE</t>
+          <t>ONTUPAIA</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Sessão_7</t>
+          <t>Sessão_10</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
+          <t>NUCHATE ESTEVAO &amp; BELITO LUCIANO</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>25-Mar-2026</t>
+          <t>15-Apr-2026</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>3918786000010065068</t>
+          <t>3918786000010092102</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -3549,7 +3549,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3559,37 +3559,37 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>MOCONE</t>
+          <t>ONTUPAIA</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Sessão_6</t>
+          <t>Sessão_9</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
+          <t>NUCHATE ESTEVAO &amp; BELITO LUCIANO</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>18-Mar-2026</t>
+          <t>08-Apr-2026</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>3918786000010065066</t>
+          <t>3918786000010092100</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -3606,7 +3606,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3616,17 +3616,17 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>MOCONE</t>
+          <t>ONTUPAIA</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Sessão_5</t>
+          <t>Sessão_8</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
+          <t>NUCHATE ESTEVAO &amp; BELITO LUCIANO</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -3636,17 +3636,17 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>11-Mar-2026</t>
+          <t>01-Apr-2026</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>3918786000010065064</t>
+          <t>3918786000010092098</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -3663,7 +3663,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3673,17 +3673,17 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>MOCONE</t>
+          <t>ONTUPAIA</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Sessão_4</t>
+          <t>Sessão_7</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
+          <t>NUCHATE ESTEVAO &amp; BELITO LUCIANO</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -3693,17 +3693,17 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>04-Mar-2026</t>
+          <t>25-Mar-2026</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>3918786000010065062</t>
+          <t>3918786000010092096</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -3720,7 +3720,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3730,37 +3730,37 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>MOCONE</t>
+          <t>ONTUPAIA</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Sessão_3</t>
+          <t>Sessão_6</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
+          <t>NUCHATE ESTEVAO &amp; BELITO LUCIANO</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>25-Feb-2026</t>
+          <t>18-Mar-2026</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>3918786000010065060</t>
+          <t>3918786000010092094</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -3777,7 +3777,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3787,17 +3787,17 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>MOCONE</t>
+          <t>ONTUPAIA</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Sessão_2</t>
+          <t>Sessão_5</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
+          <t>NUCHATE ESTEVAO &amp; BELITO LUCIANO</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -3807,17 +3807,17 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>18-Feb-2026</t>
+          <t>11-Mar-2026</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>3918786000010065058</t>
+          <t>3918786000010092092</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -3834,7 +3834,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3844,17 +3844,17 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>MOCONE</t>
+          <t>ONTUPAIA</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Sessão_1</t>
+          <t>Sessão_4</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
+          <t>NUCHATE ESTEVAO &amp; BELITO LUCIANO</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -3864,17 +3864,17 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>11-Feb-2026</t>
+          <t>04-Mar-2026</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>3918786000010065056</t>
+          <t>3918786000010092090</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -3884,14 +3884,14 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3901,17 +3901,17 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>MOCONE</t>
+          <t>ONTUPAIA</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Sessão_10</t>
+          <t>Sessão_3</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
+          <t>NUCHATE ESTEVAO &amp; BELITO LUCIANO</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -3921,17 +3921,17 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>15-Apr-2026</t>
+          <t>25-Mar-2026</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>3918786000010065054</t>
+          <t>3918786000010092088</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -3948,7 +3948,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3958,17 +3958,17 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>MURRUPELANE</t>
+          <t>ONTUPAIA</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Sessão_10</t>
+          <t>Sessão_2</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
+          <t>NUCHATE ESTEVAO &amp; BELITO LUCIANO</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -3978,17 +3978,17 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>14-Apr-2026</t>
+          <t>18-Feb-2026</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>3918786000010055144</t>
+          <t>3918786000010092086</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -4010,22 +4010,22 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>MURRUPELANE</t>
+          <t>ONTUPAIA</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Sessão_9</t>
+          <t>Sessão_1</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
+          <t>NUCHATE ESTEVAO &amp; BELITO LUCIANO</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -4035,17 +4035,17 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>09-Apr-2026</t>
+          <t>11-Feb-2026</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>3918786000010055142</t>
+          <t>3918786000010092084</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -4055,14 +4055,14 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4072,17 +4072,17 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>MORRUPELANE</t>
+          <t>MUELEGE</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Sessão_8</t>
+          <t>Sessão_11</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -4092,22 +4092,22 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>31-Mar-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>3918786000010055140</t>
+          <t>3918786000010091122</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Nacala Porto</t>
+          <t>Monapo</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -4119,7 +4119,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4129,17 +4129,17 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>MURRUPELANE</t>
+          <t>TOPELANE</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Sessão_7</t>
+          <t>Sessão_11</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -4149,22 +4149,22 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>24-Mar-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>3918786000010055138</t>
+          <t>3918786000010088069</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Nacala Porto</t>
+          <t>Monapo</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -4176,7 +4176,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4186,42 +4186,42 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>MURRUPELANE</t>
+          <t>TOPELANE</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Sessão_6</t>
+          <t>Sessão_11</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>17-Mar-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>3918786000010055136</t>
+          <t>3918786000010088067</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Nacala Porto</t>
+          <t>Monapo</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -4233,7 +4233,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4243,17 +4243,17 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>MURRUPELANE</t>
+          <t>TOPELANE</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Sessão_5</t>
+          <t>Sessão_11</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -4263,22 +4263,22 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>10-Mar-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>3918786000010055134</t>
+          <t>3918786000010087128</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Nacala Porto</t>
+          <t>Monapo</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -4290,7 +4290,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4300,42 +4300,42 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>MURRUPELANE</t>
+          <t>MESEREPANE</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Sessão_4</t>
+          <t>Sessão_11</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>03-Mar-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>3918786000010055132</t>
+          <t>3918786000010087064</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Nacala Porto</t>
+          <t>Monapo</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -4347,7 +4347,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4357,17 +4357,17 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>MORRUPELANE</t>
+          <t>MUELEGE</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Sessão_3</t>
+          <t>Sessão_10</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -4377,22 +4377,22 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>24-Feb-2026</t>
+          <t>15-Apr-2026</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>3918786000010055130</t>
+          <t>3918786000010070032</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Nacala Porto</t>
+          <t>Monapo</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -4404,27 +4404,27 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>MURRUPELANE</t>
+          <t>TOPELANE</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Sessão_2</t>
+          <t>Sessão_9</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -4434,22 +4434,22 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>17-Feb-2026</t>
+          <t>15-Apr-2026</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>3918786000010055128</t>
+          <t>3918786000010070030</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Nacala Porto</t>
+          <t>Monapo</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -4461,52 +4461,52 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>MURRUPELANE</t>
+          <t>TOPELANE</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Sessão_1</t>
+          <t>Sessão_10</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>10-Feb-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>3918786000010055126</t>
+          <t>3918786000010069058</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Nacala Porto</t>
+          <t>Monapo</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -4518,7 +4518,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4528,7 +4528,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>MESEREPANE</t>
+          <t>RAMIANE</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -4538,7 +4538,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -4553,12 +4553,12 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>3918786000010055064</t>
+          <t>3918786000010066060</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -4575,7 +4575,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4585,17 +4585,17 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>MONAPO RIO</t>
+          <t>MOCONE</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Sessão_10</t>
+          <t>Sessão_9</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -4605,22 +4605,22 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>14-Apr-2026</t>
+          <t>08-Apr-2026</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>3918786000010050002</t>
+          <t>3918786000010065072</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -4632,7 +4632,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -4642,17 +4642,17 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>MUELEGE</t>
+          <t>MOCONE</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Sessão_3</t>
+          <t>Sessão_8</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -4662,22 +4662,22 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>26-Feb-2026</t>
+          <t>01-Apr-2026</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>3918786000010039074</t>
+          <t>3918786000010065070</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -4689,7 +4689,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -4699,42 +4699,42 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>MUELEGE</t>
+          <t>MOCONE</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Sessão_4</t>
+          <t>Sessão_7</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>05-Mar-2026</t>
+          <t>25-Mar-2026</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>3918786000010039072</t>
+          <t>3918786000010065068</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -4746,7 +4746,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -4756,42 +4756,42 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>MUELEGE</t>
+          <t>MOCONE</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Sessão_2</t>
+          <t>Sessão_6</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>19-Feb-2026</t>
+          <t>18-Mar-2026</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>3918786000010039070</t>
+          <t>3918786000010065066</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -4803,7 +4803,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -4813,17 +4813,17 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>MUELEGE</t>
+          <t>MOCONE</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Sessão_1</t>
+          <t>Sessão_5</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -4833,22 +4833,22 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>14-Feb-2026</t>
+          <t>11-Mar-2026</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>3918786000010039068</t>
+          <t>3918786000010065064</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -4860,7 +4860,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -4870,17 +4870,17 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>MOCONE</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Sessão_3</t>
+          <t>Sessão_4</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>25-Mar-2026</t>
+          <t>04-Mar-2026</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>3918786000010039066</t>
+          <t>3918786000010065062</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -4917,7 +4917,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -4927,42 +4927,42 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>MOCONE</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Sessão_2</t>
+          <t>Sessão_3</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>18-Apr-2026</t>
+          <t>25-Feb-2026</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>3918786000010039064</t>
+          <t>3918786000010065060</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -4974,7 +4974,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -4984,17 +4984,17 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>MOCONE</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Sessão_1</t>
+          <t>Sessão_2</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -5004,22 +5004,22 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>13-Feb-2026</t>
+          <t>18-Feb-2026</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>3918786000010039062</t>
+          <t>3918786000010065058</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -5031,7 +5031,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5041,17 +5041,17 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>MOCONE</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Sessão_4</t>
+          <t>Sessão_1</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -5061,34 +5061,34 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>04-Mar-2026</t>
+          <t>11-Feb-2026</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>3918786000010039060</t>
+          <t>3918786000010065056</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5098,17 +5098,17 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>MOCONE</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Sessão_4</t>
+          <t>Sessão_10</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -5118,22 +5118,22 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>04-Mar-2026</t>
+          <t>15-Apr-2026</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>3918786000010039058</t>
+          <t>3918786000010065054</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -5145,7 +5145,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5155,17 +5155,17 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>MURRUPELANE</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Sessão_3</t>
+          <t>Sessão_10</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -5175,22 +5175,22 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>25-Feb-2026</t>
+          <t>14-Apr-2026</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>3918786000010039056</t>
+          <t>3918786000010055144</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -5202,27 +5202,27 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>MURRUPELANE</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Sessão_2</t>
+          <t>Sessão_9</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -5232,27 +5232,27 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>18-Feb-2026</t>
+          <t>09-Apr-2026</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>3918786000010039054</t>
+          <t>3918786000010055142</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -5269,17 +5269,17 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>MORRUPELANE</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Sessão_1</t>
+          <t>Sessão_8</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -5289,22 +5289,22 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>13-Feb-2026</t>
+          <t>31-Mar-2026</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>3918786000010039052</t>
+          <t>3918786000010055140</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -5316,7 +5316,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5326,17 +5326,17 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>MUELEGE</t>
+          <t>MURRUPELANE</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Sessão_9</t>
+          <t>Sessão_7</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -5346,22 +5346,22 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>14-Apr-2026</t>
+          <t>24-Mar-2026</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>3918786000010039050</t>
+          <t>3918786000010055138</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -5383,42 +5383,42 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>MURRUPELANE</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Sessão_10</t>
+          <t>Sessão_6</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>15-Apr-2026</t>
+          <t>17-Mar-2026</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>3918786000010037472</t>
+          <t>3918786000010055136</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -5430,7 +5430,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5440,17 +5440,17 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>RAMIANE</t>
+          <t>MURRUPELANE</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Sessão_9</t>
+          <t>Sessão_5</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -5460,22 +5460,22 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>14-Apr-2026</t>
+          <t>10-Mar-2026</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>3918786000010037470</t>
+          <t>3918786000010055134</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -5497,42 +5497,42 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>RAMIANE</t>
+          <t>MURRUPELANE</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Sessão_8</t>
+          <t>Sessão_4</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>10-Apr-2026</t>
+          <t>03-Mar-2026</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>3918786000010023384</t>
+          <t>3918786000010055132</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -5544,7 +5544,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -5554,17 +5554,17 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>RAMIANE</t>
+          <t>MORRUPELANE</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Sessão_1</t>
+          <t>Sessão_3</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -5574,22 +5574,22 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>11-Feb-2026</t>
+          <t>24-Feb-2026</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>3918786000010023382</t>
+          <t>3918786000010055130</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -5606,22 +5606,22 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>MURRUPELANE</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Sessão_9</t>
+          <t>Sessão_2</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -5631,22 +5631,22 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>08-Apr-2026</t>
+          <t>17-Feb-2026</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>3918786000010023380</t>
+          <t>3918786000010055128</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -5658,17 +5658,17 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>MURRUPELANE</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -5678,32 +5678,32 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>13-Feb-2026</t>
+          <t>10-Feb-2026</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>3918786000010023378</t>
+          <t>3918786000010055126</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -5715,7 +5715,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -5725,17 +5725,17 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>RAMIANE</t>
+          <t>MESEREPANE</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Sessão_7</t>
+          <t>Sessão_10</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -5745,17 +5745,17 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>09-Apr-2026</t>
+          <t>16-Apr-2026</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>3918786000010020060</t>
+          <t>3918786000010055064</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -5782,12 +5782,12 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>MESEREPANE</t>
+          <t>MONAPO RIO</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Sessão_9</t>
+          <t>Sessão_10</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -5802,17 +5802,17 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>09-Apr-2026</t>
+          <t>14-Apr-2026</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>3918786000010019064</t>
+          <t>3918786000010050002</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -5829,52 +5829,52 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>MATHAPUE</t>
+          <t>MUELEGE</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Sessão_8</t>
+          <t>Sessão_3</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>FERNANDES LIMA &amp; TAIRAHA ESQUADRO</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>31-Mar-2026</t>
+          <t>26-Feb-2026</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>3918786000010015292</t>
+          <t>3918786000010039074</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>Nacala Porto</t>
+          <t>Monapo</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -5886,52 +5886,52 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>MATHAPUE</t>
+          <t>MUELEGE</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Sessão_7</t>
+          <t>Sessão_4</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>FERNANDES LIMA &amp; TAIRAHA ESQUADRO</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>31-Mar-2026</t>
+          <t>05-Mar-2026</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>3918786000010015290</t>
+          <t>3918786000010039072</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>Nacala Porto</t>
+          <t>Monapo</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -5943,52 +5943,52 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>MATHAPUE</t>
+          <t>MUELEGE</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Sessão_6</t>
+          <t>Sessão_2</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>FERNANDES LIMA &amp; TAIRAHA ESQUADRO</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>31-Mar-2026</t>
+          <t>19-Feb-2026</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>3918786000010015288</t>
+          <t>3918786000010039070</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>Nacala Porto</t>
+          <t>Monapo</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -6000,52 +6000,52 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>MATHAPUE</t>
+          <t>MUELEGE</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Sessão_5</t>
+          <t>Sessão_1</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>FERNANDES LIMA &amp; TAIRAHA ESQUADRO</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>14-Feb-2026</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>31-Mar-2026</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>3918786000010015286</t>
+          <t>3918786000010039068</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>Nacala Porto</t>
+          <t>Monapo</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -6057,52 +6057,52 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>MATHAPUE</t>
+          <t>TOPELANE</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Sessão_4</t>
+          <t>Sessão_3</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>FERNANDES LIMA &amp; TAIRAHA ESQUADRO</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>31-Mar-2026</t>
+          <t>25-Mar-2026</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>3918786000010015284</t>
+          <t>3918786000010039066</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>Nacala Porto</t>
+          <t>Monapo</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -6114,52 +6114,52 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>MATHAPUE</t>
+          <t>TOPELANE</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Sessão_3</t>
+          <t>Sessão_2</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>FERNANDES LIMA &amp; TAIRAHA ESQUADRO</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>31-Mar-2026</t>
+          <t>18-Apr-2026</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>3918786000010015282</t>
+          <t>3918786000010039064</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>Nacala Porto</t>
+          <t>Monapo</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -6171,37 +6171,37 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>MATHAPUE</t>
+          <t>TOPELANE</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Sessão_2</t>
+          <t>Sessão_1</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>FERNANDES LIMA &amp; TAIRAHA ESQUADRO</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>31-Mar-2026</t>
+          <t>13-Feb-2026</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -6211,12 +6211,12 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>3918786000010015280</t>
+          <t>3918786000010039062</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>Nacala Porto</t>
+          <t>Monapo</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -6228,52 +6228,52 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>MATHAPUE</t>
+          <t>TOPELANE</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Sessão_1</t>
+          <t>Sessão_4</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>FERNANDES LIMA &amp; TAIRAHA ESQUADRO</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>31-Mar-2026</t>
+          <t>04-Mar-2026</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>3918786000010015278</t>
+          <t>3918786000010039060</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>Nacala Porto</t>
+          <t>Monapo</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -6295,17 +6295,17 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>MONAPO RIO</t>
+          <t>TOPELANE</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Sessão_9</t>
+          <t>Sessão_4</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -6315,17 +6315,17 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>08-Apr-2026</t>
+          <t>04-Mar-2026</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>3918786000010011002</t>
+          <t>3918786000010039058</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -6342,7 +6342,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6357,7 +6357,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Sessão_8</t>
+          <t>Sessão_3</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -6372,17 +6372,17 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>08-Apr-2026</t>
+          <t>25-Feb-2026</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>3918786000010007188</t>
+          <t>3918786000010039056</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>MUELEGE</t>
+          <t>TOPELANE</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Sessão_8</t>
+          <t>Sessão_2</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -6429,17 +6429,17 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>09-Apr-2026</t>
+          <t>18-Feb-2026</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>3918786000010007186</t>
+          <t>3918786000010039054</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -6456,7 +6456,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -6471,7 +6471,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Sessão_9</t>
+          <t>Sessão_1</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -6486,17 +6486,17 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>10-Apr-2026</t>
+          <t>13-Feb-2026</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>3918786000010005495</t>
+          <t>3918786000010039052</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -6523,12 +6523,12 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>MUELEGE</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Sessão_7</t>
+          <t>Sessão_9</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -6543,17 +6543,17 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>27-Mar-2026</t>
+          <t>14-Apr-2026</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>3918786000009978061</t>
+          <t>3918786000010039050</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -6570,7 +6570,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Sessão_7</t>
+          <t>Sessão_10</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -6600,17 +6600,17 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>25-Mar-2026</t>
+          <t>15-Apr-2026</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>3918786000009978059</t>
+          <t>3918786000010037472</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -6627,7 +6627,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -6637,17 +6637,17 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>RAMIANE</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Sessão_6</t>
+          <t>Sessão_9</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -6657,17 +6657,17 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>25-Mar-2026</t>
+          <t>14-Apr-2026</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>3918786000009978057</t>
+          <t>3918786000010037470</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -6694,17 +6694,17 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>RAMIANE</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Sessão_5</t>
+          <t>Sessão_8</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -6714,17 +6714,17 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>11-Mar-2026</t>
+          <t>10-Apr-2026</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>3918786000009978055</t>
+          <t>3918786000010023384</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -6741,7 +6741,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -6751,17 +6751,17 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>RAMIANE</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Sessão_5</t>
+          <t>Sessão_1</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -6771,17 +6771,17 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>11-Mar-2026</t>
+          <t>11-Feb-2026</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>3918786000009978053</t>
+          <t>3918786000010023382</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -6798,7 +6798,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -6808,17 +6808,17 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>MUELEGE</t>
+          <t>TOPELANE</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Sessão_7</t>
+          <t>Sessão_9</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -6828,17 +6828,17 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>02-Apr-2026</t>
+          <t>08-Apr-2026</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>3918786000009978051</t>
+          <t>3918786000010023380</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -6855,7 +6855,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>MESEREPANE</t>
+          <t>TOPELANE</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Sessão_8</t>
+          <t>Sessão_1</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -6885,17 +6885,17 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>02-Apr-2026</t>
+          <t>13-Feb-2026</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>3918786000009975096</t>
+          <t>3918786000010023378</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -6912,7 +6912,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Sessão_6</t>
+          <t>Sessão_7</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -6942,17 +6942,17 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>02-Apr-2026</t>
+          <t>09-Apr-2026</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>3918786000009966138</t>
+          <t>3918786000010020060</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -6969,7 +6969,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -6979,17 +6979,17 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>MESEREPANE</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Sessão_8</t>
+          <t>Sessão_9</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -6999,17 +6999,17 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>01-Apr-2026</t>
+          <t>09-Apr-2026</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>3918786000009966136</t>
+          <t>3918786000010019064</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -7026,52 +7026,52 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>MESEREPANE</t>
+          <t>MATHAPUE</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Sessão_7</t>
+          <t>Sessão_8</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+          <t>FERNANDES LIMA &amp; TAIRAHA ESQUADRO</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>01-Apr-2026</t>
+          <t>31-Mar-2026</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>3918786000009964076</t>
+          <t>3918786000010015292</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -7083,52 +7083,52 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>MESEREPANE</t>
+          <t>MATHAPUE</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Sessão_6</t>
+          <t>Sessão_7</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+          <t>FERNANDES LIMA &amp; TAIRAHA ESQUADRO</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>08-Apr-2026</t>
+          <t>31-Mar-2026</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>3918786000009964074</t>
+          <t>3918786000010015290</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
@@ -7140,52 +7140,52 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>MESEREPANE</t>
+          <t>MATHAPUE</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Sessão_5</t>
+          <t>Sessão_6</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+          <t>FERNANDES LIMA &amp; TAIRAHA ESQUADRO</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>01-Apr-2026</t>
+          <t>31-Mar-2026</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>3918786000009964072</t>
+          <t>3918786000010015288</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -7197,52 +7197,52 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>MESEREPANE</t>
+          <t>MATHAPUE</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Sessão_4</t>
+          <t>Sessão_5</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+          <t>FERNANDES LIMA &amp; TAIRAHA ESQUADRO</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>01-Apr-2026</t>
+          <t>31-Mar-2026</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>3918786000009964070</t>
+          <t>3918786000010015286</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
@@ -7254,52 +7254,52 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>MESEREPANE</t>
+          <t>MATHAPUE</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Sessão_3</t>
+          <t>Sessão_4</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+          <t>FERNANDES LIMA &amp; TAIRAHA ESQUADRO</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>01-Apr-2026</t>
+          <t>31-Mar-2026</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>3918786000009964068</t>
+          <t>3918786000010015284</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
@@ -7311,52 +7311,52 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>MESEREPANE</t>
+          <t>MATHAPUE</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Sessão_2</t>
+          <t>Sessão_3</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+          <t>FERNANDES LIMA &amp; TAIRAHA ESQUADRO</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>01-Apr-2026</t>
+          <t>31-Mar-2026</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>3918786000009964066</t>
+          <t>3918786000010015282</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -7373,47 +7373,47 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>MESEREPANE</t>
+          <t>MATHAPUE</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Sessão_1</t>
+          <t>Sessão_2</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+          <t>FERNANDES LIMA &amp; TAIRAHA ESQUADRO</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>01-Apr-2026</t>
+          <t>31-Mar-2026</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>3918786000009964064</t>
+          <t>3918786000010015280</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -7425,32 +7425,32 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>MONAPO RIO</t>
+          <t>MATHAPUE</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Sessão_8</t>
+          <t>Sessão_1</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+          <t>FERNANDES LIMA &amp; TAIRAHA ESQUADRO</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -7460,17 +7460,17 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>3918786000009964062</t>
+          <t>3918786000010015278</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
@@ -7482,7 +7482,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -7492,17 +7492,17 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>MONAPO RIO</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Sessão_8</t>
+          <t>Sessão_9</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -7512,17 +7512,17 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>01-Apr-2026</t>
+          <t>08-Apr-2026</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>3918786000009962078</t>
+          <t>3918786000010011002</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -7539,7 +7539,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -7549,17 +7549,17 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>MONAPO RIO</t>
+          <t>TOPELANE</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Sessão_7</t>
+          <t>Sessão_8</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -7569,17 +7569,17 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>24-Mar-2026</t>
+          <t>08-Apr-2026</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>3918786000009962026</t>
+          <t>3918786000010007188</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -7606,17 +7606,17 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>MONAPO RIO</t>
+          <t>MUELEGE</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Sessão_6</t>
+          <t>Sessão_8</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -7626,17 +7626,17 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>17-Mar-2026</t>
+          <t>09-Apr-2026</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>3918786000009962024</t>
+          <t>3918786000010007186</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -7653,7 +7653,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -7663,17 +7663,17 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>MONAPO RIO</t>
+          <t>TOPELANE</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Sessão_5</t>
+          <t>Sessão_9</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -7683,17 +7683,17 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>10-Mar-2026</t>
+          <t>10-Apr-2026</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>3918786000009962022</t>
+          <t>3918786000010005495</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -7720,17 +7720,17 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>MONAPO RIO</t>
+          <t>TOPELANE</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Sessão_4</t>
+          <t>Sessão_7</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -7740,17 +7740,17 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>03-Mar-2026</t>
+          <t>27-Mar-2026</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>3918786000009962020</t>
+          <t>3918786000009978061</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -7767,7 +7767,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -7777,17 +7777,17 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>MONAPO RIO</t>
+          <t>TOPELANE</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Sessão_3</t>
+          <t>Sessão_7</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -7797,17 +7797,17 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>24-Feb-2026</t>
+          <t>25-Mar-2026</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>3918786000009962018</t>
+          <t>3918786000009978059</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
@@ -7824,7 +7824,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -7834,17 +7834,17 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>MONAPO RIO</t>
+          <t>TOPELANE</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Sessão_2</t>
+          <t>Sessão_6</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -7854,17 +7854,17 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>17-Feb-2026</t>
+          <t>25-Mar-2026</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>3918786000009962016</t>
+          <t>3918786000009978057</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -7881,7 +7881,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -7891,17 +7891,17 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>MONAPO RIO</t>
+          <t>TOPELANE</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Sessão_1</t>
+          <t>Sessão_5</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -7911,17 +7911,17 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>13-Feb-2026</t>
+          <t>11-Mar-2026</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>3918786000009962014</t>
+          <t>3918786000009978055</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -7938,7 +7938,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -7948,7 +7948,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>RAMIANE</t>
+          <t>TOPELANE</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -7958,7 +7958,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -7968,17 +7968,17 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>26-Mar-2026</t>
+          <t>11-Mar-2026</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>3918786000009891291</t>
+          <t>3918786000009978053</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -7995,7 +7995,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -8005,7 +8005,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>MUELEGE</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -8015,7 +8015,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -8025,17 +8025,17 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>25-Mar-2026</t>
+          <t>02-Apr-2026</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>3918786000009891287</t>
+          <t>3918786000009978051</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -8052,7 +8052,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -8062,17 +8062,17 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>MESEREPANE</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Sessão_6</t>
+          <t>Sessão_8</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -8082,17 +8082,17 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>25-Mar-2026</t>
+          <t>02-Apr-2026</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>3918786000009888175</t>
+          <t>3918786000009975096</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -8109,7 +8109,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -8119,7 +8119,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>MUELEGE</t>
+          <t>RAMIANE</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -8129,7 +8129,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -8139,17 +8139,17 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>19-Mar-2026</t>
+          <t>02-Apr-2026</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>3918786000009886133</t>
+          <t>3918786000009966138</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -8166,7 +8166,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -8176,17 +8176,17 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>MUELEGE</t>
+          <t>TOPELANE</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Sessão_5</t>
+          <t>Sessão_8</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -8196,17 +8196,17 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>12-Mar-2026</t>
+          <t>01-Apr-2026</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>3918786000009886129</t>
+          <t>3918786000009966136</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -8223,7 +8223,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -8233,17 +8233,17 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>MESEREPANE</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Sessão_2</t>
+          <t>Sessão_7</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -8253,17 +8253,17 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>18-Feb-2026</t>
+          <t>01-Apr-2026</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>3918786000009856153</t>
+          <t>3918786000009964076</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -8280,7 +8280,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -8290,17 +8290,17 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>MESEREPANE</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Sessão_3</t>
+          <t>Sessão_6</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -8310,17 +8310,17 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>25-Feb-2026</t>
+          <t>08-Apr-2026</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>3918786000009856149</t>
+          <t>3918786000009964074</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -8337,7 +8337,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -8347,17 +8347,17 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>MESEREPANE</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Sessão_4</t>
+          <t>Sessão_5</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -8367,17 +8367,17 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>04-Mar-2026</t>
+          <t>01-Apr-2026</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>3918786000009856145</t>
+          <t>3918786000009964072</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -8394,7 +8394,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -8404,17 +8404,17 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>RAMIANE</t>
+          <t>MESEREPANE</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Sessão_2</t>
+          <t>Sessão_4</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -8424,17 +8424,17 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>19-Feb-2026</t>
+          <t>01-Apr-2026</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>3918786000009856141</t>
+          <t>3918786000009964070</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -8451,7 +8451,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -8461,7 +8461,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>RAMIANE</t>
+          <t>MESEREPANE</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -8471,7 +8471,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -8481,17 +8481,17 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>26-Feb-2026</t>
+          <t>01-Apr-2026</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>3918786000009856137</t>
+          <t>3918786000009964068</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -8508,7 +8508,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -8518,17 +8518,17 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>MESEREPANE</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Sessão_5</t>
+          <t>Sessão_2</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -8538,17 +8538,17 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>11-Mar-2026</t>
+          <t>01-Apr-2026</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>3918786000009856133</t>
+          <t>3918786000009964066</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -8565,7 +8565,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -8575,17 +8575,17 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>MESEREPANE</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Sessão_6</t>
+          <t>Sessão_1</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -8595,17 +8595,17 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>17-Mar-2026</t>
+          <t>01-Apr-2026</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>3918786000009856129</t>
+          <t>3918786000009964064</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -8622,55 +8622,1252 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>MONAPO RIO</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Sessão_8</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>31-Mar-2026</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>3918786000009964062</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>TOPELANE</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Sessão_8</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>01-Apr-2026</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>3918786000009962078</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>MONAPO RIO</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Sessão_7</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>24-Mar-2026</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>3918786000009962026</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>MONAPO RIO</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Sessão_6</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>17-Mar-2026</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>3918786000009962024</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>MONAPO RIO</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Sessão_5</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>10-Mar-2026</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>3918786000009962022</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>MONAPO RIO</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Sessão_4</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>03-Mar-2026</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>3918786000009962020</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>MONAPO RIO</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Sessão_3</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>24-Feb-2026</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>3918786000009962018</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>MONAPO RIO</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Sessão_2</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>17-Feb-2026</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>3918786000009962016</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>MONAPO RIO</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Sessão_1</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>13-Feb-2026</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>3918786000009962014</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>RAMIANE</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Sessão_5</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>26-Mar-2026</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>3918786000009891291</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>TOPELANE</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Sessão_7</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>25-Mar-2026</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>3918786000009891287</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>TOPELANE</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Sessão_6</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>25-Mar-2026</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>3918786000009888175</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>MUELEGE</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Sessão_6</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>19-Mar-2026</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>3918786000009886133</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>MUELEGE</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Sessão_5</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>12-Mar-2026</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>3918786000009886129</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>TOPELANE</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Sessão_2</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>18-Feb-2026</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>3918786000009856153</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>TOPELANE</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Sessão_3</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>25-Feb-2026</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>3918786000009856149</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>TOPELANE</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Sessão_4</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>04-Mar-2026</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>3918786000009856145</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>RAMIANE</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Sessão_2</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>19-Feb-2026</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>3918786000009856141</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>RAMIANE</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Sessão_3</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>26-Feb-2026</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>3918786000009856137</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>TOPELANE</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Sessão_5</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>11-Mar-2026</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>3918786000009856133</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>TOPELANE</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Sessão_6</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>17-Mar-2026</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>3918786000009856129</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
         <is>
           <t>RAMIANE</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr">
+      <c r="D167" t="inlineStr">
         <is>
           <t>Sessão_4</t>
         </is>
       </c>
-      <c r="E146" t="inlineStr">
+      <c r="E167" t="inlineStr">
         <is>
           <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
         </is>
       </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
         <is>
           <t>19-Mar-2026</t>
         </is>
       </c>
-      <c r="H146" t="inlineStr">
+      <c r="H167" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="I146" t="inlineStr">
+      <c r="I167" t="inlineStr">
         <is>
           <t>3918786000009856125</t>
         </is>
       </c>
-      <c r="J146" t="inlineStr">
+      <c r="J167" t="inlineStr">
         <is>
           <t>Monapo</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr">
+      <c r="K167" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -8679,271 +9876,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100DC8BB5B596CFDD4794B3344F0E8F53A4" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="481cb719fb2f51215cc00c8d40533043">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="20d57abc-823c-4051-a81a-1a0a01a8f39e" xmlns:ns3="54c5ab46-7543-4aba-b0fa-79d6a199bef5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="71df0815368817fe9627576b1e062219" ns2:_="" ns3:_="">
-    <xsd:import namespace="20d57abc-823c-4051-a81a-1a0a01a8f39e"/>
-    <xsd:import namespace="54c5ab46-7543-4aba-b0fa-79d6a199bef5"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="20d57abc-823c-4051-a81a-1a0a01a8f39e" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="16" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="17" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="19" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="edc6e55a-975c-4e83-894d-449406ca2714" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="21" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="22" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="54c5ab46-7543-4aba-b0fa-79d6a199bef5" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="12" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="13" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="20" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{21a739d7-e82a-41d6-a891-a689fdcdcba6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="54c5ab46-7543-4aba-b0fa-79d6a199bef5">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="54c5ab46-7543-4aba-b0fa-79d6a199bef5" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="20d57abc-823c-4051-a81a-1a0a01a8f39e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EB9CB245-E1FC-4C08-9999-2F16112B9993}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3700520-80DE-4630-86FE-5C01C0F0154F}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A63D2A78-69A9-441A-A9C4-1B5A651E4760}"/>
 </file>
--- a/Qualidade_Sessoes.xlsx
+++ b/Qualidade_Sessoes.xlsx
@@ -9876,4 +9876,271 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100DC8BB5B596CFDD4794B3344F0E8F53A4" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="481cb719fb2f51215cc00c8d40533043">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="20d57abc-823c-4051-a81a-1a0a01a8f39e" xmlns:ns3="54c5ab46-7543-4aba-b0fa-79d6a199bef5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="71df0815368817fe9627576b1e062219" ns2:_="" ns3:_="">
+    <xsd:import namespace="20d57abc-823c-4051-a81a-1a0a01a8f39e"/>
+    <xsd:import namespace="54c5ab46-7543-4aba-b0fa-79d6a199bef5"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="20d57abc-823c-4051-a81a-1a0a01a8f39e" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="16" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="17" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="19" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="edc6e55a-975c-4e83-894d-449406ca2714" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="21" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="22" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="54c5ab46-7543-4aba-b0fa-79d6a199bef5" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="12" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="13" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="20" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{21a739d7-e82a-41d6-a891-a689fdcdcba6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="54c5ab46-7543-4aba-b0fa-79d6a199bef5">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="54c5ab46-7543-4aba-b0fa-79d6a199bef5" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="20d57abc-823c-4051-a81a-1a0a01a8f39e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4B4200DC-FCE5-4054-A69F-C214589C833C}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5A7E49F4-0F06-4A31-B05F-84A8235AF667}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6891425A-5736-4BB5-AC64-DEB39513C3E9}"/>
 </file>
--- a/Qualidade_Sessoes.xlsx
+++ b/Qualidade_Sessoes.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K167"/>
+  <dimension ref="A1:K170"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -414,7 +414,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -424,17 +424,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>TRIANGULO</t>
+          <t>MOCONE</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Sessão_12</t>
+          <t>Sessão_9</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>VANIL HORACIO &amp; ARMANDO ROANEQUE</t>
+          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -444,17 +444,17 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>28-Apr-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3918786000010160880</t>
+          <t>3918786000010201002</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -486,7 +486,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Sessão_12</t>
+          <t>Sessão_10</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -501,17 +501,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>05-May-2026</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3918786000010152002</t>
+          <t>3918786000010198056</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -528,7 +528,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -538,42 +538,42 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MUELEGE</t>
+          <t>MURRUPELANE</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Sessão_12</t>
+          <t>Sessão_9</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>07-May-2026</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3918786000010149050</t>
+          <t>3918786000010195005</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -585,7 +585,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -595,7 +595,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>RAMIANE</t>
+          <t>TRIANGULO</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -605,7 +605,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+          <t>VANIL HORACIO &amp; ARMANDO ROANEQUE</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -615,22 +615,22 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>28-Apr-2026</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3918786000010148062</t>
+          <t>3918786000010160880</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -642,7 +642,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -652,7 +652,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MESEREPANE</t>
+          <t>MURRUPELANE</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -662,7 +662,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -677,17 +677,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3918786000010147062</t>
+          <t>3918786000010152002</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -699,7 +699,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MOCONE</t>
+          <t>MUELEGE</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -719,32 +719,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>29-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3918786000010141618</t>
+          <t>3918786000010149050</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Nacala Porto</t>
+          <t>Monapo</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -756,7 +756,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -766,7 +766,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MONAPO RIO</t>
+          <t>RAMIANE</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -786,17 +786,17 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>28-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3918786000010140062</t>
+          <t>3918786000010148062</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -813,7 +813,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>MESEREPANE</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -833,7 +833,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -843,17 +843,17 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>29-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3918786000010139064</t>
+          <t>3918786000010147062</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -870,7 +870,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>MOCONE</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -905,17 +905,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3918786000010138146</t>
+          <t>3918786000010141618</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>MONAPO RIO</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -957,17 +957,17 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>29-Apr-2026</t>
+          <t>28-Apr-2026</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3918786000010138082</t>
+          <t>3918786000010140062</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -984,7 +984,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -994,17 +994,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>TRIANGULO</t>
+          <t>TOPELANE</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Sessão_11</t>
+          <t>Sessão_12</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>VANIL HORACIO &amp; ARMANDO ROANEQUE</t>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1014,22 +1014,22 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>21-Apr-2026</t>
+          <t>29-Apr-2026</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3918786000010138022</t>
+          <t>3918786000010139064</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Nacala Porto</t>
+          <t>Monapo</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1041,7 +1041,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1051,17 +1051,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>TRIANGULO</t>
+          <t>TOPELANE</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Sessão_10</t>
+          <t>Sessão_12</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>VANIL HORACIO &amp; ARMANDO ROANEQUE</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1071,22 +1071,22 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>15-Apr-2026</t>
+          <t>29-Apr-2026</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3918786000010138020</t>
+          <t>3918786000010138146</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Nacala Porto</t>
+          <t>Monapo</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1108,17 +1108,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>TRIANGULO</t>
+          <t>TOPELANE</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Sessão_9</t>
+          <t>Sessão_12</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>VANIL HORACIO &amp; ARMANDO ROANEQUE</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1128,22 +1128,22 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>09-Apr-2026</t>
+          <t>29-Apr-2026</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3918786000010138018</t>
+          <t>3918786000010138082</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Nacala Porto</t>
+          <t>Monapo</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Sessão_8</t>
+          <t>Sessão_11</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1185,17 +1185,17 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>31-Mar-2026</t>
+          <t>21-Apr-2026</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>32</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3918786000010138016</t>
+          <t>3918786000010138022</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Sessão_7</t>
+          <t>Sessão_10</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1242,17 +1242,17 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>24-Mar-2026</t>
+          <t>15-Apr-2026</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>3918786000010138014</t>
+          <t>3918786000010138020</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Sessão_6</t>
+          <t>Sessão_9</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1299,17 +1299,17 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>19-Apr-2026</t>
+          <t>09-Apr-2026</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>3918786000010138012</t>
+          <t>3918786000010138018</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1326,7 +1326,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Sessão_5</t>
+          <t>Sessão_8</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1356,17 +1356,17 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>10-Mar-2026</t>
+          <t>31-Mar-2026</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>3918786000010138010</t>
+          <t>3918786000010138016</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Sessão_4</t>
+          <t>Sessão_7</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1413,17 +1413,17 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>03-Mar-2026</t>
+          <t>24-Mar-2026</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>35</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>3918786000010138008</t>
+          <t>3918786000010138014</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1440,7 +1440,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Sessão_3</t>
+          <t>Sessão_6</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>24-Feb-2026</t>
+          <t>19-Apr-2026</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>3918786000010138006</t>
+          <t>3918786000010138012</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1497,7 +1497,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1512,7 +1512,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Sessão_2</t>
+          <t>Sessão_5</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1527,17 +1527,17 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>17-Feb-2026</t>
+          <t>10-Mar-2026</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>3918786000010138004</t>
+          <t>3918786000010138010</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1554,7 +1554,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1569,7 +1569,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Sessão_12</t>
+          <t>Sessão_4</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1579,22 +1579,22 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>10-Feb-2026</t>
+          <t>03-Mar-2026</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>3918786000010138002</t>
+          <t>3918786000010138008</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1611,7 +1611,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1621,12 +1621,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>NAUAIA</t>
+          <t>TRIANGULO</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Sessão_12</t>
+          <t>Sessão_3</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1641,17 +1641,17 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>28-Apr-2026</t>
+          <t>24-Feb-2026</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>35</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>3918786000010132024</t>
+          <t>3918786000010138006</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1668,7 +1668,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1678,12 +1678,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>NAUAIA</t>
+          <t>TRIANGULO</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Sessão_11</t>
+          <t>Sessão_2</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1698,17 +1698,17 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>21-Apr-2026</t>
+          <t>17-Feb-2026</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>3918786000010132022</t>
+          <t>3918786000010138004</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1725,7 +1725,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1735,12 +1735,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>NAUAIA</t>
+          <t>TRIANGULO</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Sessão_10</t>
+          <t>Sessão_12</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1750,22 +1750,22 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>15-Apr-2026</t>
+          <t>10-Feb-2026</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>3918786000010132020</t>
+          <t>3918786000010138002</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1782,7 +1782,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Sessão_9</t>
+          <t>Sessão_12</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1812,17 +1812,17 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>09-Apr-2026</t>
+          <t>28-Apr-2026</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>3918786000010132018</t>
+          <t>3918786000010132024</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Sessão_8</t>
+          <t>Sessão_11</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1869,17 +1869,17 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>31-Mar-2026</t>
+          <t>21-Apr-2026</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>3918786000010132016</t>
+          <t>3918786000010132022</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -1896,7 +1896,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Sessão_7</t>
+          <t>Sessão_10</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1926,17 +1926,17 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>24-Mar-2026</t>
+          <t>15-Apr-2026</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>3918786000010132014</t>
+          <t>3918786000010132020</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -1953,7 +1953,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1968,7 +1968,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Sessão_6</t>
+          <t>Sessão_9</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1983,17 +1983,17 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>19-Mar-2026</t>
+          <t>09-Apr-2026</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>3918786000010132012</t>
+          <t>3918786000010132018</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2010,7 +2010,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2025,7 +2025,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Sessão_5</t>
+          <t>Sessão_8</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2040,17 +2040,17 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>10-Mar-2026</t>
+          <t>31-Mar-2026</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>3918786000010132010</t>
+          <t>3918786000010132016</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2067,7 +2067,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2082,7 +2082,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Sessão_4</t>
+          <t>Sessão_7</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2097,17 +2097,17 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>03-Mar-2026</t>
+          <t>24-Mar-2026</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>3918786000010132008</t>
+          <t>3918786000010132014</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2124,7 +2124,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Sessão_3</t>
+          <t>Sessão_6</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2149,22 +2149,22 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>24-Feb-2026</t>
+          <t>19-Mar-2026</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>3918786000010132006</t>
+          <t>3918786000010132012</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2181,7 +2181,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Sessão_2</t>
+          <t>Sessão_5</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2206,22 +2206,22 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>17-Feb-2026</t>
+          <t>10-Mar-2026</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>3918786000010132004</t>
+          <t>3918786000010132010</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2231,14 +2231,14 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Sessão_1</t>
+          <t>Sessão_4</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2263,22 +2263,22 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>10-Feb-2026</t>
+          <t>03-Mar-2026</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>3918786000010132002</t>
+          <t>3918786000010132008</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2295,7 +2295,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2305,17 +2305,17 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>ONTUPAIA</t>
+          <t>NAUAIA</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Sessão_12</t>
+          <t>Sessão_3</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>NUCHATE ESTEVAO &amp; BELITO LUCIANO</t>
+          <t>VANIL HORACIO &amp; ARMANDO ROANEQUE</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2325,17 +2325,17 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>29-Apr-2026</t>
+          <t>24-Feb-2026</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>3918786000010131087</t>
+          <t>3918786000010132006</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2352,7 +2352,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2362,17 +2362,17 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>NAHERENQUE</t>
+          <t>NAUAIA</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Sessão_12</t>
+          <t>Sessão_2</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>NUCHATE ESTEVAO &amp; BELITO LUCIANO</t>
+          <t>VANIL HORACIO &amp; ARMANDO ROANEQUE</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>28-Apr-2026</t>
+          <t>17-Feb-2026</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>3918786000010126084</t>
+          <t>3918786000010132004</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2402,54 +2402,54 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>NAUAIA</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Sessão_1</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>VANIL HORACIO &amp; ARMANDO ROANEQUE</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>NAHERENQUE</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Sessão_11</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>NUCHATE ESTEVAO &amp; BELITO LUCIANO</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>21-Apr-2026</t>
+          <t>10-Feb-2026</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>3918786000010126082</t>
+          <t>3918786000010132002</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2459,29 +2459,29 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>NAHERENQUE</t>
+          <t>ONTUPAIA</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Sessão_10</t>
+          <t>Sessão_12</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2491,22 +2491,22 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>29-Apr-2026</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>3918786000010126080</t>
+          <t>3918786000010131087</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2523,7 +2523,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Sessão_9</t>
+          <t>Sessão_12</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2548,22 +2548,22 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>09-Apr-2026</t>
+          <t>28-Apr-2026</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>3918786000010126078</t>
+          <t>3918786000010126084</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2580,47 +2580,47 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>NAHERENQUE</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Sessão_11</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>NUCHATE ESTEVAO &amp; BELITO LUCIANO</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>NAHERENQUE</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Sessão_8</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>NUCHATE ESTEVAO &amp; BELITO LUCIANO</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>31-Mar-2026</t>
+          <t>21-Apr-2026</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>3918786000010126076</t>
+          <t>3918786000010126082</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2630,19 +2630,19 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2652,7 +2652,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Sessão_7</t>
+          <t>Sessão_10</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2662,22 +2662,22 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>26-Mar-2026</t>
+          <t>16-Apr-2026</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>3918786000010126074</t>
+          <t>3918786000010126080</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2694,7 +2694,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2709,7 +2709,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Sessão_6</t>
+          <t>Sessão_9</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2719,22 +2719,22 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>17-Mar-2026</t>
+          <t>09-Apr-2026</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>3918786000010126072</t>
+          <t>3918786000010126078</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -2751,7 +2751,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2766,7 +2766,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Sessão_5</t>
+          <t>Sessão_8</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2781,17 +2781,17 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>10-Mar-2026</t>
+          <t>31-Mar-2026</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>3918786000010126070</t>
+          <t>3918786000010126076</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -2808,7 +2808,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2823,7 +2823,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Sessão_4</t>
+          <t>Sessão_7</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2838,17 +2838,17 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>03-Mar-2026</t>
+          <t>26-Mar-2026</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>3918786000010126068</t>
+          <t>3918786000010126074</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -2865,7 +2865,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2880,7 +2880,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Sessão_3</t>
+          <t>Sessão_6</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2890,22 +2890,22 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>24-Feb-2026</t>
+          <t>17-Mar-2026</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>3918786000010126066</t>
+          <t>3918786000010126072</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -2922,7 +2922,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2937,7 +2937,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Sessão_2</t>
+          <t>Sessão_5</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2952,17 +2952,17 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>17-Feb-2026</t>
+          <t>10-Mar-2026</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>3918786000010126064</t>
+          <t>3918786000010126070</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -2979,7 +2979,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Sessão_1</t>
+          <t>Sessão_4</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3004,22 +3004,22 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>10-Feb-2026</t>
+          <t>03-Mar-2026</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>3918786000010126062</t>
+          <t>3918786000010126068</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3036,7 +3036,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3046,17 +3046,17 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>MONAPO RIO</t>
+          <t>NAHERENQUE</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Sessão_11</t>
+          <t>Sessão_3</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+          <t>NUCHATE ESTEVAO &amp; BELITO LUCIANO</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -3066,22 +3066,22 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>21-Apr-2026</t>
+          <t>24-Feb-2026</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>3918786000010102118</t>
+          <t>3918786000010126066</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3093,7 +3093,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3103,17 +3103,17 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>MATHAPUE</t>
+          <t>NAHERENQUE</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Sessão_11</t>
+          <t>Sessão_2</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>FERNANDES LIMA &amp; TAIRAHA ESQUADRO</t>
+          <t>NUCHATE ESTEVAO &amp; BELITO LUCIANO</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -3123,17 +3123,17 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>21-Apr-2026</t>
+          <t>17-Feb-2026</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>3918786000010098124</t>
+          <t>3918786000010126064</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3150,7 +3150,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3160,37 +3160,37 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>MATHAPUE</t>
+          <t>NAHERENQUE</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Sessão_10</t>
+          <t>Sessão_1</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>FERNANDES LIMA &amp; TAIRAHA ESQUADRO</t>
+          <t>NUCHATE ESTEVAO &amp; BELITO LUCIANO</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>21-Apr-2026</t>
+          <t>10-Feb-2026</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>3918786000010098122</t>
+          <t>3918786000010126062</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3207,7 +3207,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3217,17 +3217,17 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>MATHAPUE</t>
+          <t>MONAPO RIO</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Sessão_9</t>
+          <t>Sessão_11</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>FERNANDES LIMA &amp; TAIRAHA ESQUADRO</t>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -3242,17 +3242,17 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>3918786000010098120</t>
+          <t>3918786000010102118</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Nacala Porto</t>
+          <t>Monapo</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3264,7 +3264,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>MURRUPELANE</t>
+          <t>MATHAPUE</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3284,27 +3284,27 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
+          <t>FERNANDES LIMA &amp; TAIRAHA ESQUADRO</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>21-Apr-2026</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>3918786000010095084</t>
+          <t>3918786000010098124</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -3321,7 +3321,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3331,17 +3331,17 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>MOCONE</t>
+          <t>MATHAPUE</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Sessão_11</t>
+          <t>Sessão_10</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
+          <t>FERNANDES LIMA &amp; TAIRAHA ESQUADRO</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -3351,17 +3351,17 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>21-Apr-2026</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>3918786000010095002</t>
+          <t>3918786000010098122</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -3378,7 +3378,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3388,17 +3388,17 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>RAMIANE</t>
+          <t>MATHAPUE</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Sessão_11</t>
+          <t>Sessão_9</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+          <t>FERNANDES LIMA &amp; TAIRAHA ESQUADRO</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -3408,22 +3408,22 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>21-Apr-2026</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>32</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>3918786000010094010</t>
+          <t>3918786000010098120</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -3435,7 +3435,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3445,7 +3445,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>ONTUPAIA</t>
+          <t>MURRUPELANE</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3455,27 +3455,27 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>NUCHATE ESTEVAO &amp; BELITO LUCIANO</t>
+          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>3918786000010092104</t>
+          <t>3918786000010095084</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -3492,7 +3492,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3502,17 +3502,17 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>ONTUPAIA</t>
+          <t>MOCONE</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Sessão_10</t>
+          <t>Sessão_11</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>NUCHATE ESTEVAO &amp; BELITO LUCIANO</t>
+          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -3522,17 +3522,17 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>15-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>3918786000010092102</t>
+          <t>3918786000010095002</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -3549,7 +3549,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3559,17 +3559,17 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>ONTUPAIA</t>
+          <t>RAMIANE</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Sessão_9</t>
+          <t>Sessão_11</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>NUCHATE ESTEVAO &amp; BELITO LUCIANO</t>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -3579,22 +3579,22 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>08-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>3918786000010092100</t>
+          <t>3918786000010094010</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Nacala Porto</t>
+          <t>Monapo</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -3606,7 +3606,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3621,7 +3621,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Sessão_8</t>
+          <t>Sessão_11</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>01-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>3918786000010092098</t>
+          <t>3918786000010092104</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -3663,7 +3663,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3678,7 +3678,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Sessão_7</t>
+          <t>Sessão_10</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3693,17 +3693,17 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>25-Mar-2026</t>
+          <t>15-Apr-2026</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>3918786000010092096</t>
+          <t>3918786000010092102</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -3720,7 +3720,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3735,7 +3735,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Sessão_6</t>
+          <t>Sessão_9</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -3750,17 +3750,17 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>18-Mar-2026</t>
+          <t>08-Apr-2026</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>3918786000010092094</t>
+          <t>3918786000010092100</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -3792,7 +3792,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Sessão_5</t>
+          <t>Sessão_8</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -3807,17 +3807,17 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>11-Mar-2026</t>
+          <t>01-Apr-2026</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>3918786000010092092</t>
+          <t>3918786000010092098</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -3834,7 +3834,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3849,7 +3849,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Sessão_4</t>
+          <t>Sessão_7</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -3864,17 +3864,17 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>04-Mar-2026</t>
+          <t>25-Mar-2026</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>3918786000010092090</t>
+          <t>3918786000010092096</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -3891,7 +3891,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Sessão_3</t>
+          <t>Sessão_6</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -3921,7 +3921,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>25-Mar-2026</t>
+          <t>18-Mar-2026</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>3918786000010092088</t>
+          <t>3918786000010092094</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -3948,7 +3948,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3963,7 +3963,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Sessão_2</t>
+          <t>Sessão_5</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -3978,17 +3978,17 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>18-Feb-2026</t>
+          <t>11-Mar-2026</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>3918786000010092086</t>
+          <t>3918786000010092092</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -4005,7 +4005,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4020,7 +4020,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Sessão_1</t>
+          <t>Sessão_4</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4035,17 +4035,17 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>11-Feb-2026</t>
+          <t>04-Mar-2026</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>3918786000010092084</t>
+          <t>3918786000010092090</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -4062,7 +4062,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4072,17 +4072,17 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>MUELEGE</t>
+          <t>ONTUPAIA</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Sessão_11</t>
+          <t>Sessão_3</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+          <t>NUCHATE ESTEVAO &amp; BELITO LUCIANO</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -4092,22 +4092,22 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>25-Mar-2026</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>3918786000010091122</t>
+          <t>3918786000010092088</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -4119,7 +4119,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4129,17 +4129,17 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>ONTUPAIA</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Sessão_11</t>
+          <t>Sessão_2</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+          <t>NUCHATE ESTEVAO &amp; BELITO LUCIANO</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -4149,22 +4149,22 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>18-Feb-2026</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>3918786000010088069</t>
+          <t>3918786000010092086</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -4176,7 +4176,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4186,17 +4186,17 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>ONTUPAIA</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Sessão_11</t>
+          <t>Sessão_1</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+          <t>NUCHATE ESTEVAO &amp; BELITO LUCIANO</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -4206,22 +4206,22 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>11-Feb-2026</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>3918786000010088067</t>
+          <t>3918786000010092084</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -4233,7 +4233,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4243,7 +4243,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>MUELEGE</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -4253,7 +4253,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -4263,17 +4263,17 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>22-Apr-2026</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>3918786000010087128</t>
+          <t>3918786000010091122</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -4300,7 +4300,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>MESEREPANE</t>
+          <t>TOPELANE</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -4310,7 +4310,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>3918786000010087064</t>
+          <t>3918786000010088069</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -4347,7 +4347,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>MUELEGE</t>
+          <t>TOPELANE</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Sessão_10</t>
+          <t>Sessão_11</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4377,17 +4377,17 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>15-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>3918786000010070032</t>
+          <t>3918786000010088067</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -4404,7 +4404,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4419,12 +4419,12 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Sessão_9</t>
+          <t>Sessão_11</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -4434,17 +4434,17 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>15-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>3918786000010070030</t>
+          <t>3918786000010087128</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -4461,7 +4461,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4471,17 +4471,17 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>MESEREPANE</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Sessão_10</t>
+          <t>Sessão_11</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -4491,17 +4491,17 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>22-Apr-2026</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>3918786000010069058</t>
+          <t>3918786000010087064</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -4518,7 +4518,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4528,7 +4528,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>RAMIANE</t>
+          <t>MUELEGE</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -4538,7 +4538,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -4548,17 +4548,17 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>15-Apr-2026</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>3918786000010066060</t>
+          <t>3918786000010070032</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -4575,7 +4575,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4585,7 +4585,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>MOCONE</t>
+          <t>TOPELANE</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -4595,7 +4595,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -4605,22 +4605,22 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>08-Apr-2026</t>
+          <t>15-Apr-2026</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>3918786000010065072</t>
+          <t>3918786000010070030</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Nacala Porto</t>
+          <t>Monapo</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -4632,7 +4632,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -4642,17 +4642,17 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>MOCONE</t>
+          <t>TOPELANE</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Sessão_8</t>
+          <t>Sessão_10</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -4662,22 +4662,22 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>01-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>3918786000010065070</t>
+          <t>3918786000010069058</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Nacala Porto</t>
+          <t>Monapo</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -4689,7 +4689,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -4699,42 +4699,42 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>MOCONE</t>
+          <t>RAMIANE</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Sessão_7</t>
+          <t>Sessão_10</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>25-Mar-2026</t>
+          <t>16-Apr-2026</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>3918786000010065068</t>
+          <t>3918786000010066060</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Nacala Porto</t>
+          <t>Monapo</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -4746,7 +4746,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Sessão_6</t>
+          <t>Sessão_9</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -4771,22 +4771,22 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>18-Mar-2026</t>
+          <t>08-Apr-2026</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>3918786000010065066</t>
+          <t>3918786000010065072</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -4803,7 +4803,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -4818,7 +4818,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Sessão_5</t>
+          <t>Sessão_8</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -4833,17 +4833,17 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>11-Mar-2026</t>
+          <t>01-Apr-2026</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>3918786000010065064</t>
+          <t>3918786000010065070</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -4860,7 +4860,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -4875,7 +4875,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Sessão_4</t>
+          <t>Sessão_7</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -4885,22 +4885,22 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>04-Mar-2026</t>
+          <t>25-Mar-2026</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>3918786000010065062</t>
+          <t>3918786000010065068</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -4917,7 +4917,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -4932,7 +4932,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Sessão_3</t>
+          <t>Sessão_6</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -4942,22 +4942,22 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>25-Feb-2026</t>
+          <t>18-Mar-2026</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>3918786000010065060</t>
+          <t>3918786000010065066</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -4974,7 +4974,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -4989,7 +4989,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Sessão_2</t>
+          <t>Sessão_5</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -5004,17 +5004,17 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>18-Feb-2026</t>
+          <t>11-Mar-2026</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>3918786000010065058</t>
+          <t>3918786000010065064</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -5031,7 +5031,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Sessão_1</t>
+          <t>Sessão_4</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -5061,17 +5061,17 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>11-Feb-2026</t>
+          <t>04-Mar-2026</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>3918786000010065056</t>
+          <t>3918786000010065062</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -5081,14 +5081,14 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Sessão_10</t>
+          <t>Sessão_3</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -5113,22 +5113,22 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>15-Apr-2026</t>
+          <t>25-Feb-2026</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>3918786000010065054</t>
+          <t>3918786000010065060</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -5145,7 +5145,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>MURRUPELANE</t>
+          <t>MOCONE</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Sessão_10</t>
+          <t>Sessão_2</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -5175,17 +5175,17 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>14-Apr-2026</t>
+          <t>18-Feb-2026</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>3918786000010055144</t>
+          <t>3918786000010065058</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -5202,22 +5202,22 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>MURRUPELANE</t>
+          <t>MOCONE</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Sessão_9</t>
+          <t>Sessão_1</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -5232,17 +5232,17 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>09-Apr-2026</t>
+          <t>11-Feb-2026</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>3918786000010055142</t>
+          <t>3918786000010065056</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -5252,7 +5252,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -5269,12 +5269,12 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>MORRUPELANE</t>
+          <t>MOCONE</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Sessão_8</t>
+          <t>Sessão_10</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5289,17 +5289,17 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>31-Mar-2026</t>
+          <t>15-Apr-2026</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>3918786000010055140</t>
+          <t>3918786000010065054</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -5331,7 +5331,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Sessão_7</t>
+          <t>Sessão_10</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -5346,17 +5346,17 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>24-Mar-2026</t>
+          <t>14-Apr-2026</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>3918786000010055138</t>
+          <t>3918786000010055144</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -5373,12 +5373,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -5388,7 +5388,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Sessão_6</t>
+          <t>Sessão_9</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -5398,22 +5398,22 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>17-Mar-2026</t>
+          <t>09-Apr-2026</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>3918786000010055136</t>
+          <t>3918786000010055142</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -5423,14 +5423,14 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>MURRUPELANE</t>
+          <t>MORRUPELANE</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Sessão_5</t>
+          <t>Sessão_8</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -5460,17 +5460,17 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>10-Mar-2026</t>
+          <t>31-Mar-2026</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>3918786000010055134</t>
+          <t>3918786000010055140</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -5487,7 +5487,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Sessão_4</t>
+          <t>Sessão_7</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -5512,22 +5512,22 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>03-Mar-2026</t>
+          <t>24-Mar-2026</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>3918786000010055132</t>
+          <t>3918786000010055138</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -5544,7 +5544,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>MORRUPELANE</t>
+          <t>MURRUPELANE</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Sessão_3</t>
+          <t>Sessão_6</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -5569,22 +5569,22 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>24-Feb-2026</t>
+          <t>17-Mar-2026</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>3918786000010055130</t>
+          <t>3918786000010055136</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -5601,12 +5601,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -5616,7 +5616,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Sessão_2</t>
+          <t>Sessão_5</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -5631,17 +5631,17 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>17-Feb-2026</t>
+          <t>10-Mar-2026</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>3918786000010055128</t>
+          <t>3918786000010055134</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -5658,12 +5658,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -5673,7 +5673,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Sessão_1</t>
+          <t>Sessão_4</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -5683,22 +5683,22 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>10-Feb-2026</t>
+          <t>03-Mar-2026</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>3918786000010055126</t>
+          <t>3918786000010055132</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -5715,7 +5715,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -5725,17 +5725,17 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>MESEREPANE</t>
+          <t>MORRUPELANE</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Sessão_10</t>
+          <t>Sessão_3</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -5745,22 +5745,22 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>24-Feb-2026</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>3918786000010055064</t>
+          <t>3918786000010055130</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -5772,27 +5772,27 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>MONAPO RIO</t>
+          <t>MURRUPELANE</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Sessão_10</t>
+          <t>Sessão_2</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -5802,22 +5802,22 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>14-Apr-2026</t>
+          <t>17-Feb-2026</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>3918786000010050002</t>
+          <t>3918786000010055128</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -5829,52 +5829,52 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>MUELEGE</t>
+          <t>MURRUPELANE</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Sessão_3</t>
+          <t>Sessão_1</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+          <t>MAGROFATE JUSTINO &amp; BELO SIMAO</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>26-Feb-2026</t>
+          <t>10-Feb-2026</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>3918786000010039074</t>
+          <t>3918786000010055126</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -5886,7 +5886,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -5896,17 +5896,17 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>MUELEGE</t>
+          <t>MESEREPANE</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Sessão_4</t>
+          <t>Sessão_10</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -5916,17 +5916,17 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>05-Mar-2026</t>
+          <t>16-Apr-2026</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>3918786000010039072</t>
+          <t>3918786000010055064</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -5943,7 +5943,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -5953,17 +5953,17 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>MUELEGE</t>
+          <t>MONAPO RIO</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Sessão_2</t>
+          <t>Sessão_10</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -5973,17 +5973,17 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>19-Feb-2026</t>
+          <t>14-Apr-2026</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>3918786000010039070</t>
+          <t>3918786000010050002</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -6000,7 +6000,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6015,7 +6015,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Sessão_1</t>
+          <t>Sessão_3</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -6030,17 +6030,17 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>14-Feb-2026</t>
+          <t>26-Feb-2026</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>3918786000010039068</t>
+          <t>3918786000010039074</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -6057,7 +6057,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6067,12 +6067,12 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>MUELEGE</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Sessão_3</t>
+          <t>Sessão_4</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -6087,17 +6087,17 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>25-Mar-2026</t>
+          <t>05-Mar-2026</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>3918786000010039066</t>
+          <t>3918786000010039072</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -6114,7 +6114,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6124,7 +6124,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>MUELEGE</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -6144,17 +6144,17 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>18-Apr-2026</t>
+          <t>19-Feb-2026</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>3918786000010039064</t>
+          <t>3918786000010039070</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -6171,7 +6171,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6181,7 +6181,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>MUELEGE</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -6201,17 +6201,17 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>13-Feb-2026</t>
+          <t>14-Feb-2026</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>3918786000010039062</t>
+          <t>3918786000010039068</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -6228,7 +6228,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6243,7 +6243,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Sessão_4</t>
+          <t>Sessão_3</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -6258,17 +6258,17 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>04-Mar-2026</t>
+          <t>25-Mar-2026</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>3918786000010039060</t>
+          <t>3918786000010039066</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -6285,7 +6285,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6300,7 +6300,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Sessão_4</t>
+          <t>Sessão_2</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -6315,17 +6315,17 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>04-Mar-2026</t>
+          <t>18-Apr-2026</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>3918786000010039058</t>
+          <t>3918786000010039064</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -6342,7 +6342,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6357,7 +6357,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Sessão_3</t>
+          <t>Sessão_1</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -6372,17 +6372,17 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>25-Feb-2026</t>
+          <t>13-Feb-2026</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>3918786000010039056</t>
+          <t>3918786000010039062</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -6399,7 +6399,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6414,7 +6414,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Sessão_2</t>
+          <t>Sessão_4</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -6429,17 +6429,17 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>18-Feb-2026</t>
+          <t>04-Mar-2026</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>3918786000010039054</t>
+          <t>3918786000010039060</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -6456,7 +6456,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -6471,7 +6471,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Sessão_1</t>
+          <t>Sessão_4</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -6486,17 +6486,17 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>13-Feb-2026</t>
+          <t>04-Mar-2026</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>3918786000010039052</t>
+          <t>3918786000010039058</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -6523,12 +6523,12 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>MUELEGE</t>
+          <t>TOPELANE</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Sessão_9</t>
+          <t>Sessão_3</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -6543,17 +6543,17 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>14-Apr-2026</t>
+          <t>25-Feb-2026</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>3918786000010039050</t>
+          <t>3918786000010039056</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -6570,7 +6570,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Sessão_10</t>
+          <t>Sessão_2</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -6600,17 +6600,17 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>15-Apr-2026</t>
+          <t>18-Feb-2026</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>3918786000010037472</t>
+          <t>3918786000010039054</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -6627,7 +6627,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -6637,17 +6637,17 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>RAMIANE</t>
+          <t>TOPELANE</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Sessão_9</t>
+          <t>Sessão_1</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -6657,17 +6657,17 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>14-Apr-2026</t>
+          <t>13-Feb-2026</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>3918786000010037470</t>
+          <t>3918786000010039052</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -6684,7 +6684,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -6694,17 +6694,17 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>RAMIANE</t>
+          <t>MUELEGE</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Sessão_8</t>
+          <t>Sessão_9</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -6714,17 +6714,17 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>10-Apr-2026</t>
+          <t>14-Apr-2026</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>3918786000010023384</t>
+          <t>3918786000010039050</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -6741,7 +6741,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -6751,12 +6751,12 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>RAMIANE</t>
+          <t>TOPELANE</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Sessão_1</t>
+          <t>Sessão_10</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -6771,17 +6771,17 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>11-Feb-2026</t>
+          <t>15-Apr-2026</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>3918786000010023382</t>
+          <t>3918786000010037472</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -6808,7 +6808,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>RAMIANE</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -6828,7 +6828,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>08-Apr-2026</t>
+          <t>14-Apr-2026</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -6838,7 +6838,7 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>3918786000010023380</t>
+          <t>3918786000010037470</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -6865,12 +6865,12 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>RAMIANE</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Sessão_1</t>
+          <t>Sessão_8</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -6885,17 +6885,17 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>13-Feb-2026</t>
+          <t>10-Apr-2026</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>3918786000010023378</t>
+          <t>3918786000010023384</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -6912,47 +6912,47 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>RAMIANE</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Sessão_1</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>11-Feb-2026</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>RAMIANE</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>Sessão_7</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>09-Apr-2026</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>3918786000010020060</t>
+          <t>3918786000010023382</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -6969,7 +6969,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -6979,7 +6979,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>MESEREPANE</t>
+          <t>TOPELANE</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -6989,7 +6989,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -6999,17 +6999,17 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>09-Apr-2026</t>
+          <t>08-Apr-2026</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>3918786000010019064</t>
+          <t>3918786000010023380</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -7026,52 +7026,52 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>MATHAPUE</t>
+          <t>TOPELANE</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Sessão_8</t>
+          <t>Sessão_1</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>FERNANDES LIMA &amp; TAIRAHA ESQUADRO</t>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>31-Mar-2026</t>
+          <t>13-Feb-2026</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>3918786000010015292</t>
+          <t>3918786000010023378</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>Nacala Porto</t>
+          <t>Monapo</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -7083,17 +7083,17 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>MATHAPUE</t>
+          <t>RAMIANE</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -7103,17 +7103,17 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>FERNANDES LIMA &amp; TAIRAHA ESQUADRO</t>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>31-Mar-2026</t>
+          <t>09-Apr-2026</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>3918786000010015290</t>
+          <t>3918786000010020060</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>Nacala Porto</t>
+          <t>Monapo</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
@@ -7140,52 +7140,52 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>MATHAPUE</t>
+          <t>MESEREPANE</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Sessão_6</t>
+          <t>Sessão_9</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>FERNANDES LIMA &amp; TAIRAHA ESQUADRO</t>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>31-Mar-2026</t>
+          <t>09-Apr-2026</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>3918786000010015288</t>
+          <t>3918786000010019064</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>Nacala Porto</t>
+          <t>Monapo</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -7197,12 +7197,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Sessão_5</t>
+          <t>Sessão_8</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -7222,7 +7222,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>3918786000010015286</t>
+          <t>3918786000010015292</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -7254,34 +7254,34 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>MATHAPUE</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Sessão_7</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>FERNANDES LIMA &amp; TAIRAHA ESQUADRO</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>MATHAPUE</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>Sessão_4</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>FERNANDES LIMA &amp; TAIRAHA ESQUADRO</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="G122" t="inlineStr">
         <is>
           <t>31-Mar-2026</t>
@@ -7289,12 +7289,12 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>3918786000010015284</t>
+          <t>3918786000010015290</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -7311,12 +7311,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -7326,7 +7326,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Sessão_3</t>
+          <t>Sessão_6</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -7336,7 +7336,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -7346,12 +7346,12 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>3918786000010015282</t>
+          <t>3918786000010015288</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -7368,34 +7368,34 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>MATHAPUE</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Sessão_5</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>FERNANDES LIMA &amp; TAIRAHA ESQUADRO</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>MATHAPUE</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>Sessão_2</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>FERNANDES LIMA &amp; TAIRAHA ESQUADRO</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="G124" t="inlineStr">
         <is>
           <t>31-Mar-2026</t>
@@ -7403,12 +7403,12 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>3918786000010015280</t>
+          <t>3918786000010015286</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -7425,12 +7425,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -7440,7 +7440,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Sessão_1</t>
+          <t>Sessão_4</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -7450,7 +7450,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>3918786000010015278</t>
+          <t>3918786000010015284</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -7482,52 +7482,52 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>MONAPO RIO</t>
+          <t>MATHAPUE</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Sessão_9</t>
+          <t>Sessão_3</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+          <t>FERNANDES LIMA &amp; TAIRAHA ESQUADRO</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>08-Apr-2026</t>
+          <t>31-Mar-2026</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>3918786000010011002</t>
+          <t>3918786000010015282</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
@@ -7539,52 +7539,52 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>MATHAPUE</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Sessão_8</t>
+          <t>Sessão_2</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+          <t>FERNANDES LIMA &amp; TAIRAHA ESQUADRO</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>08-Apr-2026</t>
+          <t>31-Mar-2026</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>3918786000010007188</t>
+          <t>3918786000010015280</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
@@ -7596,52 +7596,52 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>MUELEGE</t>
+          <t>MATHAPUE</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Sessão_8</t>
+          <t>Sessão_1</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+          <t>FERNANDES LIMA &amp; TAIRAHA ESQUADRO</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>09-Apr-2026</t>
+          <t>31-Mar-2026</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>3918786000010007186</t>
+          <t>3918786000010015278</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>Monapo</t>
+          <t>Nacala Porto</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
@@ -7653,7 +7653,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -7663,7 +7663,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>MONAPO RIO</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -7673,7 +7673,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -7683,17 +7683,17 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>10-Apr-2026</t>
+          <t>08-Apr-2026</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>3918786000010005495</t>
+          <t>3918786000010011002</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -7710,7 +7710,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -7725,7 +7725,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Sessão_7</t>
+          <t>Sessão_8</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -7740,7 +7740,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>27-Mar-2026</t>
+          <t>08-Apr-2026</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -7750,7 +7750,7 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>3918786000009978061</t>
+          <t>3918786000010007188</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -7767,7 +7767,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -7777,12 +7777,12 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>MUELEGE</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Sessão_7</t>
+          <t>Sessão_8</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -7797,17 +7797,17 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>25-Mar-2026</t>
+          <t>09-Apr-2026</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>3918786000009978059</t>
+          <t>3918786000010007186</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
@@ -7839,7 +7839,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Sessão_6</t>
+          <t>Sessão_9</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -7854,17 +7854,17 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>25-Mar-2026</t>
+          <t>10-Apr-2026</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>3918786000009978057</t>
+          <t>3918786000010005495</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -7881,7 +7881,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -7896,7 +7896,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Sessão_5</t>
+          <t>Sessão_7</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -7911,7 +7911,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>11-Mar-2026</t>
+          <t>27-Mar-2026</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -7921,7 +7921,7 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>3918786000009978055</t>
+          <t>3918786000009978061</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -7938,7 +7938,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -7953,7 +7953,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Sessão_5</t>
+          <t>Sessão_7</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -7968,17 +7968,17 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>11-Mar-2026</t>
+          <t>25-Mar-2026</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>3918786000009978053</t>
+          <t>3918786000009978059</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -7995,7 +7995,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -8005,12 +8005,12 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>MUELEGE</t>
+          <t>TOPELANE</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Sessão_7</t>
+          <t>Sessão_6</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -8025,17 +8025,17 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>02-Apr-2026</t>
+          <t>25-Mar-2026</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>3918786000009978051</t>
+          <t>3918786000009978057</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -8052,7 +8052,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -8062,17 +8062,17 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>MESEREPANE</t>
+          <t>TOPELANE</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Sessão_8</t>
+          <t>Sessão_5</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -8082,17 +8082,17 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>02-Apr-2026</t>
+          <t>11-Mar-2026</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>3918786000009975096</t>
+          <t>3918786000009978055</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -8109,7 +8109,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -8119,17 +8119,17 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>RAMIANE</t>
+          <t>TOPELANE</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Sessão_6</t>
+          <t>Sessão_5</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -8139,17 +8139,17 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>02-Apr-2026</t>
+          <t>11-Mar-2026</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>3918786000009966138</t>
+          <t>3918786000009978053</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -8166,7 +8166,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -8176,17 +8176,17 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>MUELEGE</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Sessão_8</t>
+          <t>Sessão_7</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -8196,17 +8196,17 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>01-Apr-2026</t>
+          <t>02-Apr-2026</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>3918786000009966136</t>
+          <t>3918786000009978051</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -8223,7 +8223,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -8238,7 +8238,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Sessão_7</t>
+          <t>Sessão_8</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -8253,7 +8253,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>01-Apr-2026</t>
+          <t>02-Apr-2026</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>3918786000009964076</t>
+          <t>3918786000009975096</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -8280,7 +8280,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -8290,7 +8290,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>MESEREPANE</t>
+          <t>RAMIANE</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -8300,7 +8300,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -8310,17 +8310,17 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>08-Apr-2026</t>
+          <t>02-Apr-2026</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>3918786000009964074</t>
+          <t>3918786000009966138</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -8337,7 +8337,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -8347,17 +8347,17 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>MESEREPANE</t>
+          <t>TOPELANE</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Sessão_5</t>
+          <t>Sessão_8</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -8377,7 +8377,7 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>3918786000009964072</t>
+          <t>3918786000009966136</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -8394,7 +8394,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -8409,7 +8409,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Sessão_4</t>
+          <t>Sessão_7</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -8429,12 +8429,12 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>3918786000009964070</t>
+          <t>3918786000009964076</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -8451,7 +8451,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Sessão_3</t>
+          <t>Sessão_6</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -8481,17 +8481,17 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>01-Apr-2026</t>
+          <t>08-Apr-2026</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>3918786000009964068</t>
+          <t>3918786000009964074</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -8508,7 +8508,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -8523,7 +8523,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Sessão_2</t>
+          <t>Sessão_5</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -8543,12 +8543,12 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>3918786000009964066</t>
+          <t>3918786000009964072</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -8565,7 +8565,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -8580,7 +8580,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Sessão_1</t>
+          <t>Sessão_4</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -8600,12 +8600,12 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>3918786000009964064</t>
+          <t>3918786000009964070</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -8632,12 +8632,12 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>MONAPO RIO</t>
+          <t>MESEREPANE</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Sessão_8</t>
+          <t>Sessão_3</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -8652,17 +8652,17 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>31-Mar-2026</t>
+          <t>01-Apr-2026</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>3918786000009964062</t>
+          <t>3918786000009964068</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -8679,7 +8679,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -8689,17 +8689,17 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>MESEREPANE</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Sessão_8</t>
+          <t>Sessão_2</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -8714,12 +8714,12 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>3918786000009962078</t>
+          <t>3918786000009964066</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
@@ -8736,7 +8736,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -8746,12 +8746,12 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>MONAPO RIO</t>
+          <t>MESEREPANE</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Sessão_7</t>
+          <t>Sessão_1</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -8766,17 +8766,17 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>24-Mar-2026</t>
+          <t>01-Apr-2026</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>3918786000009962026</t>
+          <t>3918786000009964064</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
@@ -8808,7 +8808,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Sessão_6</t>
+          <t>Sessão_8</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -8823,17 +8823,17 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>17-Mar-2026</t>
+          <t>31-Mar-2026</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>3918786000009962024</t>
+          <t>3918786000009964062</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
@@ -8850,7 +8850,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -8860,17 +8860,17 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>MONAPO RIO</t>
+          <t>TOPELANE</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Sessão_5</t>
+          <t>Sessão_8</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -8880,17 +8880,17 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>10-Mar-2026</t>
+          <t>01-Apr-2026</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>3918786000009962022</t>
+          <t>3918786000009962078</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -8922,7 +8922,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Sessão_4</t>
+          <t>Sessão_7</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -8937,17 +8937,17 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>03-Mar-2026</t>
+          <t>24-Mar-2026</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>3918786000009962020</t>
+          <t>3918786000009962026</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
@@ -8979,7 +8979,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Sessão_3</t>
+          <t>Sessão_6</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -8994,17 +8994,17 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>24-Feb-2026</t>
+          <t>17-Mar-2026</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>3918786000009962018</t>
+          <t>3918786000009962024</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -9036,7 +9036,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Sessão_2</t>
+          <t>Sessão_5</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -9051,17 +9051,17 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>17-Feb-2026</t>
+          <t>10-Mar-2026</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>3918786000009962016</t>
+          <t>3918786000009962022</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
@@ -9093,7 +9093,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Sessão_1</t>
+          <t>Sessão_4</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -9108,17 +9108,17 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>13-Feb-2026</t>
+          <t>03-Mar-2026</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>3918786000009962014</t>
+          <t>3918786000009962020</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
@@ -9135,7 +9135,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -9145,17 +9145,17 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>RAMIANE</t>
+          <t>MONAPO RIO</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Sessão_5</t>
+          <t>Sessão_3</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -9165,17 +9165,17 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>26-Mar-2026</t>
+          <t>24-Feb-2026</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>3918786000009891291</t>
+          <t>3918786000009962018</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
@@ -9192,7 +9192,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -9202,17 +9202,17 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>MONAPO RIO</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Sessão_7</t>
+          <t>Sessão_2</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -9222,17 +9222,17 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>25-Mar-2026</t>
+          <t>17-Feb-2026</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>3918786000009891287</t>
+          <t>3918786000009962016</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
@@ -9249,7 +9249,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -9259,17 +9259,17 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>MONAPO RIO</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Sessão_6</t>
+          <t>Sessão_1</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+          <t>SERGIO FAUSTO &amp; ZITO JOSIAS</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -9279,17 +9279,17 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>25-Mar-2026</t>
+          <t>13-Feb-2026</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>3918786000009888175</t>
+          <t>3918786000009962014</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
@@ -9306,7 +9306,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -9316,17 +9316,17 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>MUELEGE</t>
+          <t>RAMIANE</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Sessão_6</t>
+          <t>Sessão_5</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -9336,7 +9336,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>19-Mar-2026</t>
+          <t>26-Mar-2026</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -9346,7 +9346,7 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>3918786000009886133</t>
+          <t>3918786000009891291</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
@@ -9363,7 +9363,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -9373,17 +9373,17 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>MUELEGE</t>
+          <t>TOPELANE</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Sessão_5</t>
+          <t>Sessão_7</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -9393,17 +9393,17 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>12-Mar-2026</t>
+          <t>25-Mar-2026</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>3918786000009886129</t>
+          <t>3918786000009891287</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
@@ -9420,7 +9420,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -9435,12 +9435,12 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Sessão_2</t>
+          <t>Sessão_6</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -9450,17 +9450,17 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>18-Feb-2026</t>
+          <t>25-Mar-2026</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>3918786000009856153</t>
+          <t>3918786000009888175</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
@@ -9477,7 +9477,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -9487,17 +9487,17 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>MUELEGE</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Sessão_3</t>
+          <t>Sessão_6</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -9507,7 +9507,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>25-Feb-2026</t>
+          <t>19-Mar-2026</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -9517,7 +9517,7 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>3918786000009856149</t>
+          <t>3918786000009886133</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
@@ -9534,7 +9534,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -9544,17 +9544,17 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>MUELEGE</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Sessão_4</t>
+          <t>Sessão_5</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+          <t>PAULO ALEXANDRE &amp; TOMAS NHAMPA</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -9564,17 +9564,17 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>04-Mar-2026</t>
+          <t>12-Mar-2026</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>3918786000009856145</t>
+          <t>3918786000009886129</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
@@ -9601,7 +9601,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>RAMIANE</t>
+          <t>TOPELANE</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -9621,17 +9621,17 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>19-Feb-2026</t>
+          <t>18-Feb-2026</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>3918786000009856141</t>
+          <t>3918786000009856153</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
@@ -9648,7 +9648,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -9658,7 +9658,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>RAMIANE</t>
+          <t>TOPELANE</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -9678,17 +9678,17 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>26-Feb-2026</t>
+          <t>25-Feb-2026</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>3918786000009856137</t>
+          <t>3918786000009856149</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
@@ -9705,7 +9705,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -9720,7 +9720,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Sessão_5</t>
+          <t>Sessão_4</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -9735,17 +9735,17 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>11-Mar-2026</t>
+          <t>04-Mar-2026</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>3918786000009856133</t>
+          <t>3918786000009856145</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
@@ -9762,7 +9762,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -9772,12 +9772,12 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>TOPELANE</t>
+          <t>RAMIANE</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Sessão_6</t>
+          <t>Sessão_2</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -9792,17 +9792,17 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>17-Mar-2026</t>
+          <t>19-Feb-2026</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>3918786000009856129</t>
+          <t>3918786000009856141</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
@@ -9819,55 +9819,226 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>RAMIANE</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Sessão_3</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>26-Feb-2026</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>3918786000009856137</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>TOPELANE</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Sessão_5</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>11-Mar-2026</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>3918786000009856133</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>TOPELANE</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Sessão_6</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>17-Mar-2026</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>3918786000009856129</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>Monapo</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr">
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
         <is>
           <t>RAMIANE</t>
         </is>
       </c>
-      <c r="D167" t="inlineStr">
+      <c r="D170" t="inlineStr">
         <is>
           <t>Sessão_4</t>
         </is>
       </c>
-      <c r="E167" t="inlineStr">
+      <c r="E170" t="inlineStr">
         <is>
           <t>COSTA MARQUES &amp; OTILIA PASSIEL</t>
         </is>
       </c>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G167" t="inlineStr">
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
         <is>
           <t>19-Mar-2026</t>
         </is>
       </c>
-      <c r="H167" t="inlineStr">
+      <c r="H170" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="I167" t="inlineStr">
+      <c r="I170" t="inlineStr">
         <is>
           <t>3918786000009856125</t>
         </is>
       </c>
-      <c r="J167" t="inlineStr">
+      <c r="J170" t="inlineStr">
         <is>
           <t>Monapo</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr">
+      <c r="K170" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -10134,13 +10305,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4B4200DC-FCE5-4054-A69F-C214589C833C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6DF66064-9E6D-454B-A278-049E0AF7A007}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5A7E49F4-0F06-4A31-B05F-84A8235AF667}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{46159C7B-FEBD-4BA3-BF4F-D67258D0263C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6891425A-5736-4BB5-AC64-DEB39513C3E9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DFF3CEA8-968B-4FB1-8983-6A4839D8E81C}"/>
 </file>
--- a/Qualidade_Sessoes.xlsx
+++ b/Qualidade_Sessoes.xlsx
@@ -10047,271 +10047,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100DC8BB5B596CFDD4794B3344F0E8F53A4" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="481cb719fb2f51215cc00c8d40533043">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="20d57abc-823c-4051-a81a-1a0a01a8f39e" xmlns:ns3="54c5ab46-7543-4aba-b0fa-79d6a199bef5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="71df0815368817fe9627576b1e062219" ns2:_="" ns3:_="">
-    <xsd:import namespace="20d57abc-823c-4051-a81a-1a0a01a8f39e"/>
-    <xsd:import namespace="54c5ab46-7543-4aba-b0fa-79d6a199bef5"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="20d57abc-823c-4051-a81a-1a0a01a8f39e" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="16" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="17" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="19" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="edc6e55a-975c-4e83-894d-449406ca2714" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="21" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="22" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="54c5ab46-7543-4aba-b0fa-79d6a199bef5" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="12" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="13" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="20" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{21a739d7-e82a-41d6-a891-a689fdcdcba6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="54c5ab46-7543-4aba-b0fa-79d6a199bef5">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="54c5ab46-7543-4aba-b0fa-79d6a199bef5" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="20d57abc-823c-4051-a81a-1a0a01a8f39e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6DF66064-9E6D-454B-A278-049E0AF7A007}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{46159C7B-FEBD-4BA3-BF4F-D67258D0263C}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DFF3CEA8-968B-4FB1-8983-6A4839D8E81C}"/>
 </file>
--- a/Qualidade_Sessoes.xlsx
+++ b/Qualidade_Sessoes.xlsx
@@ -10047,4 +10047,271 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100DC8BB5B596CFDD4794B3344F0E8F53A4" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="481cb719fb2f51215cc00c8d40533043">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="20d57abc-823c-4051-a81a-1a0a01a8f39e" xmlns:ns3="54c5ab46-7543-4aba-b0fa-79d6a199bef5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="71df0815368817fe9627576b1e062219" ns2:_="" ns3:_="">
+    <xsd:import namespace="20d57abc-823c-4051-a81a-1a0a01a8f39e"/>
+    <xsd:import namespace="54c5ab46-7543-4aba-b0fa-79d6a199bef5"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="20d57abc-823c-4051-a81a-1a0a01a8f39e" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="16" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="17" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="19" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="edc6e55a-975c-4e83-894d-449406ca2714" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="21" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="22" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="54c5ab46-7543-4aba-b0fa-79d6a199bef5" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="12" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="13" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="20" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{21a739d7-e82a-41d6-a891-a689fdcdcba6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="54c5ab46-7543-4aba-b0fa-79d6a199bef5">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="54c5ab46-7543-4aba-b0fa-79d6a199bef5" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="20d57abc-823c-4051-a81a-1a0a01a8f39e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CC439CF6-9315-4939-97B0-6B3B54792452}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6DE09368-BF4E-425C-8506-DE7AA3F692B7}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5B01AB1F-B90D-48DB-9B99-9A1AE4419568}"/>
 </file>
--- a/Qualidade_Sessoes.xlsx
+++ b/Qualidade_Sessoes.xlsx
@@ -10305,13 +10305,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CC439CF6-9315-4939-97B0-6B3B54792452}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A10AC6AC-8705-469D-8149-D10956DE0CD5}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6DE09368-BF4E-425C-8506-DE7AA3F692B7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FFB6F85F-A402-4B53-830F-A99DEA1544D1}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5B01AB1F-B90D-48DB-9B99-9A1AE4419568}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D11353ED-4446-4AB4-9FC4-8DD1687CE22E}"/>
 </file>
--- a/Qualidade_Sessoes.xlsx
+++ b/Qualidade_Sessoes.xlsx
@@ -10305,13 +10305,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A10AC6AC-8705-469D-8149-D10956DE0CD5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{17C03E81-6C94-48BF-8793-32440DC620D9}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FFB6F85F-A402-4B53-830F-A99DEA1544D1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB788E5D-2D79-4363-AF59-D9AE6FBE16C9}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D11353ED-4446-4AB4-9FC4-8DD1687CE22E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{73DE38E5-A439-4DFE-870D-009DEC8E8546}"/>
 </file>